--- a/docs/scripts_reference.xlsx
+++ b/docs/scripts_reference.xlsx
@@ -355,7 +355,7 @@
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">193 件</t>
+          <t xml:space="preserve">205 件</t>
         </is>
       </c>
     </row>
@@ -6541,76 +6541,68 @@
     <row r="125" ht="33.0" customHeight="1">
       <c r="A125" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
+          <t xml:space="preserve">4.6-3 JMeter 性能試験 (jmeter コンテナの呼び出し)</t>
         </is>
       </c>
       <c r="B125" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--env-list-limit N\|all</t>
+          <t xml:space="preserve">--jmeter-service NAME</t>
         </is>
       </c>
       <c r="C125" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 以上の整数または all</t>
+          <t xml:space="preserve">Compose サービス名</t>
         </is>
       </c>
       <c r="D125" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">all</t>
-        </is>
-      </c>
-      <c r="E125" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">不可</t>
-        </is>
-      </c>
+          <t xml:space="preserve">jmeter</t>
+        </is>
+      </c>
+      <c r="E125" s="7"/>
       <c r="F125" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">環境変数一覧の表示件数 (コンテナごと)</t>
-        </is>
-      </c>
-    </row>
-    <row r="126" ht="19.5" customHeight="1">
+          <t xml:space="preserve">JMeter 実行コンテナのサービス名 (→ 5.4-5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="126" ht="33.0" customHeight="1">
       <c r="A126" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
+          <t xml:space="preserve">4.6-3 JMeter 性能試験 (jmeter コンテナの呼び出し)</t>
         </is>
       </c>
       <c r="B126" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--env-list-file FILE</t>
+          <t xml:space="preserve">--jmeter-profile NAME</t>
         </is>
       </c>
       <c r="C126" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ファイルパス</t>
-        </is>
-      </c>
-      <c r="D126" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(なし)</t>
-        </is>
-      </c>
-      <c r="E126" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">不可</t>
-        </is>
-      </c>
+          <t xml:space="preserve">profiles 名</t>
+        </is>
+      </c>
+      <c r="D126" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">loadtest</t>
+        </is>
+      </c>
+      <c r="E126" s="7"/>
       <c r="F126" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">環境変数一覧をファイルにも出力</t>
-        </is>
-      </c>
-    </row>
-    <row r="127" ht="19.5" customHeight="1">
+          <t xml:space="preserve">compose へ --profile として渡す値</t>
+        </is>
+      </c>
+    </row>
+    <row r="127" ht="33.0" customHeight="1">
       <c r="A127" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
+          <t xml:space="preserve">4.6-3 JMeter 性能試験 (jmeter コンテナの呼び出し)</t>
         </is>
       </c>
       <c r="B127" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-tree</t>
+          <t xml:space="preserve">--no-jmeter-profile</t>
         </is>
       </c>
       <c r="C127" s="3" t="inlineStr">
@@ -6618,371 +6610,331 @@
           <t xml:space="preserve">フラグ</t>
         </is>
       </c>
-      <c r="D127" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false (非表示)</t>
-        </is>
-      </c>
-      <c r="E127" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">不可</t>
-        </is>
-      </c>
+      <c r="D127" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="E127" s="7"/>
       <c r="F127" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">コンテナ内ツリーと JBoss EAP デプロイ構造を画面へ表示する</t>
-        </is>
-      </c>
-    </row>
-    <row r="128" ht="19.5" customHeight="1">
+          <t xml:space="preserve">compose へ --profile を渡さない (profiles を使っていない構成)</t>
+        </is>
+      </c>
+    </row>
+    <row r="128" ht="33.0" customHeight="1">
       <c r="A128" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
+          <t xml:space="preserve">4.6-3 JMeter 性能試験 (jmeter コンテナの呼び出し)</t>
         </is>
       </c>
       <c r="B128" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-directory-tree</t>
+          <t xml:space="preserve">--jmeter-report-dir DIR</t>
         </is>
       </c>
       <c r="C128" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
-        </is>
-      </c>
-      <c r="D128" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
-        </is>
-      </c>
-      <c r="E128" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">不可</t>
-        </is>
-      </c>
+          <t xml:space="preserve">ディレクトリパス</t>
+        </is>
+      </c>
+      <c r="D128" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(--report-dir → 一時ディレクトリ)</t>
+        </is>
+      </c>
+      <c r="E128" s="7"/>
       <c r="F128" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">上記の画面表示を行わない。深さ等の指定による自動有効化も打ち消す</t>
+          <t xml:space="preserve">結果 (result.jtl / report/index.html / jmeter.log) の出力先</t>
         </is>
       </c>
     </row>
     <row r="129" ht="33.0" customHeight="1">
       <c r="A129" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
+          <t xml:space="preserve">4.6-3 JMeter 性能試験 (jmeter コンテナの呼び出し)</t>
         </is>
       </c>
       <c r="B129" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-tree-report</t>
+          <t xml:space="preserve">--jmeter-plan FILE</t>
         </is>
       </c>
       <c r="C129" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
+          <t xml:space="preserve">.jmx のファイル名</t>
         </is>
       </c>
       <c r="D129" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">false (非出力)</t>
-        </is>
-      </c>
-      <c r="E129" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">不可</t>
-        </is>
-      </c>
+          <t xml:space="preserve">(対話で選択)</t>
+        </is>
+      </c>
+      <c r="E129" s="7"/>
       <c r="F129" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">全量レポートの [3] [4] へツリーとデプロイ構造を出力する (--report-dir と併用)</t>
-        </is>
-      </c>
-    </row>
-    <row r="130" ht="19.5" customHeight="1">
+          <t xml:space="preserve">実行するテスト計画</t>
+        </is>
+      </c>
+    </row>
+    <row r="130" ht="33.0" customHeight="1">
       <c r="A130" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
+          <t xml:space="preserve">4.6-3 JMeter 性能試験 (jmeter コンテナの呼び出し)</t>
         </is>
       </c>
       <c r="B130" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-directory-tree-report</t>
+          <t xml:space="preserve">--jmeter-threads N</t>
         </is>
       </c>
       <c r="C130" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
+          <t xml:space="preserve">1 以上の整数</t>
         </is>
       </c>
       <c r="D130" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">true (既定)</t>
-        </is>
-      </c>
-      <c r="E130" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">不可</t>
-        </is>
-      </c>
+          <t xml:space="preserve">(対話で入力)</t>
+        </is>
+      </c>
+      <c r="E130" s="7"/>
       <c r="F130" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">全量レポートへツリーとデプロイ構造を出力しない</t>
-        </is>
-      </c>
-    </row>
-    <row r="131" ht="49.5" customHeight="1">
+          <t xml:space="preserve">スレッド数 (同時実行ユーザ数) の上書き値</t>
+        </is>
+      </c>
+    </row>
+    <row r="131" ht="33.0" customHeight="1">
       <c r="A131" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
+          <t xml:space="preserve">4.6-3 JMeter 性能試験 (jmeter コンテナの呼び出し)</t>
         </is>
       </c>
       <c r="B131" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-tree-excel</t>
+          <t xml:space="preserve">--jmeter-rampup SEC</t>
         </is>
       </c>
       <c r="C131" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
+          <t xml:space="preserve">0 以上の整数</t>
         </is>
       </c>
       <c r="D131" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">false (非出力)</t>
-        </is>
-      </c>
-      <c r="E131" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">不可</t>
-        </is>
-      </c>
+          <t xml:space="preserve">(対話で入力)</t>
+        </is>
+      </c>
+      <c r="E131" s="7"/>
       <c r="F131" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ディレクトリとシンボリックリンクのツリーを Excel ブック (.xlsx) へ追加出力する。リンク先は右端の列へ並べる。対象は frontend と backend の両方のコンテナ (--report-dir または --directory-tree-excel-file と併用)</t>
-        </is>
-      </c>
-    </row>
-    <row r="132" ht="19.5" customHeight="1">
+          <t xml:space="preserve">Ramp-Up 期間 (秒) の上書き値</t>
+        </is>
+      </c>
+    </row>
+    <row r="132" ht="33.0" customHeight="1">
       <c r="A132" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
+          <t xml:space="preserve">4.6-3 JMeter 性能試験 (jmeter コンテナの呼び出し)</t>
         </is>
       </c>
       <c r="B132" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-directory-tree-excel</t>
+          <t xml:space="preserve">--jmeter-loops N</t>
         </is>
       </c>
       <c r="C132" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
+          <t xml:space="preserve">1 以上の整数または -1</t>
         </is>
       </c>
       <c r="D132" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">true (既定)</t>
-        </is>
-      </c>
-      <c r="E132" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">不可</t>
-        </is>
-      </c>
+          <t xml:space="preserve">(対話で入力)</t>
+        </is>
+      </c>
+      <c r="E132" s="7"/>
       <c r="F132" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">上記の Excel 出力を行わない</t>
+          <t xml:space="preserve">ループ回数の上書き値 (-1 = 試験時間まで無限に回す)</t>
         </is>
       </c>
     </row>
     <row r="133" ht="33.0" customHeight="1">
       <c r="A133" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
+          <t xml:space="preserve">4.6-3 JMeter 性能試験 (jmeter コンテナの呼び出し)</t>
         </is>
       </c>
       <c r="B133" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-tree-excel-file FILE</t>
+          <t xml:space="preserve">--jmeter-target NAME</t>
         </is>
       </c>
       <c r="C133" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">.xlsx のパス</t>
-        </is>
-      </c>
-      <c r="D133" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(なし)</t>
-        </is>
-      </c>
-      <c r="E133" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">不可</t>
-        </is>
-      </c>
+          <t xml:space="preserve">targets.json のキー</t>
+        </is>
+      </c>
+      <c r="D133" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(コンテナの既定)</t>
+        </is>
+      </c>
+      <c r="E133" s="7"/>
       <c r="F133" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">上記 Excel の出力先を明示指定する。指定すると Excel 出力を有効にする (--report-dir が無くても出力できる)</t>
+          <t xml:space="preserve">負荷をかける相手 (frontend / backend / alb など)</t>
         </is>
       </c>
     </row>
     <row r="134" ht="33.0" customHeight="1">
       <c r="A134" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
+          <t xml:space="preserve">4.6-3 JMeter 性能試験 (jmeter コンテナの呼び出し)</t>
         </is>
       </c>
       <c r="B134" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-tree-depth N\|all</t>
+          <t xml:space="preserve">--jmeter-duration SEC</t>
         </is>
       </c>
       <c r="C134" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 以上の整数または all</t>
+          <t xml:space="preserve">0 以上の整数</t>
         </is>
       </c>
       <c r="D134" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">all</t>
-        </is>
-      </c>
-      <c r="E134" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">不可</t>
-        </is>
-      </c>
+          <t xml:space="preserve">(コンテナの既定)</t>
+        </is>
+      </c>
+      <c r="E134" s="7"/>
       <c r="F134" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">コンテナ内ツリーの最大深さ (/ 直下を 1 とする)。指定すると画面表示を自動で有効化</t>
+          <t xml:space="preserve">試験時間 (秒)</t>
         </is>
       </c>
     </row>
     <row r="135" ht="33.0" customHeight="1">
       <c r="A135" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
+          <t xml:space="preserve">4.6-3 JMeter 性能試験 (jmeter コンテナの呼び出し)</t>
         </is>
       </c>
       <c r="B135" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-file-limit N\|all</t>
+          <t xml:space="preserve">--no-jmeter-build</t>
         </is>
       </c>
       <c r="C135" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 以上の整数または all</t>
-        </is>
-      </c>
-      <c r="D135" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(ファイル非表示)</t>
-        </is>
-      </c>
-      <c r="E135" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">不可</t>
-        </is>
-      </c>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D135" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="E135" s="7"/>
       <c r="F135" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">通常ファイルの表示を有効化。N 件超過時は拡張子別件数を表示。指定すると画面表示を自動で有効化</t>
+          <t xml:space="preserve">実行前の compose build &lt;jmeter サービス&gt; を行わない</t>
         </is>
       </c>
     </row>
     <row r="136" ht="33.0" customHeight="1">
       <c r="A136" s="11" t="inlineStr">
         <is>
+          <t xml:space="preserve">4.6-3 JMeter 性能試験 (jmeter コンテナの呼び出し)</t>
+        </is>
+      </c>
+      <c r="B136" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--jmeter-status</t>
+        </is>
+      </c>
+      <c r="C136" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D136" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="E136" s="7"/>
+      <c r="F136" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">実行状況を表示して終了する (ビルド・起動・後始末をしない)</t>
+        </is>
+      </c>
+    </row>
+    <row r="137" ht="33.0" customHeight="1">
+      <c r="A137" s="11" t="inlineStr">
+        <is>
           <t xml:space="preserve">4.7 情報表示・レポート</t>
         </is>
       </c>
-      <c r="B136" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--deployment-dir-env NAME</t>
-        </is>
-      </c>
-      <c r="C136" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">環境変数名</t>
-        </is>
-      </c>
-      <c r="D136" s="3" t="inlineStr">
+      <c r="B137" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--env-list-limit N\|all</t>
+        </is>
+      </c>
+      <c r="C137" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 以上の整数または all</t>
+        </is>
+      </c>
+      <c r="D137" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">all</t>
+        </is>
+      </c>
+      <c r="E137" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
+      <c r="F137" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">環境変数一覧の表示件数 (コンテナごと)</t>
+        </is>
+      </c>
+    </row>
+    <row r="138" ht="19.5" customHeight="1">
+      <c r="A138" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
+        </is>
+      </c>
+      <c r="B138" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--env-list-file FILE</t>
+        </is>
+      </c>
+      <c r="C138" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ファイルパス</t>
+        </is>
+      </c>
+      <c r="D138" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">(なし)</t>
         </is>
       </c>
-      <c r="E136" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">可</t>
-        </is>
-      </c>
-      <c r="F136" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ディレクトリパスを値に持つ環境変数。その配下を階層表示。指定すると画面表示を自動で有効化</t>
-        </is>
-      </c>
-    </row>
-    <row r="137" ht="115.5" customHeight="1">
-      <c r="A137" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
-        </is>
-      </c>
-      <c r="B137" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--report-dir DIR</t>
-        </is>
-      </c>
-      <c r="C137" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ディレクトリパス</t>
-        </is>
-      </c>
-      <c r="D137" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(なし)</t>
-        </is>
-      </c>
-      <c r="E137" s="7" t="inlineStr">
+      <c r="E138" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">不可</t>
         </is>
       </c>
-      <c r="F137" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">全量レポートを DIR/build_and_verify_&lt;日時&gt;.txt へ保存。サービス別ビルドログ (..._build_log_&lt;サービス名&gt;.txt) と読み取り専用ファイルシステム分析の Excel / テキストも同じディレクトリへ追加出力。Java 例外解析の Excel / テキストは --deploy-exception-excel / --deploy-exception-text 指定時のみ。ディレクトリ構成のツリー Excel は --directory-tree-excel 指定時のみ。ツリーとデプロイ構造は --directory-tree-report、[10] は --deploy-exception-report、[11] は --readonly-analysis-report 併用時のみ保存</t>
-        </is>
-      </c>
-    </row>
-    <row r="138" ht="33.0" customHeight="1">
-      <c r="A138" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
-        </is>
-      </c>
-      <c r="B138" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--deploy-exception-display</t>
-        </is>
-      </c>
-      <c r="C138" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">フラグ</t>
-        </is>
-      </c>
-      <c r="D138" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false (非表示)</t>
-        </is>
-      </c>
-      <c r="E138" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">不可</t>
-        </is>
-      </c>
       <c r="F138" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">WAR デプロイ時 Java 例外解析の結果を画面へ表示する。既定では表示しない。--no-deploy-exception-analysis とは排他</t>
+          <t xml:space="preserve">環境変数一覧をファイルにも出力</t>
         </is>
       </c>
     </row>
@@ -6994,7 +6946,7 @@
       </c>
       <c r="B139" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-deploy-exception-display</t>
+          <t xml:space="preserve">--directory-tree</t>
         </is>
       </c>
       <c r="C139" s="3" t="inlineStr">
@@ -7002,9 +6954,9 @@
           <t xml:space="preserve">フラグ</t>
         </is>
       </c>
-      <c r="D139" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">—</t>
+      <c r="D139" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false (非表示)</t>
         </is>
       </c>
       <c r="E139" s="7" t="inlineStr">
@@ -7014,11 +6966,11 @@
       </c>
       <c r="F139" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">画面表示を行わない (既定と同じ。--deploy-exception-display を打ち消す)</t>
-        </is>
-      </c>
-    </row>
-    <row r="140" ht="49.5" customHeight="1">
+          <t xml:space="preserve">コンテナ内ツリーと JBoss EAP デプロイ構造を画面へ表示する</t>
+        </is>
+      </c>
+    </row>
+    <row r="140" ht="19.5" customHeight="1">
       <c r="A140" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">4.7 情報表示・レポート</t>
@@ -7026,7 +6978,7 @@
       </c>
       <c r="B140" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--deploy-exception-report</t>
+          <t xml:space="preserve">--no-directory-tree</t>
         </is>
       </c>
       <c r="C140" s="3" t="inlineStr">
@@ -7034,9 +6986,9 @@
           <t xml:space="preserve">フラグ</t>
         </is>
       </c>
-      <c r="D140" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false (非出力)</t>
+      <c r="D140" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
         </is>
       </c>
       <c r="E140" s="7" t="inlineStr">
@@ -7046,7 +6998,7 @@
       </c>
       <c r="F140" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">--report-dir の全量レポート [10] へ解析結果を出力する。既定では出力せず、見出しの下に未出力である旨だけを残す。--no-deploy-exception-analysis とは排他</t>
+          <t xml:space="preserve">上記の画面表示を行わない。深さ等の指定による自動有効化も打ち消す</t>
         </is>
       </c>
     </row>
@@ -7058,7 +7010,7 @@
       </c>
       <c r="B141" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-deploy-exception-report</t>
+          <t xml:space="preserve">--directory-tree-report</t>
         </is>
       </c>
       <c r="C141" s="3" t="inlineStr">
@@ -7066,9 +7018,9 @@
           <t xml:space="preserve">フラグ</t>
         </is>
       </c>
-      <c r="D141" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">—</t>
+      <c r="D141" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false (非出力)</t>
         </is>
       </c>
       <c r="E141" s="7" t="inlineStr">
@@ -7078,11 +7030,11 @@
       </c>
       <c r="F141" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">全量レポートへ解析結果を出力しない (既定と同じ。--deploy-exception-report を打ち消す)</t>
-        </is>
-      </c>
-    </row>
-    <row r="142" ht="33.0" customHeight="1">
+          <t xml:space="preserve">全量レポートの [3] [4] へツリーとデプロイ構造を出力する (--report-dir と併用)</t>
+        </is>
+      </c>
+    </row>
+    <row r="142" ht="19.5" customHeight="1">
       <c r="A142" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">4.7 情報表示・レポート</t>
@@ -7090,17 +7042,17 @@
       </c>
       <c r="B142" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--deploy-exception-excel FILE</t>
+          <t xml:space="preserve">--no-directory-tree-report</t>
         </is>
       </c>
       <c r="C142" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">.xlsx のパス</t>
-        </is>
-      </c>
-      <c r="D142" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(なし)</t>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D142" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">true (既定)</t>
         </is>
       </c>
       <c r="E142" s="7" t="inlineStr">
@@ -7110,11 +7062,11 @@
       </c>
       <c r="F142" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">WAR デプロイ時 Java 例外解析の Excel 出力先。指定したときだけ出力する (--report-dir だけでは出力しない)。--no-deploy-exception-analysis とは排他</t>
-        </is>
-      </c>
-    </row>
-    <row r="143" ht="33.0" customHeight="1">
+          <t xml:space="preserve">全量レポートへツリーとデプロイ構造を出力しない</t>
+        </is>
+      </c>
+    </row>
+    <row r="143" ht="49.5" customHeight="1">
       <c r="A143" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">4.7 情報表示・レポート</t>
@@ -7122,17 +7074,17 @@
       </c>
       <c r="B143" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--deploy-exception-text FILE</t>
+          <t xml:space="preserve">--directory-tree-excel</t>
         </is>
       </c>
       <c r="C143" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ファイルパス</t>
-        </is>
-      </c>
-      <c r="D143" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(なし。指定時のみ出力)</t>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D143" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false (非出力)</t>
         </is>
       </c>
       <c r="E143" s="7" t="inlineStr">
@@ -7142,7 +7094,7 @@
       </c>
       <c r="F143" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">同じ内容のテキスト出力先。--report-dir を指定しただけでは出力しない。--no-deploy-exception-analysis とは排他。Excel と同じパスは不可</t>
+          <t xml:space="preserve">ディレクトリとシンボリックリンクのツリーを Excel ブック (.xlsx) へ追加出力する。リンク先は右端の列へ並べる。対象は frontend と backend の両方のコンテナ (--report-dir または --directory-tree-excel-file と併用)</t>
         </is>
       </c>
     </row>
@@ -7154,17 +7106,17 @@
       </c>
       <c r="B144" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--deploy-exception-limit N</t>
+          <t xml:space="preserve">--no-directory-tree-excel</t>
         </is>
       </c>
       <c r="C144" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 以上の整数</t>
+          <t xml:space="preserve">フラグ</t>
         </is>
       </c>
       <c r="D144" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">50</t>
+          <t xml:space="preserve">true (既定)</t>
         </is>
       </c>
       <c r="E144" s="7" t="inlineStr">
@@ -7174,7 +7126,7 @@
       </c>
       <c r="F144" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">詳細分析を行う例外の最大件数</t>
+          <t xml:space="preserve">上記の Excel 出力を行わない</t>
         </is>
       </c>
     </row>
@@ -7186,17 +7138,17 @@
       </c>
       <c r="B145" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-deploy-exception-analysis</t>
+          <t xml:space="preserve">--directory-tree-excel-file FILE</t>
         </is>
       </c>
       <c r="C145" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
+          <t xml:space="preserve">.xlsx のパス</t>
         </is>
       </c>
       <c r="D145" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">(なし)</t>
         </is>
       </c>
       <c r="E145" s="7" t="inlineStr">
@@ -7206,7 +7158,7 @@
       </c>
       <c r="F145" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Java 例外の解析とファイル出力を行わない</t>
+          <t xml:space="preserve">上記 Excel の出力先を明示指定する。指定すると Excel 出力を有効にする (--report-dir が無くても出力できる)</t>
         </is>
       </c>
     </row>
@@ -7218,17 +7170,17 @@
       </c>
       <c r="B146" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--readonly-analysis-display</t>
+          <t xml:space="preserve">--directory-tree-depth N\|all</t>
         </is>
       </c>
       <c r="C146" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
+          <t xml:space="preserve">1 以上の整数または all</t>
         </is>
       </c>
       <c r="D146" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">false (非表示)</t>
+          <t xml:space="preserve">all</t>
         </is>
       </c>
       <c r="E146" s="7" t="inlineStr">
@@ -7238,7 +7190,7 @@
       </c>
       <c r="F146" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">読み取り専用ファイルシステム分析の結果を画面へ表示する。既定では表示しない (結果は Excel / テキストに残る)。--no-readonly-analysis とは排他</t>
+          <t xml:space="preserve">コンテナ内ツリーの最大深さ (/ 直下を 1 とする)。指定すると画面表示を自動で有効化</t>
         </is>
       </c>
     </row>
@@ -7250,17 +7202,17 @@
       </c>
       <c r="B147" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-readonly-analysis-display</t>
+          <t xml:space="preserve">--directory-file-limit N\|all</t>
         </is>
       </c>
       <c r="C147" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
-        </is>
-      </c>
-      <c r="D147" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">—</t>
+          <t xml:space="preserve">1 以上の整数または all</t>
+        </is>
+      </c>
+      <c r="D147" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(ファイル非表示)</t>
         </is>
       </c>
       <c r="E147" s="7" t="inlineStr">
@@ -7270,11 +7222,11 @@
       </c>
       <c r="F147" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">画面表示を行わない (既定と同じ。--readonly-analysis-display を打ち消す)</t>
-        </is>
-      </c>
-    </row>
-    <row r="148" ht="49.5" customHeight="1">
+          <t xml:space="preserve">通常ファイルの表示を有効化。N 件超過時は拡張子別件数を表示。指定すると画面表示を自動で有効化</t>
+        </is>
+      </c>
+    </row>
+    <row r="148" ht="33.0" customHeight="1">
       <c r="A148" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">4.7 情報表示・レポート</t>
@@ -7282,59 +7234,59 @@
       </c>
       <c r="B148" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--readonly-analysis-report</t>
+          <t xml:space="preserve">--deployment-dir-env NAME</t>
         </is>
       </c>
       <c r="C148" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
-        </is>
-      </c>
-      <c r="D148" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false (非出力)</t>
+          <t xml:space="preserve">環境変数名</t>
+        </is>
+      </c>
+      <c r="D148" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(なし)</t>
         </is>
       </c>
       <c r="E148" s="7" t="inlineStr">
         <is>
+          <t xml:space="preserve">可</t>
+        </is>
+      </c>
+      <c r="F148" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ディレクトリパスを値に持つ環境変数。その配下を階層表示。指定すると画面表示を自動で有効化</t>
+        </is>
+      </c>
+    </row>
+    <row r="149" ht="115.5" customHeight="1">
+      <c r="A149" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
+        </is>
+      </c>
+      <c r="B149" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--report-dir DIR</t>
+        </is>
+      </c>
+      <c r="C149" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ディレクトリパス</t>
+        </is>
+      </c>
+      <c r="D149" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(なし)</t>
+        </is>
+      </c>
+      <c r="E149" s="7" t="inlineStr">
+        <is>
           <t xml:space="preserve">不可</t>
         </is>
       </c>
-      <c r="F148" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--report-dir の全量レポート [11] へ分析結果を出力する。既定では出力せず、見出しの下に未出力である旨と Excel / テキストの出力先だけを残す。--no-readonly-analysis とは排他</t>
-        </is>
-      </c>
-    </row>
-    <row r="149" ht="33.0" customHeight="1">
-      <c r="A149" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
-        </is>
-      </c>
-      <c r="B149" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--no-readonly-analysis-report</t>
-        </is>
-      </c>
-      <c r="C149" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">フラグ</t>
-        </is>
-      </c>
-      <c r="D149" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">—</t>
-        </is>
-      </c>
-      <c r="E149" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">不可</t>
-        </is>
-      </c>
       <c r="F149" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">全量レポートへ分析結果を出力しない (既定と同じ。--readonly-analysis-report を打ち消す)</t>
+          <t xml:space="preserve">全量レポートを DIR/build_and_verify_&lt;日時&gt;.txt へ保存。サービス別ビルドログ (..._build_log_&lt;サービス名&gt;.txt) と読み取り専用ファイルシステム分析の Excel / テキストも同じディレクトリへ追加出力。Java 例外解析の Excel / テキストは --deploy-exception-excel / --deploy-exception-text 指定時のみ。ディレクトリ構成のツリー Excel は --directory-tree-excel 指定時のみ。ツリーとデプロイ構造は --directory-tree-report、[10] は --deploy-exception-report、[11] は --readonly-analysis-report 併用時のみ保存</t>
         </is>
       </c>
     </row>
@@ -7346,17 +7298,17 @@
       </c>
       <c r="B150" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--readonly-analysis-excel FILE</t>
+          <t xml:space="preserve">--deploy-exception-display</t>
         </is>
       </c>
       <c r="C150" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">.xlsx のパス</t>
-        </is>
-      </c>
-      <c r="D150" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(なし)</t>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D150" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false (非表示)</t>
         </is>
       </c>
       <c r="E150" s="7" t="inlineStr">
@@ -7366,11 +7318,11 @@
       </c>
       <c r="F150" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">読み取り専用ファイルシステム分析の Excel 出力先。--no-readonly-analysis とは排他</t>
-        </is>
-      </c>
-    </row>
-    <row r="151" ht="33.0" customHeight="1">
+          <t xml:space="preserve">WAR デプロイ時 Java 例外解析の結果を画面へ表示する。既定では表示しない。--no-deploy-exception-analysis とは排他</t>
+        </is>
+      </c>
+    </row>
+    <row r="151" ht="19.5" customHeight="1">
       <c r="A151" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">4.7 情報表示・レポート</t>
@@ -7378,17 +7330,17 @@
       </c>
       <c r="B151" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--readonly-analysis-text FILE</t>
+          <t xml:space="preserve">--no-deploy-exception-display</t>
         </is>
       </c>
       <c r="C151" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ファイルパス</t>
+          <t xml:space="preserve">フラグ</t>
         </is>
       </c>
       <c r="D151" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">(なし)</t>
+          <t xml:space="preserve">—</t>
         </is>
       </c>
       <c r="E151" s="7" t="inlineStr">
@@ -7398,11 +7350,11 @@
       </c>
       <c r="F151" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">同じ内容のテキスト出力先。--no-readonly-analysis とは排他。Excel と同じパスは不可</t>
-        </is>
-      </c>
-    </row>
-    <row r="152" ht="19.5" customHeight="1">
+          <t xml:space="preserve">画面表示を行わない (既定と同じ。--deploy-exception-display を打ち消す)</t>
+        </is>
+      </c>
+    </row>
+    <row r="152" ht="49.5" customHeight="1">
       <c r="A152" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">4.7 情報表示・レポート</t>
@@ -7410,7 +7362,7 @@
       </c>
       <c r="B152" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-readonly-analysis</t>
+          <t xml:space="preserve">--deploy-exception-report</t>
         </is>
       </c>
       <c r="C152" s="3" t="inlineStr">
@@ -7418,9 +7370,9 @@
           <t xml:space="preserve">フラグ</t>
         </is>
       </c>
-      <c r="D152" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
+      <c r="D152" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false (非出力)</t>
         </is>
       </c>
       <c r="E152" s="7" t="inlineStr">
@@ -7430,11 +7382,11 @@
       </c>
       <c r="F152" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">読み取り専用ファイルシステムの書き込み先分析とファイル出力を行わない</t>
-        </is>
-      </c>
-    </row>
-    <row r="153" ht="49.5" customHeight="1">
+          <t xml:space="preserve">--report-dir の全量レポート [10] へ解析結果を出力する。既定では出力せず、見出しの下に未出力である旨だけを残す。--no-deploy-exception-analysis とは排他</t>
+        </is>
+      </c>
+    </row>
+    <row r="153" ht="33.0" customHeight="1">
       <c r="A153" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">4.7 情報表示・レポート</t>
@@ -7442,27 +7394,27 @@
       </c>
       <c r="B153" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--undertow-host-header NAME</t>
+          <t xml:space="preserve">--no-deploy-exception-report</t>
         </is>
       </c>
       <c r="C153" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ホスト名 (カンマ区切りも可)</t>
+          <t xml:space="preserve">フラグ</t>
         </is>
       </c>
       <c r="D153" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">(なし)</t>
+          <t xml:space="preserve">—</t>
         </is>
       </c>
       <c r="E153" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">可</t>
+          <t xml:space="preserve">不可</t>
         </is>
       </c>
       <c r="F153" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Undertow バーチャルホスト分析で振り分けを判定する Host ヘッダー名を追加する。ポート付きでも可 (Undertow と同じ規則で落とす)。--no-undertow-analysis とは排他</t>
+          <t xml:space="preserve">全量レポートへ解析結果を出力しない (既定と同じ。--deploy-exception-report を打ち消す)</t>
         </is>
       </c>
     </row>
@@ -7474,17 +7426,17 @@
       </c>
       <c r="B154" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--undertow-probe-path PATH</t>
+          <t xml:space="preserve">--deploy-exception-excel FILE</t>
         </is>
       </c>
       <c r="C154" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">/ で始まるパス</t>
-        </is>
-      </c>
-      <c r="D154" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(WFLYUT0021 から検出)</t>
+          <t xml:space="preserve">.xlsx のパス</t>
+        </is>
+      </c>
+      <c r="D154" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(なし)</t>
         </is>
       </c>
       <c r="E154" s="7" t="inlineStr">
@@ -7494,11 +7446,11 @@
       </c>
       <c r="F154" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Host ヘッダーを差し替えた実リクエストの送信先パス。--no-undertow-analysis とは排他</t>
-        </is>
-      </c>
-    </row>
-    <row r="155" ht="19.5" customHeight="1">
+          <t xml:space="preserve">WAR デプロイ時 Java 例外解析の Excel 出力先。指定したときだけ出力する (--report-dir だけでは出力しない)。--no-deploy-exception-analysis とは排他</t>
+        </is>
+      </c>
+    </row>
+    <row r="155" ht="33.0" customHeight="1">
       <c r="A155" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">4.7 情報表示・レポート</t>
@@ -7506,17 +7458,17 @@
       </c>
       <c r="B155" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-undertow-probe</t>
+          <t xml:space="preserve">--deploy-exception-text FILE</t>
         </is>
       </c>
       <c r="C155" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
+          <t xml:space="preserve">ファイルパス</t>
         </is>
       </c>
       <c r="D155" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">(なし。指定時のみ出力)</t>
         </is>
       </c>
       <c r="E155" s="7" t="inlineStr">
@@ -7526,11 +7478,11 @@
       </c>
       <c r="F155" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">実リクエストを送らず、standalone.xml の解析だけで判定する</t>
-        </is>
-      </c>
-    </row>
-    <row r="156" ht="33.0" customHeight="1">
+          <t xml:space="preserve">同じ内容のテキスト出力先。--report-dir を指定しただけでは出力しない。--no-deploy-exception-analysis とは排他。Excel と同じパスは不可</t>
+        </is>
+      </c>
+    </row>
+    <row r="156" ht="19.5" customHeight="1">
       <c r="A156" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">4.7 情報表示・レポート</t>
@@ -7538,17 +7490,17 @@
       </c>
       <c r="B156" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--undertow-analysis-text FILE</t>
+          <t xml:space="preserve">--deploy-exception-limit N</t>
         </is>
       </c>
       <c r="C156" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ファイルパス</t>
-        </is>
-      </c>
-      <c r="D156" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(なし)</t>
+          <t xml:space="preserve">1 以上の整数</t>
+        </is>
+      </c>
+      <c r="D156" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">50</t>
         </is>
       </c>
       <c r="E156" s="7" t="inlineStr">
@@ -7558,7 +7510,7 @@
       </c>
       <c r="F156" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Undertow バーチャルホスト分析のテキスト出力先 (内容は画面表示と同一)。--no-undertow-analysis / --no-undertow-analysis-text とは排他</t>
+          <t xml:space="preserve">詳細分析を行う例外の最大件数</t>
         </is>
       </c>
     </row>
@@ -7570,7 +7522,7 @@
       </c>
       <c r="B157" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--undertow-analysis-display</t>
+          <t xml:space="preserve">--no-deploy-exception-analysis</t>
         </is>
       </c>
       <c r="C157" s="3" t="inlineStr">
@@ -7590,7 +7542,7 @@
       </c>
       <c r="F157" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">分析結果をダイアログの操作後に画面へも出力する (既定では画面へ出さない)。--no-undertow-analysis とは排他</t>
+          <t xml:space="preserve">Java 例外の解析とファイル出力を行わない</t>
         </is>
       </c>
     </row>
@@ -7602,7 +7554,7 @@
       </c>
       <c r="B158" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-undertow-analysis-display</t>
+          <t xml:space="preserve">--readonly-analysis-display</t>
         </is>
       </c>
       <c r="C158" s="3" t="inlineStr">
@@ -7612,7 +7564,7 @@
       </c>
       <c r="D158" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">true (既定)</t>
+          <t xml:space="preserve">false (非表示)</t>
         </is>
       </c>
       <c r="E158" s="7" t="inlineStr">
@@ -7622,7 +7574,7 @@
       </c>
       <c r="F158" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">画面出力を抑制する (既定と同じ。--undertow-analysis-display を打ち消す)。--no-undertow-analysis-text との同時指定は出力先が無くなるため不可</t>
+          <t xml:space="preserve">読み取り専用ファイルシステム分析の結果を画面へ表示する。既定では表示しない (結果は Excel / テキストに残る)。--no-readonly-analysis とは排他</t>
         </is>
       </c>
     </row>
@@ -7634,7 +7586,7 @@
       </c>
       <c r="B159" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-undertow-analysis-text</t>
+          <t xml:space="preserve">--no-readonly-analysis-display</t>
         </is>
       </c>
       <c r="C159" s="3" t="inlineStr">
@@ -7644,7 +7596,7 @@
       </c>
       <c r="D159" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">—</t>
         </is>
       </c>
       <c r="E159" s="7" t="inlineStr">
@@ -7654,11 +7606,11 @@
       </c>
       <c r="F159" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">テキスト出力だけを抑制する。--no-undertow-analysis-display との同時指定は不可</t>
-        </is>
-      </c>
-    </row>
-    <row r="160" ht="19.5" customHeight="1">
+          <t xml:space="preserve">画面表示を行わない (既定と同じ。--readonly-analysis-display を打ち消す)</t>
+        </is>
+      </c>
+    </row>
+    <row r="160" ht="49.5" customHeight="1">
       <c r="A160" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">4.7 情報表示・レポート</t>
@@ -7666,7 +7618,7 @@
       </c>
       <c r="B160" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-undertow-analysis</t>
+          <t xml:space="preserve">--readonly-analysis-report</t>
         </is>
       </c>
       <c r="C160" s="3" t="inlineStr">
@@ -7674,9 +7626,9 @@
           <t xml:space="preserve">フラグ</t>
         </is>
       </c>
-      <c r="D160" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
+      <c r="D160" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false (非出力)</t>
         </is>
       </c>
       <c r="E160" s="7" t="inlineStr">
@@ -7686,7 +7638,7 @@
       </c>
       <c r="F160" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Undertow バーチャルホスト (default-host) の分析と出力を一切行わない</t>
+          <t xml:space="preserve">--report-dir の全量レポート [11] へ分析結果を出力する。既定では出力せず、見出しの下に未出力である旨と Excel / テキストの出力先だけを残す。--no-readonly-analysis とは排他</t>
         </is>
       </c>
     </row>
@@ -7698,59 +7650,59 @@
       </c>
       <c r="B161" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--cert-check-text FILE</t>
+          <t xml:space="preserve">--no-readonly-analysis-report</t>
         </is>
       </c>
       <c r="C161" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ファイルパス</t>
+          <t xml:space="preserve">フラグ</t>
         </is>
       </c>
       <c r="D161" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="E161" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
+      <c r="F161" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">全量レポートへ分析結果を出力しない (既定と同じ。--readonly-analysis-report を打ち消す)</t>
+        </is>
+      </c>
+    </row>
+    <row r="162" ht="33.0" customHeight="1">
+      <c r="A162" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
+        </is>
+      </c>
+      <c r="B162" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--readonly-analysis-excel FILE</t>
+        </is>
+      </c>
+      <c r="C162" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">.xlsx のパス</t>
+        </is>
+      </c>
+      <c r="D162" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">(なし)</t>
         </is>
       </c>
-      <c r="E161" s="7" t="inlineStr">
+      <c r="E162" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">不可</t>
         </is>
       </c>
-      <c r="F161" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">証明書チェック (--keep-container-mode logs の操作) の結果テキストの出力先。--no-cert-check-text とは排他</t>
-        </is>
-      </c>
-    </row>
-    <row r="162" ht="19.5" customHeight="1">
-      <c r="A162" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.7 情報表示・レポート</t>
-        </is>
-      </c>
-      <c r="B162" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--no-cert-check-text</t>
-        </is>
-      </c>
-      <c r="C162" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">フラグ</t>
-        </is>
-      </c>
-      <c r="D162" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
-        </is>
-      </c>
-      <c r="E162" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">不可</t>
-        </is>
-      </c>
       <c r="F162" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">証明書チェック結果のテキスト出力を行わない (画面表示だけにする)</t>
+          <t xml:space="preserve">読み取り専用ファイルシステム分析の Excel 出力先。--no-readonly-analysis とは排他</t>
         </is>
       </c>
     </row>
@@ -7762,7 +7714,7 @@
       </c>
       <c r="B163" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--jboss-module-list-text FILE</t>
+          <t xml:space="preserve">--readonly-analysis-text FILE</t>
         </is>
       </c>
       <c r="C163" s="3" t="inlineStr">
@@ -7782,7 +7734,7 @@
       </c>
       <c r="F163" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">JBoss モジュール一覧 (--keep-container-mode logs の操作) の結果テキストの出力先。--no-jboss-module-list-text とは排他</t>
+          <t xml:space="preserve">同じ内容のテキスト出力先。--no-readonly-analysis とは排他。Excel と同じパスは不可</t>
         </is>
       </c>
     </row>
@@ -7794,7 +7746,7 @@
       </c>
       <c r="B164" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-jboss-module-list-text</t>
+          <t xml:space="preserve">--no-readonly-analysis</t>
         </is>
       </c>
       <c r="C164" s="3" t="inlineStr">
@@ -7814,11 +7766,11 @@
       </c>
       <c r="F164" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">JBoss モジュール一覧のテキスト出力を行わない (画面表示だけにする)</t>
-        </is>
-      </c>
-    </row>
-    <row r="165" ht="33.0" customHeight="1">
+          <t xml:space="preserve">読み取り専用ファイルシステムの書き込み先分析とファイル出力を行わない</t>
+        </is>
+      </c>
+    </row>
+    <row r="165" ht="49.5" customHeight="1">
       <c r="A165" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">4.7 情報表示・レポート</t>
@@ -7826,12 +7778,12 @@
       </c>
       <c r="B165" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--truststore-inventory-text FILE</t>
+          <t xml:space="preserve">--undertow-host-header NAME</t>
         </is>
       </c>
       <c r="C165" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ファイルパス</t>
+          <t xml:space="preserve">ホスト名 (カンマ区切りも可)</t>
         </is>
       </c>
       <c r="D165" s="3" t="inlineStr">
@@ -7841,12 +7793,12 @@
       </c>
       <c r="E165" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">不可</t>
+          <t xml:space="preserve">可</t>
         </is>
       </c>
       <c r="F165" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">トラストストア一覧 (--keep-container-mode logs の操作) の結果テキストの出力先。--no-truststore-inventory-text とは排他</t>
+          <t xml:space="preserve">Undertow バーチャルホスト分析で振り分けを判定する Host ヘッダー名を追加する。ポート付きでも可 (Undertow と同じ規則で落とす)。--no-undertow-analysis とは排他</t>
         </is>
       </c>
     </row>
@@ -7858,95 +7810,103 @@
       </c>
       <c r="B166" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-truststore-inventory-text</t>
+          <t xml:space="preserve">--undertow-probe-path PATH</t>
         </is>
       </c>
       <c r="C166" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">/ で始まるパス</t>
+        </is>
+      </c>
+      <c r="D166" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(WFLYUT0021 から検出)</t>
+        </is>
+      </c>
+      <c r="E166" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
+      <c r="F166" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Host ヘッダーを差し替えた実リクエストの送信先パス。--no-undertow-analysis とは排他</t>
+        </is>
+      </c>
+    </row>
+    <row r="167" ht="19.5" customHeight="1">
+      <c r="A167" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
+        </is>
+      </c>
+      <c r="B167" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--no-undertow-probe</t>
+        </is>
+      </c>
+      <c r="C167" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">フラグ</t>
         </is>
       </c>
-      <c r="D166" s="3" t="inlineStr">
+      <c r="D167" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">false</t>
         </is>
       </c>
-      <c r="E166" s="7" t="inlineStr">
+      <c r="E167" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">不可</t>
         </is>
       </c>
-      <c r="F166" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">トラストストア一覧のテキスト出力を行わない (画面表示だけにする)</t>
-        </is>
-      </c>
-    </row>
-    <row r="167" ht="33.0" customHeight="1">
-      <c r="A167" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.8 終了時のクリーンアップ</t>
-        </is>
-      </c>
-      <c r="B167" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--cleanup-all-docker-data</t>
-        </is>
-      </c>
-      <c r="C167" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">フラグ</t>
-        </is>
-      </c>
-      <c r="D167" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
-        </is>
-      </c>
-      <c r="E167" s="7"/>
       <c r="F167" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">終了時に確認フレーズ入力のうえ、Docker context の全データを削除。--keep-container とは排他</t>
+          <t xml:space="preserve">実リクエストを送らず、standalone.xml の解析だけで判定する</t>
         </is>
       </c>
     </row>
     <row r="168" ht="33.0" customHeight="1">
       <c r="A168" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
         </is>
       </c>
       <c r="B168" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">(オプション不要)</t>
+          <t xml:space="preserve">--undertow-analysis-text FILE</t>
         </is>
       </c>
       <c r="C168" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">—</t>
-        </is>
-      </c>
-      <c r="D168" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">有効</t>
-        </is>
-      </c>
-      <c r="E168" s="7"/>
+          <t xml:space="preserve">ファイルパス</t>
+        </is>
+      </c>
+      <c r="D168" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(なし)</t>
+        </is>
+      </c>
+      <c r="E168" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
       <c r="F168" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">旧世代イメージの回収。ビルド前後で image ID を突き合わせ、世代交代した旧 ID がどのタグからも参照されていない場合だけ削除する</t>
+          <t xml:space="preserve">Undertow バーチャルホスト分析のテキスト出力先 (内容は画面表示と同一)。--no-undertow-analysis / --no-undertow-analysis-text とは排他</t>
         </is>
       </c>
     </row>
     <row r="169" ht="33.0" customHeight="1">
       <c r="A169" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
         </is>
       </c>
       <c r="B169" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-reclaim-old-image</t>
+          <t xml:space="preserve">--undertow-analysis-display</t>
         </is>
       </c>
       <c r="C169" s="3" t="inlineStr">
@@ -7959,22 +7919,26 @@
           <t xml:space="preserve">false</t>
         </is>
       </c>
-      <c r="E169" s="7"/>
+      <c r="E169" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
       <c r="F169" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">旧世代イメージの回収を行わない (従来どおり残す)</t>
+          <t xml:space="preserve">分析結果をダイアログの操作後に画面へも出力する (既定では画面へ出さない)。--no-undertow-analysis とは排他</t>
         </is>
       </c>
     </row>
     <row r="170" ht="33.0" customHeight="1">
       <c r="A170" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
         </is>
       </c>
       <c r="B170" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--prune-build-cache</t>
+          <t xml:space="preserve">--no-undertow-analysis-display</t>
         </is>
       </c>
       <c r="C170" s="3" t="inlineStr">
@@ -7982,471 +7946,623 @@
           <t xml:space="preserve">フラグ</t>
         </is>
       </c>
-      <c r="D170" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
-        </is>
-      </c>
-      <c r="E170" s="7"/>
+      <c r="D170" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">true (既定)</t>
+        </is>
+      </c>
+      <c r="E170" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
       <c r="F170" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">終了時に docker builder prune --all --force を実行</t>
+          <t xml:space="preserve">画面出力を抑制する (既定と同じ。--undertow-analysis-display を打ち消す)。--no-undertow-analysis-text との同時指定は出力先が無くなるため不可</t>
         </is>
       </c>
     </row>
     <row r="171" ht="33.0" customHeight="1">
       <c r="A171" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
         </is>
       </c>
       <c r="B171" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--prune-build-cache-keep SIZE</t>
+          <t xml:space="preserve">--no-undertow-analysis-text</t>
         </is>
       </c>
       <c r="C171" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">サイズ (10GB / 512MB)</t>
+          <t xml:space="preserve">フラグ</t>
         </is>
       </c>
       <c r="D171" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="E171" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
+      <c r="F171" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">テキスト出力だけを抑制する。--no-undertow-analysis-display との同時指定は不可</t>
+        </is>
+      </c>
+    </row>
+    <row r="172" ht="19.5" customHeight="1">
+      <c r="A172" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
+        </is>
+      </c>
+      <c r="B172" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--no-undertow-analysis</t>
+        </is>
+      </c>
+      <c r="C172" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D172" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="E172" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
+      <c r="F172" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Undertow バーチャルホスト (default-host) の分析と出力を一切行わない</t>
+        </is>
+      </c>
+    </row>
+    <row r="173" ht="33.0" customHeight="1">
+      <c r="A173" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
+        </is>
+      </c>
+      <c r="B173" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--cert-check-text FILE</t>
+        </is>
+      </c>
+      <c r="C173" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ファイルパス</t>
+        </is>
+      </c>
+      <c r="D173" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">(なし)</t>
         </is>
       </c>
-      <c r="E171" s="7"/>
-      <c r="F171" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">終了時に docker builder prune --force --keep-storage SIZE を実行。指定すると --prune-build-cache も暗黙に有効化</t>
-        </is>
-      </c>
-    </row>
-    <row r="172" ht="33.0" customHeight="1">
-      <c r="A172" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
-        </is>
-      </c>
-      <c r="B172" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--disk-usage-report</t>
-        </is>
-      </c>
-      <c r="C172" s="3" t="inlineStr">
+      <c r="E173" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
+      <c r="F173" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">証明書チェック (--keep-container-mode logs の操作) の結果テキストの出力先。--no-cert-check-text とは排他</t>
+        </is>
+      </c>
+    </row>
+    <row r="174" ht="19.5" customHeight="1">
+      <c r="A174" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
+        </is>
+      </c>
+      <c r="B174" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--no-cert-check-text</t>
+        </is>
+      </c>
+      <c r="C174" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">フラグ</t>
         </is>
       </c>
-      <c r="D172" s="3" t="inlineStr">
+      <c r="D174" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">false</t>
         </is>
       </c>
-      <c r="E172" s="7"/>
-      <c r="F172" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ビルド前と終了時に Docker 管理対象の使用量を測定し、実行前からの増減を表示 (削除は行わない)</t>
-        </is>
-      </c>
-    </row>
-    <row r="173" ht="66.0" customHeight="1">
-      <c r="A173" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.8-3 ホスト側システムログ (/var/log/messages) への出力抑制</t>
-        </is>
-      </c>
-      <c r="B173" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--suppress-syslog</t>
-        </is>
-      </c>
-      <c r="C173" s="3" t="inlineStr">
+      <c r="E174" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
+      <c r="F174" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">証明書チェック結果のテキスト出力を行わない (画面表示だけにする)</t>
+        </is>
+      </c>
+    </row>
+    <row r="175" ht="33.0" customHeight="1">
+      <c r="A175" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
+        </is>
+      </c>
+      <c r="B175" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--jboss-module-list-text FILE</t>
+        </is>
+      </c>
+      <c r="C175" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ファイルパス</t>
+        </is>
+      </c>
+      <c r="D175" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(なし)</t>
+        </is>
+      </c>
+      <c r="E175" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
+      <c r="F175" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">JBoss モジュール一覧 (--keep-container-mode logs の操作) の結果テキストの出力先。--no-jboss-module-list-text とは排他</t>
+        </is>
+      </c>
+    </row>
+    <row r="176" ht="19.5" customHeight="1">
+      <c r="A176" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
+        </is>
+      </c>
+      <c r="B176" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--no-jboss-module-list-text</t>
+        </is>
+      </c>
+      <c r="C176" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">フラグ</t>
         </is>
       </c>
-      <c r="D173" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">有効</t>
-        </is>
-      </c>
-      <c r="E173" s="7"/>
-      <c r="F173" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">/var/log/messages への docker 関連ログを抑制する。(1) journald / syslog になるサービスのログドライバを差し替える (元の compose ファイルは変更しない) (2) 存在確認の docker inspect を、エラーにならない一覧 API へ置き換える</t>
-        </is>
-      </c>
-    </row>
-    <row r="174" ht="49.5" customHeight="1">
-      <c r="A174" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.8-3 ホスト側システムログ (/var/log/messages) への出力抑制</t>
-        </is>
-      </c>
-      <c r="B174" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--no-suppress-syslog</t>
-        </is>
-      </c>
-      <c r="C174" s="3" t="inlineStr">
+      <c r="D176" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="E176" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
+      <c r="F176" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">JBoss モジュール一覧のテキスト出力を行わない (画面表示だけにする)</t>
+        </is>
+      </c>
+    </row>
+    <row r="177" ht="33.0" customHeight="1">
+      <c r="A177" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
+        </is>
+      </c>
+      <c r="B177" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--truststore-inventory-text FILE</t>
+        </is>
+      </c>
+      <c r="C177" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ファイルパス</t>
+        </is>
+      </c>
+      <c r="D177" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(なし)</t>
+        </is>
+      </c>
+      <c r="E177" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
+      <c r="F177" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">トラストストア一覧 (--keep-container-mode logs の操作) の結果テキストの出力先。--no-truststore-inventory-text とは排他</t>
+        </is>
+      </c>
+    </row>
+    <row r="178" ht="33.0" customHeight="1">
+      <c r="A178" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
+        </is>
+      </c>
+      <c r="B178" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--no-truststore-inventory-text</t>
+        </is>
+      </c>
+      <c r="C178" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">フラグ</t>
         </is>
       </c>
-      <c r="D174" s="3" t="inlineStr">
+      <c r="D178" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">false</t>
         </is>
       </c>
-      <c r="E174" s="7"/>
-      <c r="F174" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">上記の抑制を行わず、従来どおりの動作にする</t>
-        </is>
-      </c>
-    </row>
-    <row r="175" ht="49.5" customHeight="1">
-      <c r="A175" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.8-3 ホスト側システムログ (/var/log/messages) への出力抑制</t>
-        </is>
-      </c>
-      <c r="B175" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--syslog-log-driver DRIVER</t>
-        </is>
-      </c>
-      <c r="C175" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">json-file / local</t>
-        </is>
-      </c>
-      <c r="D175" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">json-file</t>
-        </is>
-      </c>
-      <c r="E175" s="7"/>
-      <c r="F175" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">コンテナログの差し替え先ドライバ。journald / syslog は抑制にならず、none は起動確認のログが読めなくなるため受け付けない</t>
-        </is>
-      </c>
-    </row>
-    <row r="176" ht="49.5" customHeight="1">
-      <c r="A176" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.8-3 ホスト側システムログ (/var/log/messages) への出力抑制</t>
-        </is>
-      </c>
-      <c r="B176" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--syslog-audit</t>
-        </is>
-      </c>
-      <c r="C176" s="3" t="inlineStr">
+      <c r="E178" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
+      <c r="F178" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">トラストストア一覧のテキスト出力を行わない (画面表示だけにする)</t>
+        </is>
+      </c>
+    </row>
+    <row r="179" ht="33.0" customHeight="1">
+      <c r="A179" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.8 終了時のクリーンアップ</t>
+        </is>
+      </c>
+      <c r="B179" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--cleanup-all-docker-data</t>
+        </is>
+      </c>
+      <c r="C179" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">フラグ</t>
         </is>
       </c>
-      <c r="D176" s="3" t="inlineStr">
+      <c r="D179" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">false</t>
         </is>
       </c>
-      <c r="E176" s="7"/>
-      <c r="F176" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">実行前後で /var/log/messages の行数を数え、増えた分を出力元別に集計して表示する (読み取りに root 権限が必要)</t>
-        </is>
-      </c>
-    </row>
-    <row r="177" ht="49.5" customHeight="1">
-      <c r="A177" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.8-3 ホスト側システムログ (/var/log/messages) への出力抑制</t>
-        </is>
-      </c>
-      <c r="B177" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--no-syslog-audit</t>
-        </is>
-      </c>
-      <c r="C177" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">フラグ</t>
-        </is>
-      </c>
-      <c r="D177" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">有効</t>
-        </is>
-      </c>
-      <c r="E177" s="7"/>
-      <c r="F177" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">増加量の計測を行わない</t>
-        </is>
-      </c>
-    </row>
-    <row r="178" ht="49.5" customHeight="1">
-      <c r="A178" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.8-3 ホスト側システムログ (/var/log/messages) への出力抑制</t>
-        </is>
-      </c>
-      <c r="B178" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--syslog-audit-file FILE</t>
-        </is>
-      </c>
-      <c r="C178" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ファイルパス</t>
-        </is>
-      </c>
-      <c r="D178" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">/var/log/messages</t>
-        </is>
-      </c>
-      <c r="E178" s="7"/>
-      <c r="F178" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">計測対象のログファイル。指定すると --syslog-audit も有効になる</t>
-        </is>
-      </c>
-    </row>
-    <row r="179" ht="19.5" customHeight="1">
-      <c r="A179" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.9 その他</t>
-        </is>
-      </c>
-      <c r="B179" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-h, --help</t>
-        </is>
-      </c>
-      <c r="C179" s="3"/>
-      <c r="D179" s="3"/>
       <c r="E179" s="7"/>
       <c r="F179" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ヘルプを表示して exit 0</t>
+          <t xml:space="preserve">終了時に確認フレーズ入力のうえ、Docker context の全データを削除。--keep-container とは排他</t>
         </is>
       </c>
     </row>
     <row r="180" ht="33.0" customHeight="1">
       <c r="A180" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.4-3 対話 bash セッションの tree</t>
+          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
         </is>
       </c>
       <c r="B180" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">-a</t>
-        </is>
-      </c>
-      <c r="C180" s="3"/>
-      <c r="D180" s="3"/>
+          <t xml:space="preserve">(オプション不要)</t>
+        </is>
+      </c>
+      <c r="C180" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="D180" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">有効</t>
+        </is>
+      </c>
       <c r="E180" s="7"/>
-      <c r="F180" s="3"/>
+      <c r="F180" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">旧世代イメージの回収。ビルド前後で image ID を突き合わせ、世代交代した旧 ID がどのタグからも参照されていない場合だけ削除する</t>
+        </is>
+      </c>
     </row>
     <row r="181" ht="33.0" customHeight="1">
       <c r="A181" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.4-3 対話 bash セッションの tree</t>
+          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
         </is>
       </c>
       <c r="B181" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">-d</t>
-        </is>
-      </c>
-      <c r="C181" s="3"/>
-      <c r="D181" s="3"/>
+          <t xml:space="preserve">--no-reclaim-old-image</t>
+        </is>
+      </c>
+      <c r="C181" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D181" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
       <c r="E181" s="7"/>
-      <c r="F181" s="3"/>
+      <c r="F181" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">旧世代イメージの回収を行わない (従来どおり残す)</t>
+        </is>
+      </c>
     </row>
     <row r="182" ht="33.0" customHeight="1">
       <c r="A182" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.4-3 対話 bash セッションの tree</t>
+          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
         </is>
       </c>
       <c r="B182" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">-f</t>
-        </is>
-      </c>
-      <c r="C182" s="3"/>
-      <c r="D182" s="3"/>
+          <t xml:space="preserve">--prune-build-cache</t>
+        </is>
+      </c>
+      <c r="C182" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D182" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
       <c r="E182" s="7"/>
-      <c r="F182" s="3"/>
+      <c r="F182" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">終了時に docker builder prune --all --force を実行</t>
+        </is>
+      </c>
     </row>
     <row r="183" ht="33.0" customHeight="1">
       <c r="A183" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.4-3 対話 bash セッションの tree</t>
+          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
         </is>
       </c>
       <c r="B183" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">-L 深さ</t>
-        </is>
-      </c>
-      <c r="C183" s="3"/>
-      <c r="D183" s="3"/>
+          <t xml:space="preserve">--prune-build-cache-keep SIZE</t>
+        </is>
+      </c>
+      <c r="C183" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">サイズ (10GB / 512MB)</t>
+        </is>
+      </c>
+      <c r="D183" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(なし)</t>
+        </is>
+      </c>
       <c r="E183" s="7"/>
-      <c r="F183" s="3"/>
+      <c r="F183" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">終了時に docker builder prune --force --keep-storage SIZE を実行。指定すると --prune-build-cache も暗黙に有効化</t>
+        </is>
+      </c>
     </row>
     <row r="184" ht="33.0" customHeight="1">
       <c r="A184" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.4-3 対話 bash セッションの tree</t>
+          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
         </is>
       </c>
       <c r="B184" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--noreport</t>
-        </is>
-      </c>
-      <c r="C184" s="3"/>
-      <c r="D184" s="3"/>
+          <t xml:space="preserve">--disk-usage-report</t>
+        </is>
+      </c>
+      <c r="C184" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D184" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
       <c r="E184" s="7"/>
-      <c r="F184" s="3"/>
-    </row>
-    <row r="185" ht="33.0" customHeight="1">
+      <c r="F184" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ビルド前と終了時に Docker 管理対象の使用量を測定し、実行前からの増減を表示 (削除は行わない)</t>
+        </is>
+      </c>
+    </row>
+    <row r="185" ht="66.0" customHeight="1">
       <c r="A185" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+          <t xml:space="preserve">4.8-3 ホスト側システムログ (/var/log/messages) への出力抑制</t>
         </is>
       </c>
       <c r="B185" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">(未指定)</t>
-        </is>
-      </c>
-      <c r="C185" s="3"/>
-      <c r="D185" s="3"/>
+          <t xml:space="preserve">--suppress-syslog</t>
+        </is>
+      </c>
+      <c r="C185" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D185" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">有効</t>
+        </is>
+      </c>
       <c r="E185" s="7"/>
       <c r="F185" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">画面表示・レポート出力とも行わない (既定)。画面には有効化方法を 1 行だけ案内する</t>
-        </is>
-      </c>
-    </row>
-    <row r="186" ht="33.0" customHeight="1">
+          <t xml:space="preserve">/var/log/messages への docker 関連ログを抑制する。(1) journald / syslog になるサービスのログドライバを差し替える (元の compose ファイルは変更しない) (2) 存在確認の docker inspect を、エラーにならない一覧 API へ置き換える</t>
+        </is>
+      </c>
+    </row>
+    <row r="186" ht="49.5" customHeight="1">
       <c r="A186" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+          <t xml:space="preserve">4.8-3 ホスト側システムログ (/var/log/messages) への出力抑制</t>
         </is>
       </c>
       <c r="B186" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-tree</t>
-        </is>
-      </c>
-      <c r="C186" s="3"/>
-      <c r="D186" s="3"/>
+          <t xml:space="preserve">--no-suppress-syslog</t>
+        </is>
+      </c>
+      <c r="C186" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D186" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
       <c r="E186" s="7"/>
       <c r="F186" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">画面へツリーと JBoss EAP デプロイ構造を表示する</t>
-        </is>
-      </c>
-    </row>
-    <row r="187" ht="33.0" customHeight="1">
+          <t xml:space="preserve">上記の抑制を行わず、従来どおりの動作にする</t>
+        </is>
+      </c>
+    </row>
+    <row r="187" ht="49.5" customHeight="1">
       <c r="A187" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+          <t xml:space="preserve">4.8-3 ホスト側システムログ (/var/log/messages) への出力抑制</t>
         </is>
       </c>
       <c r="B187" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-directory-tree</t>
-        </is>
-      </c>
-      <c r="C187" s="3"/>
-      <c r="D187" s="3"/>
+          <t xml:space="preserve">--syslog-log-driver DRIVER</t>
+        </is>
+      </c>
+      <c r="C187" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">json-file / local</t>
+        </is>
+      </c>
+      <c r="D187" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">json-file</t>
+        </is>
+      </c>
       <c r="E187" s="7"/>
       <c r="F187" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">画面表示を行わない。下記オプションによる自動有効化も打ち消す</t>
-        </is>
-      </c>
-    </row>
-    <row r="188" ht="33.0" customHeight="1">
+          <t xml:space="preserve">コンテナログの差し替え先ドライバ。journald / syslog は抑制にならず、none は起動確認のログが読めなくなるため受け付けない</t>
+        </is>
+      </c>
+    </row>
+    <row r="188" ht="49.5" customHeight="1">
       <c r="A188" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+          <t xml:space="preserve">4.8-3 ホスト側システムログ (/var/log/messages) への出力抑制</t>
         </is>
       </c>
       <c r="B188" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-tree-report</t>
-        </is>
-      </c>
-      <c r="C188" s="3"/>
-      <c r="D188" s="3"/>
+          <t xml:space="preserve">--syslog-audit</t>
+        </is>
+      </c>
+      <c r="C188" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D188" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
       <c r="E188" s="7"/>
       <c r="F188" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">--report-dir の全量レポート [3] [4] へ出力する (画面表示とは独立)</t>
-        </is>
-      </c>
-    </row>
-    <row r="189" ht="33.0" customHeight="1">
+          <t xml:space="preserve">実行前後で /var/log/messages の行数を数え、増えた分を出力元別に集計して表示する (読み取りに root 権限が必要)</t>
+        </is>
+      </c>
+    </row>
+    <row r="189" ht="49.5" customHeight="1">
       <c r="A189" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+          <t xml:space="preserve">4.8-3 ホスト側システムログ (/var/log/messages) への出力抑制</t>
         </is>
       </c>
       <c r="B189" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-directory-tree-report</t>
-        </is>
-      </c>
-      <c r="C189" s="3"/>
-      <c r="D189" s="3"/>
+          <t xml:space="preserve">--no-syslog-audit</t>
+        </is>
+      </c>
+      <c r="C189" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D189" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">有効</t>
+        </is>
+      </c>
       <c r="E189" s="7"/>
       <c r="F189" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">全量レポートへ出力しない (既定)</t>
-        </is>
-      </c>
-    </row>
-    <row r="190" ht="33.0" customHeight="1">
+          <t xml:space="preserve">増加量の計測を行わない</t>
+        </is>
+      </c>
+    </row>
+    <row r="190" ht="49.5" customHeight="1">
       <c r="A190" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+          <t xml:space="preserve">4.8-3 ホスト側システムログ (/var/log/messages) への出力抑制</t>
         </is>
       </c>
       <c r="B190" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-tree-excel</t>
-        </is>
-      </c>
-      <c r="C190" s="3"/>
-      <c r="D190" s="3"/>
+          <t xml:space="preserve">--syslog-audit-file FILE</t>
+        </is>
+      </c>
+      <c r="C190" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ファイルパス</t>
+        </is>
+      </c>
+      <c r="D190" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">/var/log/messages</t>
+        </is>
+      </c>
       <c r="E190" s="7"/>
       <c r="F190" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ディレクトリとシンボリックリンクのツリーを Excel ブックへ追加出力する (frontend / backend の両方が対象。リンク先は右端の列)</t>
-        </is>
-      </c>
-    </row>
-    <row r="191" ht="33.0" customHeight="1">
+          <t xml:space="preserve">計測対象のログファイル。指定すると --syslog-audit も有効になる</t>
+        </is>
+      </c>
+    </row>
+    <row r="191" ht="19.5" customHeight="1">
       <c r="A191" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+          <t xml:space="preserve">4.9 その他</t>
         </is>
       </c>
       <c r="B191" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-directory-tree-excel</t>
+          <t xml:space="preserve">-h, --help</t>
         </is>
       </c>
       <c r="C191" s="3"/>
@@ -8454,109 +8570,89 @@
       <c r="E191" s="7"/>
       <c r="F191" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">上記の Excel 出力を行わない (既定)</t>
+          <t xml:space="preserve">ヘルプを表示して exit 0</t>
         </is>
       </c>
     </row>
     <row r="192" ht="33.0" customHeight="1">
       <c r="A192" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+          <t xml:space="preserve">5.4-3 対話 bash セッションの tree</t>
         </is>
       </c>
       <c r="B192" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-tree-excel-file FILE</t>
+          <t xml:space="preserve">-a</t>
         </is>
       </c>
       <c r="C192" s="3"/>
       <c r="D192" s="3"/>
       <c r="E192" s="7"/>
-      <c r="F192" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">上記 Excel の出力先を明示指定する (.xlsx)。指定すると Excel 出力を有効にする</t>
-        </is>
-      </c>
+      <c r="F192" s="3"/>
     </row>
     <row r="193" ht="33.0" customHeight="1">
       <c r="A193" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+          <t xml:space="preserve">5.4-3 対話 bash セッションの tree</t>
         </is>
       </c>
       <c r="B193" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-tree-depth N</t>
+          <t xml:space="preserve">-d</t>
         </is>
       </c>
       <c r="C193" s="3"/>
       <c r="D193" s="3"/>
       <c r="E193" s="7"/>
-      <c r="F193" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">/ 直下を深さ 1 として N 階層まで表示 (既定 all は最下層まで)。指定すると画面表示を自動で有効化</t>
-        </is>
-      </c>
+      <c r="F193" s="3"/>
     </row>
     <row r="194" ht="33.0" customHeight="1">
       <c r="A194" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+          <t xml:space="preserve">5.4-3 対話 bash セッションの tree</t>
         </is>
       </c>
       <c r="B194" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-file-limit N</t>
+          <t xml:space="preserve">-f</t>
         </is>
       </c>
       <c r="C194" s="3"/>
       <c r="D194" s="3"/>
       <c r="E194" s="7"/>
-      <c r="F194" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">通常ファイルを表示。各ディレクトリ直下が N 件以下なら全ファイル名、超過時は拡張子別件数。指定すると画面表示を自動で有効化</t>
-        </is>
-      </c>
+      <c r="F194" s="3"/>
     </row>
     <row r="195" ht="33.0" customHeight="1">
       <c r="A195" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+          <t xml:space="preserve">5.4-3 対話 bash セッションの tree</t>
         </is>
       </c>
       <c r="B195" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-file-limit all</t>
+          <t xml:space="preserve">-L 深さ</t>
         </is>
       </c>
       <c r="C195" s="3"/>
       <c r="D195" s="3"/>
       <c r="E195" s="7"/>
-      <c r="F195" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">件数にかかわらず全ファイル名を表示</t>
-        </is>
-      </c>
+      <c r="F195" s="3"/>
     </row>
     <row r="196" ht="33.0" customHeight="1">
       <c r="A196" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+          <t xml:space="preserve">5.4-3 対話 bash セッションの tree</t>
         </is>
       </c>
       <c r="B196" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--deployment-dir-env NAME</t>
+          <t xml:space="preserve">--noreport</t>
         </is>
       </c>
       <c r="C196" s="3"/>
       <c r="D196" s="3"/>
       <c r="E196" s="7"/>
-      <c r="F196" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">指定した環境変数のディレクトリも表示対象へ追加。指定すると画面表示を自動で有効化</t>
-        </is>
-      </c>
+      <c r="F196" s="3"/>
     </row>
     <row r="197" ht="33.0" customHeight="1">
       <c r="A197" s="11" t="inlineStr">
@@ -8566,7 +8662,7 @@
       </c>
       <c r="B197" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">ファイル表示の既定</t>
+          <t xml:space="preserve">(未指定)</t>
         </is>
       </c>
       <c r="C197" s="3"/>
@@ -8574,12 +8670,252 @@
       <c r="E197" s="7"/>
       <c r="F197" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">画面表示・レポート出力とも行わない (既定)。画面には有効化方法を 1 行だけ案内する</t>
+        </is>
+      </c>
+    </row>
+    <row r="198" ht="33.0" customHeight="1">
+      <c r="A198" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+        </is>
+      </c>
+      <c r="B198" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--directory-tree</t>
+        </is>
+      </c>
+      <c r="C198" s="3"/>
+      <c r="D198" s="3"/>
+      <c r="E198" s="7"/>
+      <c r="F198" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">画面へツリーと JBoss EAP デプロイ構造を表示する</t>
+        </is>
+      </c>
+    </row>
+    <row r="199" ht="33.0" customHeight="1">
+      <c r="A199" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+        </is>
+      </c>
+      <c r="B199" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--no-directory-tree</t>
+        </is>
+      </c>
+      <c r="C199" s="3"/>
+      <c r="D199" s="3"/>
+      <c r="E199" s="7"/>
+      <c r="F199" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">画面表示を行わない。下記オプションによる自動有効化も打ち消す</t>
+        </is>
+      </c>
+    </row>
+    <row r="200" ht="33.0" customHeight="1">
+      <c r="A200" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+        </is>
+      </c>
+      <c r="B200" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--directory-tree-report</t>
+        </is>
+      </c>
+      <c r="C200" s="3"/>
+      <c r="D200" s="3"/>
+      <c r="E200" s="7"/>
+      <c r="F200" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--report-dir の全量レポート [3] [4] へ出力する (画面表示とは独立)</t>
+        </is>
+      </c>
+    </row>
+    <row r="201" ht="33.0" customHeight="1">
+      <c r="A201" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+        </is>
+      </c>
+      <c r="B201" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--no-directory-tree-report</t>
+        </is>
+      </c>
+      <c r="C201" s="3"/>
+      <c r="D201" s="3"/>
+      <c r="E201" s="7"/>
+      <c r="F201" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">全量レポートへ出力しない (既定)</t>
+        </is>
+      </c>
+    </row>
+    <row r="202" ht="33.0" customHeight="1">
+      <c r="A202" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+        </is>
+      </c>
+      <c r="B202" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--directory-tree-excel</t>
+        </is>
+      </c>
+      <c r="C202" s="3"/>
+      <c r="D202" s="3"/>
+      <c r="E202" s="7"/>
+      <c r="F202" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ディレクトリとシンボリックリンクのツリーを Excel ブックへ追加出力する (frontend / backend の両方が対象。リンク先は右端の列)</t>
+        </is>
+      </c>
+    </row>
+    <row r="203" ht="33.0" customHeight="1">
+      <c r="A203" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+        </is>
+      </c>
+      <c r="B203" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--no-directory-tree-excel</t>
+        </is>
+      </c>
+      <c r="C203" s="3"/>
+      <c r="D203" s="3"/>
+      <c r="E203" s="7"/>
+      <c r="F203" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">上記の Excel 出力を行わない (既定)</t>
+        </is>
+      </c>
+    </row>
+    <row r="204" ht="33.0" customHeight="1">
+      <c r="A204" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+        </is>
+      </c>
+      <c r="B204" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--directory-tree-excel-file FILE</t>
+        </is>
+      </c>
+      <c r="C204" s="3"/>
+      <c r="D204" s="3"/>
+      <c r="E204" s="7"/>
+      <c r="F204" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">上記 Excel の出力先を明示指定する (.xlsx)。指定すると Excel 出力を有効にする</t>
+        </is>
+      </c>
+    </row>
+    <row r="205" ht="33.0" customHeight="1">
+      <c r="A205" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+        </is>
+      </c>
+      <c r="B205" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--directory-tree-depth N</t>
+        </is>
+      </c>
+      <c r="C205" s="3"/>
+      <c r="D205" s="3"/>
+      <c r="E205" s="7"/>
+      <c r="F205" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">/ 直下を深さ 1 として N 階層まで表示 (既定 all は最下層まで)。指定すると画面表示を自動で有効化</t>
+        </is>
+      </c>
+    </row>
+    <row r="206" ht="33.0" customHeight="1">
+      <c r="A206" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+        </is>
+      </c>
+      <c r="B206" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--directory-file-limit N</t>
+        </is>
+      </c>
+      <c r="C206" s="3"/>
+      <c r="D206" s="3"/>
+      <c r="E206" s="7"/>
+      <c r="F206" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">通常ファイルを表示。各ディレクトリ直下が N 件以下なら全ファイル名、超過時は拡張子別件数。指定すると画面表示を自動で有効化</t>
+        </is>
+      </c>
+    </row>
+    <row r="207" ht="33.0" customHeight="1">
+      <c r="A207" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+        </is>
+      </c>
+      <c r="B207" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--directory-file-limit all</t>
+        </is>
+      </c>
+      <c r="C207" s="3"/>
+      <c r="D207" s="3"/>
+      <c r="E207" s="7"/>
+      <c r="F207" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">件数にかかわらず全ファイル名を表示</t>
+        </is>
+      </c>
+    </row>
+    <row r="208" ht="33.0" customHeight="1">
+      <c r="A208" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+        </is>
+      </c>
+      <c r="B208" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--deployment-dir-env NAME</t>
+        </is>
+      </c>
+      <c r="C208" s="3"/>
+      <c r="D208" s="3"/>
+      <c r="E208" s="7"/>
+      <c r="F208" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">指定した環境変数のディレクトリも表示対象へ追加。指定すると画面表示を自動で有効化</t>
+        </is>
+      </c>
+    </row>
+    <row r="209" ht="33.0" customHeight="1">
+      <c r="A209" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+        </is>
+      </c>
+      <c r="B209" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ファイル表示の既定</t>
+        </is>
+      </c>
+      <c r="C209" s="3"/>
+      <c r="D209" s="3"/>
+      <c r="E209" s="7"/>
+      <c r="F209" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">表示を有効にした場合もディレクトリのみ (通常ファイルは --directory-file-limit 指定時のみ)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:F197"/>
+  <autoFilter ref="A4:F209"/>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A2:F2"/>
@@ -12053,7 +12389,7 @@
         </is>
       </c>
     </row>
-    <row r="35" ht="66.0" customHeight="1">
+    <row r="35" ht="82.5" customHeight="1">
       <c r="A35" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">build_and_verify.sh</t>
@@ -12061,39 +12397,108 @@
       </c>
       <c r="B35" s="7" t="inlineStr">
         <is>
+          <t xml:space="preserve">10-4</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">起動後に JMeter で性能試験を行う (対話で計画とスレッド数 / Ramp-Up / ループを指定)
+結果 (result.jtl) と HTML レポートは --report-dir と同じディレクトリへ出る</t>
+        </is>
+      </c>
+      <c r="D35" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">./build_and_verify.sh --verify-startup --keep-container-mode logs --report-dir ./reports</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="82.5" customHeight="1">
+      <c r="A36" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">build_and_verify.sh</t>
+        </is>
+      </c>
+      <c r="B36" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10-5</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">負荷条件をあらかじめ決めておき、対話での入力を省く</t>
+        </is>
+      </c>
+      <c r="D36" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">./build_and_verify.sh --verify-startup --keep-container-mode logs --report-dir ./reports \
+  --jmeter-plan sample-frontend.jmx --jmeter-threads 200 --jmeter-rampup 200 --jmeter-loops -1 \
+  --jmeter-target frontend --jmeter-duration 600</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="33.0" customHeight="1">
+      <c r="A37" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">build_and_verify.sh</t>
+        </is>
+      </c>
+      <c r="B37" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10-6</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">背面で走らせた性能試験の進捗を、別の端末から確認する</t>
+        </is>
+      </c>
+      <c r="D37" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">./build_and_verify.sh --jmeter-status --report-dir ./reports</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="66.0" customHeight="1">
+      <c r="A38" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">build_and_verify.sh</t>
+        </is>
+      </c>
+      <c r="B38" s="7" t="inlineStr">
+        <is>
           <t xml:space="preserve">11</t>
         </is>
       </c>
-      <c r="C35" s="3" t="inlineStr">
+      <c r="C38" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">全量レポートを保存 (ツリーは画面・レポートとも既定では出さない)
 (JVM パラメータと OpenTelemetry 設定は指定不要で同じレポートへ保存される)</t>
         </is>
       </c>
-      <c r="D35" s="6" t="inlineStr">
+      <c r="D38" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">./build_and_verify.sh --verify-startup --report-dir ./reports</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="82.5" customHeight="1">
-      <c r="A36" s="11" t="inlineStr">
+    <row r="39" ht="82.5" customHeight="1">
+      <c r="A39" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">build_and_verify.sh</t>
         </is>
       </c>
-      <c r="B36" s="7" t="inlineStr">
+      <c r="B39" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">11-2</t>
         </is>
       </c>
-      <c r="C36" s="3" t="inlineStr">
+      <c r="C39" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">画面にもレポートにもコンテナ内ツリーを出す
 --directory-tree-depth / --directory-file-limit を付けると画面表示は自動で有効になる</t>
         </is>
       </c>
-      <c r="D36" s="6" t="inlineStr">
+      <c r="D39" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">./build_and_verify.sh --verify-startup \
     --report-dir ./reports --directory-tree-report \
@@ -12101,160 +12506,160 @@
         </is>
       </c>
     </row>
-    <row r="37" ht="33.0" customHeight="1">
-      <c r="A37" s="11" t="inlineStr">
+    <row r="40" ht="33.0" customHeight="1">
+      <c r="A40" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">build_and_verify.sh</t>
         </is>
       </c>
-      <c r="B37" s="7" t="inlineStr">
+      <c r="B40" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">11-3</t>
         </is>
       </c>
-      <c r="C37" s="3" t="inlineStr">
+      <c r="C40" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">画面には出さず、全量レポートにだけツリーを残す</t>
         </is>
       </c>
-      <c r="D37" s="6" t="inlineStr">
+      <c r="D40" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">./build_and_verify.sh --verify-startup \
     --report-dir ./reports --directory-tree-report</t>
         </is>
       </c>
     </row>
-    <row r="38" ht="33.0" customHeight="1">
-      <c r="A38" s="11" t="inlineStr">
+    <row r="41" ht="33.0" customHeight="1">
+      <c r="A41" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">build_and_verify.sh</t>
         </is>
       </c>
-      <c r="B38" s="7" t="inlineStr">
+      <c r="B41" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">12</t>
         </is>
       </c>
-      <c r="C38" s="3" t="inlineStr">
+      <c r="C41" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">デプロイ構造を環境変数から特定して表示 (指定すると画面表示が有効になる)</t>
         </is>
       </c>
-      <c r="D38" s="6" t="inlineStr">
+      <c r="D41" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">./build_and_verify.sh --verify-startup \
     --deployment-dir-env JBOSS_HOME,APP_DEPLOY_DIR</t>
         </is>
       </c>
     </row>
-    <row r="39" ht="49.5" customHeight="1">
-      <c r="A39" s="11" t="inlineStr">
+    <row r="42" ht="49.5" customHeight="1">
+      <c r="A42" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">build_and_verify.sh</t>
         </is>
       </c>
-      <c r="B39" s="7" t="inlineStr">
+      <c r="B42" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">13</t>
         </is>
       </c>
-      <c r="C39" s="3" t="inlineStr">
+      <c r="C42" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">認証情報を一時配置してビルド
 (コピー先に .npmrc があっても強制上書きし、終了時に元のファイルへ戻す)</t>
         </is>
       </c>
-      <c r="D39" s="6" t="inlineStr">
+      <c r="D42" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">./build_and_verify.sh --copy-file .npmrc:./app</t>
         </is>
       </c>
     </row>
-    <row r="40" ht="33.0" customHeight="1">
-      <c r="A40" s="11" t="inlineStr">
+    <row r="43" ht="33.0" customHeight="1">
+      <c r="A43" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">build_and_verify.sh</t>
         </is>
       </c>
-      <c r="B40" s="7" t="inlineStr">
+      <c r="B43" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">13-2</t>
         </is>
       </c>
-      <c r="C40" s="3" t="inlineStr">
+      <c r="C43" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">コピー先の既存ファイルには一切触れず、あれば中止する</t>
         </is>
       </c>
-      <c r="D40" s="6" t="inlineStr">
+      <c r="D43" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">./build_and_verify.sh --copy-file-no-overwrite --copy-file .npmrc:./app</t>
         </is>
       </c>
     </row>
-    <row r="41" ht="33.0" customHeight="1">
-      <c r="A41" s="11" t="inlineStr">
+    <row r="44" ht="33.0" customHeight="1">
+      <c r="A44" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">build_and_verify.sh</t>
         </is>
       </c>
-      <c r="B41" s="7" t="inlineStr">
+      <c r="B44" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">14</t>
         </is>
       </c>
-      <c r="C41" s="3" t="inlineStr">
+      <c r="C44" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">パラメータストアのマスターパスワードを使ってビルド</t>
         </is>
       </c>
-      <c r="D41" s="6" t="inlineStr">
+      <c r="D44" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">./build_and_verify.sh --jboss-password-param /j1/jboss/master-password</t>
         </is>
       </c>
     </row>
-    <row r="42" ht="66.0" customHeight="1">
-      <c r="A42" s="11" t="inlineStr">
+    <row r="45" ht="66.0" customHeight="1">
+      <c r="A45" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">build_and_verify.sh</t>
         </is>
       </c>
-      <c r="B42" s="7" t="inlineStr">
+      <c r="B45" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">14-2</t>
         </is>
       </c>
-      <c r="C42" s="3" t="inlineStr">
+      <c r="C45" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">マスターパスワードが実行時の値まで一致しているかを検証
 (standalone.xml と CredentialStore まで見るので起動確認と併用する)</t>
         </is>
       </c>
-      <c r="D42" s="6" t="inlineStr">
+      <c r="D45" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">export JBOSS_MASTER_PASSWORD='pa$w#o"r`d&amp;x'
 ./build_and_verify.sh --verify-startup --verify-jboss-password</t>
         </is>
       </c>
     </row>
-    <row r="43" ht="49.5" customHeight="1">
-      <c r="A43" s="11" t="inlineStr">
+    <row r="46" ht="49.5" customHeight="1">
+      <c r="A46" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">build_and_verify.sh</t>
         </is>
       </c>
-      <c r="B43" s="7" t="inlineStr">
+      <c r="B46" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">14-3</t>
         </is>
       </c>
-      <c r="C43" s="3" t="inlineStr">
+      <c r="C46" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">パラメータストアから取得した値で検証し、平文は伏せる</t>
         </is>
       </c>
-      <c r="D43" s="6" t="inlineStr">
+      <c r="D46" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">./build_and_verify.sh --verify-startup \
     --jboss-password-param /j1/jboss/master-password \
@@ -12262,23 +12667,23 @@
         </is>
       </c>
     </row>
-    <row r="44" ht="49.5" customHeight="1">
-      <c r="A44" s="11" t="inlineStr">
+    <row r="47" ht="49.5" customHeight="1">
+      <c r="A47" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">build_and_verify.sh</t>
         </is>
       </c>
-      <c r="B44" s="7" t="inlineStr">
+      <c r="B47" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">14-4</t>
         </is>
       </c>
-      <c r="C44" s="3" t="inlineStr">
+      <c r="C47" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">既定以外のパスに設定ファイル・CredentialStore がある場合</t>
         </is>
       </c>
-      <c r="D44" s="6" t="inlineStr">
+      <c r="D47" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">./build_and_verify.sh --verify-startup --verify-jboss-password \
     --jboss-config-file /opt/eap/standalone/configuration/standalone-full.xml \
@@ -12286,47 +12691,47 @@
         </is>
       </c>
     </row>
-    <row r="45" ht="66.0" customHeight="1">
-      <c r="A45" s="11" t="inlineStr">
+    <row r="48" ht="66.0" customHeight="1">
+      <c r="A48" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">build_and_verify.sh</t>
         </is>
       </c>
-      <c r="B45" s="7" t="inlineStr">
+      <c r="B48" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">14-5</t>
         </is>
       </c>
-      <c r="C45" s="3" t="inlineStr">
+      <c r="C48" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">cwagent の設定ファイルチェックとコンテナ内設定の照合を行う
 (compose.yml に cwagent があれば自動。送達レポートは既定では行わない)</t>
         </is>
       </c>
-      <c r="D45" s="6" t="inlineStr">
+      <c r="D48" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">./build_and_verify.sh --verify-startup \
     --compose-service app,cwagent,cloudwatch-logs-mock --startup-service app</t>
         </is>
       </c>
     </row>
-    <row r="46" ht="66.0" customHeight="1">
-      <c r="A46" s="11" t="inlineStr">
+    <row r="49" ht="66.0" customHeight="1">
+      <c r="A49" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">build_and_verify.sh</t>
         </is>
       </c>
-      <c r="B46" s="7" t="inlineStr">
+      <c r="B49" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">14-6</t>
         </is>
       </c>
-      <c r="C46" s="3" t="inlineStr">
+      <c r="C49" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">送達レポートまで行い、送達待ちを 3 分へ延ばして届かなければビルド失敗とする</t>
         </is>
       </c>
-      <c r="D46" s="6" t="inlineStr">
+      <c r="D49" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">./build_and_verify.sh --verify-startup \
     --compose-service app,cwagent,cloudwatch-logs-mock --startup-service app \
@@ -12335,24 +12740,24 @@
         </is>
       </c>
     </row>
-    <row r="47" ht="66.0" customHeight="1">
-      <c r="A47" s="11" t="inlineStr">
+    <row r="50" ht="66.0" customHeight="1">
+      <c r="A50" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">build_and_verify.sh</t>
         </is>
       </c>
-      <c r="B47" s="7" t="inlineStr">
+      <c r="B50" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">14-7</t>
         </is>
       </c>
-      <c r="C47" s="3" t="inlineStr">
+      <c r="C50" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">実 CloudWatch Logs のロググループへ届いたかを aws logs で確認する
 (ロググループが無ければ設定ファイルの名前で作成してから確認する)</t>
         </is>
       </c>
-      <c r="D47" s="6" t="inlineStr">
+      <c r="D50" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">./build_and_verify.sh --verify-startup \
     --compose-service app,cwagent --startup-service app \
@@ -12361,131 +12766,131 @@
         </is>
       </c>
     </row>
-    <row r="48" ht="33.0" customHeight="1">
-      <c r="A48" s="11" t="inlineStr">
+    <row r="51" ht="33.0" customHeight="1">
+      <c r="A51" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">build_and_verify.sh</t>
         </is>
       </c>
-      <c r="B48" s="7" t="inlineStr">
+      <c r="B51" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">15</t>
         </is>
       </c>
-      <c r="C48" s="3" t="inlineStr">
+      <c r="C51" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">検証後に Docker を完全クリーンアップ (確認フレーズ入力が必要)</t>
         </is>
       </c>
-      <c r="D48" s="6" t="inlineStr">
+      <c r="D51" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">./build_and_verify.sh --verify-startup --cleanup-all-docker-data</t>
         </is>
       </c>
     </row>
-    <row r="49" ht="82.5" customHeight="1">
-      <c r="A49" s="11" t="inlineStr">
+    <row r="52" ht="82.5" customHeight="1">
+      <c r="A52" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">build_and_verify.sh</t>
         </is>
       </c>
-      <c r="B49" s="7" t="inlineStr">
+      <c r="B52" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">15-2</t>
         </is>
       </c>
-      <c r="C49" s="3" t="inlineStr">
+      <c r="C52" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">ディスクを増やさずに --no-cache の検証を回す
 旧世代イメージの回収は既定で有効。ビルドキャッシュは 10GB まで残して削除し、
 実行前からの増減を表示する</t>
         </is>
       </c>
-      <c r="D49" s="6" t="inlineStr">
+      <c r="D52" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">./build_and_verify.sh --no-cache --verify-startup \
     --disk-usage-report --prune-build-cache-keep 10GB</t>
         </is>
       </c>
     </row>
-    <row r="50" ht="33.0" customHeight="1">
-      <c r="A50" s="11" t="inlineStr">
+    <row r="53" ht="33.0" customHeight="1">
+      <c r="A53" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">build_and_verify.sh</t>
         </is>
       </c>
-      <c r="B50" s="7" t="inlineStr">
+      <c r="B53" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">15-3</t>
         </is>
       </c>
-      <c r="C50" s="3" t="inlineStr">
+      <c r="C53" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">使用量の増減だけを先に測る (削除は行わない)</t>
         </is>
       </c>
-      <c r="D50" s="6" t="inlineStr">
+      <c r="D53" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">./build_and_verify.sh --no-cache --disk-usage-report</t>
         </is>
       </c>
     </row>
-    <row r="51" ht="33.0" customHeight="1">
-      <c r="A51" s="11" t="inlineStr">
+    <row r="54" ht="33.0" customHeight="1">
+      <c r="A54" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">build_and_verify.sh</t>
         </is>
       </c>
-      <c r="B51" s="7" t="inlineStr">
+      <c r="B54" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">15-4</t>
         </is>
       </c>
-      <c r="C51" s="3" t="inlineStr">
+      <c r="C54" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">世代を比較したいので旧イメージを残す (調査用)</t>
         </is>
       </c>
-      <c r="D51" s="6" t="inlineStr">
+      <c r="D54" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">./build_and_verify.sh --no-cache --no-reclaim-old-image</t>
         </is>
       </c>
     </row>
-    <row r="52" ht="33.0" customHeight="1">
-      <c r="A52" s="11" t="inlineStr">
+    <row r="55" ht="33.0" customHeight="1">
+      <c r="A55" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">build_and_verify.sh</t>
         </is>
       </c>
-      <c r="B52" s="7" t="inlineStr">
+      <c r="B55" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">16</t>
         </is>
       </c>
-      <c r="C52" s="3" t="inlineStr">
+      <c r="C55" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">build_and_push.sh 経由での呼び出し (同じ処理)</t>
         </is>
       </c>
-      <c r="D52" s="6" t="inlineStr">
+      <c r="D55" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">./build_and_push.sh --build-only --verify-startup --log-dir ./logs</t>
         </is>
       </c>
     </row>
-    <row r="53" ht="115.5" customHeight="1">
-      <c r="A53" s="11" t="inlineStr">
+    <row r="56" ht="115.5" customHeight="1">
+      <c r="A56" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">build_and_verify.sh</t>
         </is>
       </c>
-      <c r="B53" s="7" t="inlineStr">
+      <c r="B56" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">17</t>
         </is>
       </c>
-      <c r="C53" s="3" t="inlineStr">
+      <c r="C56" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">全量レポートへ Java 例外解析を残す
 (reports/build_and_verify_&lt;日時&gt;.txt … [10] に例外解析の全文。
@@ -12493,7 +12898,7 @@
 画面表示も Excel / テキストの出力も行わない)</t>
         </is>
       </c>
-      <c r="D53" s="6" t="inlineStr">
+      <c r="D56" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">./build_and_verify.sh --verify-startup \
     --compose-service app --startup-service app \
@@ -12502,23 +12907,23 @@
         </is>
       </c>
     </row>
-    <row r="54" ht="82.5" customHeight="1">
-      <c r="A54" s="11" t="inlineStr">
+    <row r="57" ht="82.5" customHeight="1">
+      <c r="A57" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">build_and_verify.sh</t>
         </is>
       </c>
-      <c r="B54" s="7" t="inlineStr">
+      <c r="B57" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">17-2</t>
         </is>
       </c>
-      <c r="C54" s="3" t="inlineStr">
+      <c r="C57" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">解析結果を画面でも読む (既定は非表示)</t>
         </is>
       </c>
-      <c r="D54" s="6" t="inlineStr">
+      <c r="D57" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">./build_and_verify.sh --verify-startup \
     --compose-service app --startup-service app \
@@ -12528,24 +12933,24 @@
         </is>
       </c>
     </row>
-    <row r="55" ht="66.0" customHeight="1">
-      <c r="A55" s="11" t="inlineStr">
+    <row r="58" ht="66.0" customHeight="1">
+      <c r="A58" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">build_and_verify.sh</t>
         </is>
       </c>
-      <c r="B55" s="7" t="inlineStr">
+      <c r="B58" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">17-3</t>
         </is>
       </c>
-      <c r="C55" s="3" t="inlineStr">
+      <c r="C58" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Java 例外解析の Excel / テキストを任意のパスへ出力する
 (テキストは --deploy-exception-text を指定したときだけ出力される)</t>
         </is>
       </c>
-      <c r="D55" s="6" t="inlineStr">
+      <c r="D58" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">./build_and_verify.sh --verify-startup \
     --compose-service app --startup-service app \
@@ -12554,40 +12959,40 @@
         </is>
       </c>
     </row>
-    <row r="56" ht="33.0" customHeight="1">
-      <c r="A56" s="11" t="inlineStr">
+    <row r="59" ht="33.0" customHeight="1">
+      <c r="A59" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">build_and_verify.sh</t>
         </is>
       </c>
-      <c r="B56" s="7" t="inlineStr">
+      <c r="B59" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">17-4</t>
         </is>
       </c>
-      <c r="C56" s="3" t="inlineStr">
+      <c r="C59" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Java 例外解析を行わない (解析処理ごと省く)</t>
         </is>
       </c>
-      <c r="D56" s="6" t="inlineStr">
+      <c r="D59" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">./build_and_verify.sh --verify-startup --no-deploy-exception-analysis</t>
         </is>
       </c>
     </row>
-    <row r="57" ht="198.0" customHeight="1">
-      <c r="A57" s="11" t="inlineStr">
+    <row r="60" ht="198.0" customHeight="1">
+      <c r="A60" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">build_and_verify.sh</t>
         </is>
       </c>
-      <c r="B57" s="7" t="inlineStr">
+      <c r="B60" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">17-5</t>
         </is>
       </c>
-      <c r="C57" s="3" t="inlineStr">
+      <c r="C60" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">読み取り専用ファイルシステム (read_only) の書き込み先分析
 既定で毎回実行される。--report-dir があれば
@@ -12597,7 +13002,7 @@
 対象から外し、entrypoint.sh などが起動のたびに書く場所を「要対応」に挙げる</t>
         </is>
       </c>
-      <c r="D57" s="6" t="inlineStr">
+      <c r="D60" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">./build_and_verify.sh --verify-startup \
     --compose-service app --startup-service app \
@@ -12606,23 +13011,23 @@
         </is>
       </c>
     </row>
-    <row r="58" ht="66.0" customHeight="1">
-      <c r="A58" s="11" t="inlineStr">
+    <row r="61" ht="66.0" customHeight="1">
+      <c r="A61" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">build_and_verify.sh</t>
         </is>
       </c>
-      <c r="B58" s="7" t="inlineStr">
+      <c r="B61" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">17-6</t>
         </is>
       </c>
-      <c r="C58" s="3" t="inlineStr">
+      <c r="C61" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">読み取り専用ファイルシステム分析の Excel / テキストを任意のパスへ出力する</t>
         </is>
       </c>
-      <c r="D58" s="6" t="inlineStr">
+      <c r="D61" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">./build_and_verify.sh --verify-startup \
     --compose-service app --startup-service app \
@@ -12631,24 +13036,24 @@
         </is>
       </c>
     </row>
-    <row r="59" ht="66.0" customHeight="1">
-      <c r="A59" s="11" t="inlineStr">
+    <row r="62" ht="66.0" customHeight="1">
+      <c r="A62" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">build_and_verify.sh</t>
         </is>
       </c>
-      <c r="B59" s="7" t="inlineStr">
+      <c r="B62" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">17-7</t>
         </is>
       </c>
-      <c r="C59" s="3" t="inlineStr">
+      <c r="C62" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">読み取り専用ファイルシステム分析の結果を画面でも読む
 既定では画面へ出さず、Excel / テキストへ残すだけ</t>
         </is>
       </c>
-      <c r="D59" s="6" t="inlineStr">
+      <c r="D62" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">./build_and_verify.sh --verify-startup \
     --compose-service app --startup-service app \
@@ -12656,85 +13061,85 @@
         </is>
       </c>
     </row>
-    <row r="60" ht="33.0" customHeight="1">
-      <c r="A60" s="11" t="inlineStr">
+    <row r="63" ht="33.0" customHeight="1">
+      <c r="A63" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">build_and_verify.sh</t>
         </is>
       </c>
-      <c r="B60" s="7" t="inlineStr">
+      <c r="B63" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">17-8</t>
         </is>
       </c>
-      <c r="C60" s="3" t="inlineStr">
+      <c r="C63" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">読み取り専用ファイルシステムの分析を行わない</t>
         </is>
       </c>
-      <c r="D60" s="6" t="inlineStr">
+      <c r="D63" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">./build_and_verify.sh --verify-startup --no-readonly-analysis</t>
         </is>
       </c>
     </row>
-    <row r="61" ht="66.0" customHeight="1">
-      <c r="A61" s="11" t="inlineStr">
+    <row r="64" ht="66.0" customHeight="1">
+      <c r="A64" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">build_and_verify.sh</t>
         </is>
       </c>
-      <c r="B61" s="7" t="inlineStr">
+      <c r="B64" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">18</t>
         </is>
       </c>
-      <c r="C61" s="3" t="inlineStr">
+      <c r="C64" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">ビルドが exporting layers から進まないときの調査
 進捗を 10 秒ごとに表示し、60 秒出力が途切れたら診断を出す</t>
         </is>
       </c>
-      <c r="D61" s="6" t="inlineStr">
+      <c r="D64" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">./build_and_verify.sh --build-progress-interval 10 --build-stall-timeout 60</t>
         </is>
       </c>
     </row>
-    <row r="62" ht="33.0" customHeight="1">
-      <c r="A62" s="11" t="inlineStr">
+    <row r="65" ht="33.0" customHeight="1">
+      <c r="A65" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">build_and_verify.sh</t>
         </is>
       </c>
-      <c r="B62" s="7" t="inlineStr">
+      <c r="B65" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">19</t>
         </is>
       </c>
-      <c r="C62" s="3" t="inlineStr">
+      <c r="C65" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">30 分を超えたらビルドを中断して確実にプロンプトを戻す</t>
         </is>
       </c>
-      <c r="D62" s="6" t="inlineStr">
+      <c r="D65" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">./build_and_verify.sh --build-timeout 1800</t>
         </is>
       </c>
     </row>
-    <row r="63" ht="132.0" customHeight="1">
-      <c r="A63" s="11" t="inlineStr">
+    <row r="66" ht="132.0" customHeight="1">
+      <c r="A66" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">build_and_verify.sh</t>
         </is>
       </c>
-      <c r="B63" s="7" t="inlineStr">
+      <c r="B66" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">20</t>
         </is>
       </c>
-      <c r="C63" s="3" t="inlineStr">
+      <c r="C66" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">ECS サーキットブレーカによるタスク停止の再現 (既定で有効)
 必須コンテナの healthcheck が unhealthy になった実行でだけ動く。
@@ -12742,7 +13147,7 @@
 停止前後の server.log を突き合わせて切れ方まで判定する</t>
         </is>
       </c>
-      <c r="D63" s="6" t="inlineStr">
+      <c r="D66" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">./build_and_verify.sh --verify-startup \
     --compose-service app --startup-service app \
@@ -12750,24 +13155,24 @@
         </is>
       </c>
     </row>
-    <row r="64" ht="66.0" customHeight="1">
-      <c r="A64" s="11" t="inlineStr">
+    <row r="67" ht="66.0" customHeight="1">
+      <c r="A67" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">build_and_verify.sh</t>
         </is>
       </c>
-      <c r="B64" s="7" t="inlineStr">
+      <c r="B67" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">20-2</t>
         </is>
       </c>
-      <c r="C64" s="3" t="inlineStr">
+      <c r="C67" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">正常に起動する構成でも、事象を手元で起こしてみる
 (動作確認をすべて終えた後に 1 回だけ停止する。置き換えは行わない)</t>
         </is>
       </c>
-      <c r="D64" s="6" t="inlineStr">
+      <c r="D67" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">./build_and_verify.sh --verify-startup \
     --compose-service app --startup-service app \
@@ -12775,75 +13180,75 @@
         </is>
       </c>
     </row>
-    <row r="65" ht="33.0" customHeight="1">
-      <c r="A65" s="11" t="inlineStr">
+    <row r="68" ht="33.0" customHeight="1">
+      <c r="A68" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">build_and_verify.sh</t>
         </is>
       </c>
-      <c r="B65" s="7" t="inlineStr">
+      <c r="B68" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">20-3</t>
         </is>
       </c>
-      <c r="C65" s="3" t="inlineStr">
+      <c r="C68" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">SIGKILL を早めて reload との重なりを作りやすくする</t>
         </is>
       </c>
-      <c r="D65" s="6" t="inlineStr">
+      <c r="D68" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">./build_and_verify.sh --verify-startup \
     --ecs-stop-timeout 5 --ecs-circuit-breaker-reload-delay 0</t>
         </is>
       </c>
     </row>
-    <row r="66" ht="33.0" customHeight="1">
-      <c r="A66" s="11" t="inlineStr">
+    <row r="69" ht="33.0" customHeight="1">
+      <c r="A69" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">build_and_verify.sh</t>
         </is>
       </c>
-      <c r="B66" s="7" t="inlineStr">
+      <c r="B69" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">20-4</t>
         </is>
       </c>
-      <c r="C66" s="3" t="inlineStr">
+      <c r="C69" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">切断の要因を切り分ける (reload を挟まず、停止だけを再現する)</t>
         </is>
       </c>
-      <c r="D66" s="6" t="inlineStr">
+      <c r="D69" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">./build_and_verify.sh --verify-startup --no-ecs-circuit-breaker-reload</t>
         </is>
       </c>
     </row>
-    <row r="67" ht="33.0" customHeight="1">
-      <c r="A67" s="11" t="inlineStr">
+    <row r="70" ht="33.0" customHeight="1">
+      <c r="A70" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">build_and_verify.sh</t>
         </is>
       </c>
-      <c r="B67" s="7" t="inlineStr">
+      <c r="B70" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">20-5</t>
         </is>
       </c>
-      <c r="C67" s="3" t="inlineStr">
+      <c r="C70" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">再現を行わない (従来どおり、unhealthy でも止めない)</t>
         </is>
       </c>
-      <c r="D67" s="6" t="inlineStr">
+      <c r="D70" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">./build_and_verify.sh --verify-startup --no-ecs-circuit-breaker</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:D67"/>
+  <autoFilter ref="A4:D70"/>
   <mergeCells count="2">
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A2:D2"/>

--- a/docs/scripts_reference.xlsx
+++ b/docs/scripts_reference.xlsx
@@ -345,7 +345,7 @@
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">31 件</t>
+          <t xml:space="preserve">33 件</t>
         </is>
       </c>
       <c r="C9" s="7" t="inlineStr">
@@ -629,8 +629,22 @@
       <c r="C27" s="8"/>
       <c r="D27" s="8"/>
     </row>
+    <row r="28" ht="66.0" customHeight="1">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ベース → フロント → バックを続けてプッシュし、ベースのタグを受け渡したい</t>
+        </is>
+      </c>
+      <c r="B28" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">build_and_push_all.sh (各イメージ用ラッパー経由で本スクリプトを呼ぶ。5.9 参照)</t>
+        </is>
+      </c>
+      <c r="C28" s="8"/>
+      <c r="D28" s="8"/>
+    </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="10">
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="A4:D4"/>
@@ -640,6 +654,7 @@
     <mergeCell ref="B25:D25"/>
     <mergeCell ref="B26:D26"/>
     <mergeCell ref="B27:D27"/>
+    <mergeCell ref="B28:D28"/>
   </mergeCells>
   <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1004,7 +1019,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="33.0" customHeight="1">
+    <row r="14" ht="66.0" customHeight="1">
       <c r="A14" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">4.2 ビルドと出力</t>
@@ -1012,17 +1027,17 @@
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--build-progress-interval SEC</t>
+          <t xml:space="preserve">--base-image-tag TAG</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 以上の整数 (秒)</t>
-        </is>
-      </c>
-      <c r="D14" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">30</t>
+          <t xml:space="preserve">英数字と . _ - (先頭は英数字か _、128 文字以内)</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(なし = 渡さない)</t>
         </is>
       </c>
       <c r="E14" s="7" t="inlineStr">
@@ -1032,7 +1047,7 @@
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ビルド中に経過時間・BuildKit のフェーズ・data root の空き容量の増減を表示する間隔。0 で表示しない (5.7 参照)</t>
+          <t xml:space="preserve">指定した場合のみ、ビルド引数 BASE_IMAGE_TAG=TAG として compose build へ渡す (--build-arg)。フロント / バックのように、プッシュ済みのベースイメージを FROM で参照するイメージのビルドで使う。ベースイメージ自体のビルドでは指定しない (5.9 参照)</t>
         </is>
       </c>
     </row>
@@ -1044,7 +1059,7 @@
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--build-stall-timeout SEC</t>
+          <t xml:space="preserve">--build-progress-interval SEC</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
@@ -1054,7 +1069,7 @@
       </c>
       <c r="D15" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">300</t>
+          <t xml:space="preserve">30</t>
         </is>
       </c>
       <c r="E15" s="7" t="inlineStr">
@@ -1064,7 +1079,7 @@
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ビルド出力がこの秒数途切れたら停滞と判断し、原因の切り分け診断を表示する。0 で検知しない。検知しても処理は中断しない</t>
+          <t xml:space="preserve">ビルド中に経過時間・BuildKit のフェーズ・data root の空き容量の増減を表示する間隔。0 で表示しない (5.7 参照)</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1091,7 @@
       </c>
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--build-timeout SEC</t>
+          <t xml:space="preserve">--build-stall-timeout SEC</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
@@ -1086,7 +1101,7 @@
       </c>
       <c r="D16" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 (無制限)</t>
+          <t xml:space="preserve">300</t>
         </is>
       </c>
       <c r="E16" s="7" t="inlineStr">
@@ -1096,7 +1111,7 @@
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ビルド全体の上限秒数。超えたら診断のうえ SIGTERM で中断し (20 秒後に SIGKILL)、exit 1</t>
+          <t xml:space="preserve">ビルド出力がこの秒数途切れたら停滞と判断し、原因の切り分け診断を表示する。0 で検知しない。検知しても処理は中断しない</t>
         </is>
       </c>
     </row>
@@ -1108,59 +1123,59 @@
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
+          <t xml:space="preserve">--build-timeout SEC</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0 以上の整数 (秒)</t>
+        </is>
+      </c>
+      <c r="D17" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0 (無制限)</t>
+        </is>
+      </c>
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ビルド全体の上限秒数。超えたら診断のうえ SIGTERM で中断し (20 秒後に SIGKILL)、exit 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="33.0" customHeight="1">
+      <c r="A18" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.2 ビルドと出力</t>
+        </is>
+      </c>
+      <c r="B18" s="11" t="inlineStr">
+        <is>
           <t xml:space="preserve">--no-build-watchdog</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr">
+      <c r="C18" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">フラグ</t>
         </is>
       </c>
-      <c r="D17" s="3" t="inlineStr">
+      <c r="D18" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">false</t>
         </is>
       </c>
-      <c r="E17" s="7" t="inlineStr">
+      <c r="E18" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="F17" s="3" t="inlineStr">
+      <c r="F18" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">上記の監視をすべて行わない。監視が有効な間は BUILDKIT_PROGRESS=tty を plain へ切り替えるため、tty 形式を使いたい場合に指定する</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="19.5" customHeight="1">
-      <c r="A18" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.2 ビルドと出力</t>
-        </is>
-      </c>
-      <c r="B18" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--container-name NAME</t>
-        </is>
-      </c>
-      <c r="C18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">任意の文字列</t>
-        </is>
-      </c>
-      <c r="D18" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--repository の値</t>
-        </is>
-      </c>
-      <c r="E18" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">不可</t>
-        </is>
-      </c>
-      <c r="F18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">imagedefinition.json の name</t>
         </is>
       </c>
     </row>
@@ -1172,17 +1187,17 @@
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--output FILE</t>
+          <t xml:space="preserve">--container-name NAME</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ファイルパス</t>
+          <t xml:space="preserve">任意の文字列</t>
         </is>
       </c>
       <c r="D19" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">imagedefinition.json</t>
+          <t xml:space="preserve">--repository の値</t>
         </is>
       </c>
       <c r="E19" s="7" t="inlineStr">
@@ -1192,63 +1207,71 @@
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">imagedefinition の出力先</t>
+          <t xml:space="preserve">imagedefinition.json の name</t>
         </is>
       </c>
     </row>
     <row r="20" ht="19.5" customHeight="1">
       <c r="A20" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.3 実行制御・ログ</t>
+          <t xml:space="preserve">4.2 ビルドと出力</t>
         </is>
       </c>
       <c r="B20" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--dry-run</t>
+          <t xml:space="preserve">--output FILE</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
-        </is>
-      </c>
-      <c r="D20" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
-        </is>
-      </c>
-      <c r="E20" s="7"/>
+          <t xml:space="preserve">ファイルパス</t>
+        </is>
+      </c>
+      <c r="D20" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">imagedefinition.json</t>
+        </is>
+      </c>
+      <c r="E20" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ビルド/ログイン/タグ付け/プッシュ/ファイル出力を行わず、実行内容のみ表示</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="19.5" customHeight="1">
+          <t xml:space="preserve">imagedefinition の出力先</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="66.0" customHeight="1">
       <c r="A21" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.3 実行制御・ログ</t>
+          <t xml:space="preserve">4.2 ビルドと出力</t>
         </is>
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--build-only</t>
+          <t xml:space="preserve">--image-uri-file FILE</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
+          <t xml:space="preserve">ファイルパス</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">false</t>
-        </is>
-      </c>
-      <c r="E21" s="7"/>
+          <t xml:space="preserve">(なし)</t>
+        </is>
+      </c>
+      <c r="E21" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ビルドのみ実行 (build_and_verify.sh へ委譲)。ECR 関連処理は行わない</t>
+          <t xml:space="preserve">プッシュしたイメージの参照 (&lt;registry&gt;/&lt;repository&gt;:&lt;tag&gt;) を 1 行で書き出す。呼び出し元のスクリプト (build_and_push_all.sh など) がタグを受け取るためのもの。プッシュと imagedefinition の出力が済んだ最後に書き出す。--dry-run 時もプレビュー上の参照を書き出す (5.9 参照)</t>
         </is>
       </c>
     </row>
@@ -1260,23 +1283,23 @@
       </c>
       <c r="B22" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--log-dir DIR</t>
+          <t xml:space="preserve">--dry-run</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ディレクトリパス</t>
+          <t xml:space="preserve">フラグ</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">(なし)</t>
+          <t xml:space="preserve">false</t>
         </is>
       </c>
       <c r="E22" s="7"/>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">画面出力を DIR/build_and_push_&lt;日時&gt;.log にも保存。ディレクトリは自動作成</t>
+          <t xml:space="preserve">ビルド/ログイン/タグ付け/プッシュ/ファイル出力を行わず、実行内容のみ表示</t>
         </is>
       </c>
     </row>
@@ -1288,7 +1311,7 @@
       </c>
       <c r="B23" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">-h, --help</t>
+          <t xml:space="preserve">--build-only</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
@@ -1298,30 +1321,30 @@
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">—</t>
+          <t xml:space="preserve">false</t>
         </is>
       </c>
       <c r="E23" s="7"/>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ヘルプを表示して exit 0</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="33.0" customHeight="1">
+          <t xml:space="preserve">ビルドのみ実行 (build_and_verify.sh へ委譲)。ECR 関連処理は行わない</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="19.5" customHeight="1">
       <c r="A24" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.4 ビルド前後の一時ファイル</t>
+          <t xml:space="preserve">4.3 実行制御・ログ</t>
         </is>
       </c>
       <c r="B24" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--copy-file SRC:DEST_DIR</t>
+          <t xml:space="preserve">--log-dir DIR</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">コピー元:コピー先ディレクトリ</t>
+          <t xml:space="preserve">ディレクトリパス</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
@@ -1329,59 +1352,55 @@
           <t xml:space="preserve">(なし)</t>
         </is>
       </c>
-      <c r="E24" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">可</t>
-        </is>
-      </c>
+      <c r="E24" s="7"/>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ビルド前にコピーし、終了後 (成功・失敗を問わず) 自動削除</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="49.5" customHeight="1">
+          <t xml:space="preserve">画面出力を DIR/build_and_push_&lt;日時&gt;.log にも保存。ディレクトリは自動作成</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="19.5" customHeight="1">
       <c r="A25" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.5 JBoss マスターパスワード (BuildKit シークレット)</t>
+          <t xml:space="preserve">4.3 実行制御・ログ</t>
         </is>
       </c>
       <c r="B25" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--jboss-password-param NAME</t>
+          <t xml:space="preserve">-h, --help</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">SSM パラメータ名</t>
+          <t xml:space="preserve">フラグ</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">(なし)</t>
+          <t xml:space="preserve">—</t>
         </is>
       </c>
       <c r="E25" s="7"/>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">パラメータストアから取得 (--with-decryption)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="49.5" customHeight="1">
+          <t xml:space="preserve">ヘルプを表示して exit 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="33.0" customHeight="1">
       <c r="A26" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.5 JBoss マスターパスワード (BuildKit シークレット)</t>
+          <t xml:space="preserve">4.4 ビルド前後の一時ファイル</t>
         </is>
       </c>
       <c r="B26" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--jboss-password VALUE</t>
+          <t xml:space="preserve">--copy-file SRC:DEST_DIR</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">パスワード文字列</t>
+          <t xml:space="preserve">コピー元:コピー先ディレクトリ</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
@@ -1389,10 +1408,14 @@
           <t xml:space="preserve">(なし)</t>
         </is>
       </c>
-      <c r="E26" s="7"/>
+      <c r="E26" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">可</t>
+        </is>
+      </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">直接指定。--jboss-password-param とは排他</t>
+          <t xml:space="preserve">ビルド前にコピーし、終了後 (成功・失敗を問わず) 自動削除</t>
         </is>
       </c>
     </row>
@@ -1404,83 +1427,83 @@
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--jboss-password-env NAME</t>
+          <t xml:space="preserve">--jboss-password-param NAME</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">環境変数名</t>
-        </is>
-      </c>
-      <c r="D27" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">JBOSS_MASTER_PASSWORD</t>
+          <t xml:space="preserve">SSM パラメータ名</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(なし)</t>
         </is>
       </c>
       <c r="E27" s="7"/>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">受け渡しに使う環境変数名。単独指定時は既存の環境変数値を使用</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="33.0" customHeight="1">
+          <t xml:space="preserve">パラメータストアから取得 (--with-decryption)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="49.5" customHeight="1">
       <c r="A28" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.6 スイッチバック</t>
+          <t xml:space="preserve">4.5 JBoss マスターパスワード (BuildKit シークレット)</t>
         </is>
       </c>
       <c r="B28" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--switchback-shell PATH</t>
+          <t xml:space="preserve">--jboss-password VALUE</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">シェルスクリプトのパス</t>
-        </is>
-      </c>
-      <c r="D28" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">env SWITCHBACK_SHELL</t>
+          <t xml:space="preserve">パスワード文字列</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(なし)</t>
         </is>
       </c>
       <c r="E28" s="7"/>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">別チーム提供のスイッチバック用シェル (source で読み込む)</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="19.5" customHeight="1">
+          <t xml:space="preserve">直接指定。--jboss-password-param とは排他</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="49.5" customHeight="1">
       <c r="A29" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.6 スイッチバック</t>
+          <t xml:space="preserve">4.5 JBoss マスターパスワード (BuildKit シークレット)</t>
         </is>
       </c>
       <c r="B29" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--auto-switchback</t>
+          <t xml:space="preserve">--jboss-password-env NAME</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
-        </is>
-      </c>
-      <c r="D29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">環境変数名</t>
+        </is>
+      </c>
+      <c r="D29" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">JBOSS_MASTER_PASSWORD</t>
         </is>
       </c>
       <c r="E29" s="7"/>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ECR 権限が無い場合に自動でスイッチバックして継続</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="19.5" customHeight="1">
+          <t xml:space="preserve">受け渡しに使う環境変数名。単独指定時は既存の環境変数値を使用</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="33.0" customHeight="1">
       <c r="A30" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">4.6 スイッチバック</t>
@@ -1488,83 +1511,79 @@
       </c>
       <c r="B30" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--warn-only</t>
+          <t xml:space="preserve">--switchback-shell PATH</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
+          <t xml:space="preserve">シェルスクリプトのパス</t>
         </is>
       </c>
       <c r="D30" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">既定</t>
+          <t xml:space="preserve">env SWITCHBACK_SHELL</t>
         </is>
       </c>
       <c r="E30" s="7"/>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ECR 権限が無い場合に警告して終了</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="33.0" customHeight="1">
+          <t xml:space="preserve">別チーム提供のスイッチバック用シェル (source で読み込む)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="19.5" customHeight="1">
       <c r="A31" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.7 CA 証明書 (BuildKit シークレット)</t>
+          <t xml:space="preserve">4.6 スイッチバック</t>
         </is>
       </c>
       <c r="B31" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--cacert-dir DIR</t>
+          <t xml:space="preserve">--auto-switchback</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ディレクトリのパス</t>
+          <t xml:space="preserve">フラグ</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">(なし)</t>
-        </is>
-      </c>
-      <c r="E31" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">可</t>
-        </is>
-      </c>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="E31" s="7"/>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">cacert.crt を置いたディレクトリ。指定した全ディレクトリ分を 1 つの tar にまとめてビルドへ渡す</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="33.0" customHeight="1">
+          <t xml:space="preserve">ECR 権限が無い場合に自動でスイッチバックして継続</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="19.5" customHeight="1">
       <c r="A32" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.7 CA 証明書 (BuildKit シークレット)</t>
+          <t xml:space="preserve">4.6 スイッチバック</t>
         </is>
       </c>
       <c r="B32" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--cacert-secret-id ID</t>
+          <t xml:space="preserve">--warn-only</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">英数字と . _ -</t>
+          <t xml:space="preserve">フラグ</t>
         </is>
       </c>
       <c r="D32" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">cacerts</t>
+          <t xml:space="preserve">既定</t>
         </is>
       </c>
       <c r="E32" s="7"/>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">シークレット id。compose.yml の secrets 名、Dockerfile の RUN --mount=type=secret,id=... と一致させる</t>
+          <t xml:space="preserve">ECR 権限が無い場合に警告して終了</t>
         </is>
       </c>
     </row>
@@ -1576,23 +1595,27 @@
       </c>
       <c r="B33" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--cacert-bundle PATH</t>
+          <t xml:space="preserve">--cacert-dir DIR</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">tar のパス</t>
-        </is>
-      </c>
-      <c r="D33" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">一時ファイル</t>
-        </is>
-      </c>
-      <c r="E33" s="7"/>
+          <t xml:space="preserve">ディレクトリのパス</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(なし)</t>
+        </is>
+      </c>
+      <c r="E33" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">可</t>
+        </is>
+      </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">生成する tar の出力先。指定時は自動削除しない</t>
+          <t xml:space="preserve">cacert.crt を置いたディレクトリ。指定した全ディレクトリ分を 1 つの tar にまとめてビルドへ渡す</t>
         </is>
       </c>
     </row>
@@ -1604,23 +1627,23 @@
       </c>
       <c r="B34" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--cacert-bundle-env NAME</t>
+          <t xml:space="preserve">--cacert-secret-id ID</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">環境変数名</t>
+          <t xml:space="preserve">英数字と . _ -</t>
         </is>
       </c>
       <c r="D34" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">CACERT_BUNDLE_FILE</t>
+          <t xml:space="preserve">cacerts</t>
         </is>
       </c>
       <c r="E34" s="7"/>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">tar のパスを compose へ渡す環境変数名。compose.yml の file: が参照する変数名と一致させる</t>
+          <t xml:space="preserve">シークレット id。compose.yml の secrets 名、Dockerfile の RUN --mount=type=secret,id=... と一致させる</t>
         </is>
       </c>
     </row>
@@ -1632,32 +1655,88 @@
       </c>
       <c r="B35" s="11" t="inlineStr">
         <is>
+          <t xml:space="preserve">--cacert-bundle PATH</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tar のパス</t>
+        </is>
+      </c>
+      <c r="D35" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">一時ファイル</t>
+        </is>
+      </c>
+      <c r="E35" s="7"/>
+      <c r="F35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">生成する tar の出力先。指定時は自動削除しない</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="33.0" customHeight="1">
+      <c r="A36" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.7 CA 証明書 (BuildKit シークレット)</t>
+        </is>
+      </c>
+      <c r="B36" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--cacert-bundle-env NAME</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">環境変数名</t>
+        </is>
+      </c>
+      <c r="D36" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CACERT_BUNDLE_FILE</t>
+        </is>
+      </c>
+      <c r="E36" s="7"/>
+      <c r="F36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tar のパスを compose へ渡す環境変数名。compose.yml の file: が参照する変数名と一致させる</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="33.0" customHeight="1">
+      <c r="A37" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.7 CA 証明書 (BuildKit シークレット)</t>
+        </is>
+      </c>
+      <c r="B37" s="11" t="inlineStr">
+        <is>
           <t xml:space="preserve">--cacert-glob PATTERN</t>
         </is>
       </c>
-      <c r="C35" s="3" t="inlineStr">
+      <c r="C37" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">glob パターン</t>
         </is>
       </c>
-      <c r="D35" s="8" t="inlineStr">
+      <c r="D37" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">*.crt と *.pem</t>
         </is>
       </c>
-      <c r="E35" s="7" t="inlineStr">
+      <c r="E37" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">可</t>
         </is>
       </c>
-      <c r="F35" s="3" t="inlineStr">
+      <c r="F37" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">各ディレクトリから取り込むファイルのパターン。指定するとこの値だけが対象になる</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:F35"/>
+  <autoFilter ref="A4:F37"/>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A2:F2"/>
@@ -9334,7 +9413,7 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="99.0" customHeight="1">
+    <row r="22" ht="148.5" customHeight="1">
       <c r="A22" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">16</t>
@@ -9347,7 +9426,7 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">docker compose -f &lt;file&gt; build [--no-cache] [service] を監視プロセス付きで実行 (進捗表示・停滞検知・上限時間での中断。5.7 参照)。開始前に data root の空き容量を確認</t>
+          <t xml:space="preserve">docker compose -f &lt;file&gt; build [--no-cache] [--build-arg BASE_IMAGE_TAG=&lt;tag&gt;] [service] を監視プロセス付きで実行 (--build-arg は --base-image-tag 指定時のみ) (進捗表示・停滞検知・上限時間での中断。5.7 参照)。開始前に data root の空き容量を確認</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
@@ -9444,7 +9523,7 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="33.0" customHeight="1">
+    <row r="27" ht="82.5" customHeight="1">
       <c r="A27" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">21</t>
@@ -9457,7 +9536,7 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">imagedefinition.json を書き込み (書き込み失敗も検出)</t>
+          <t xml:space="preserve">imagedefinition.json を書き込み (書き込み失敗も検出)。--image-uri-file 指定時は、最後にプッシュしたイメージの参照を書き出す</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
@@ -10662,7 +10741,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="33.0" customHeight="1">
+    <row r="7" ht="49.5" customHeight="1">
       <c r="A7" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">build_and_push.sh</t>
@@ -10680,7 +10759,7 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">不明なオプション、値の欠落、ビルド監視の各値が 0 未満か非数値、--account-id/--registry 未指定、リポジトリ名・タグ接頭辞の形式違反、JBoss オプションの排他違反、--copy-file の書式不正</t>
+          <t xml:space="preserve">不明なオプション、値の欠落、ビルド監視の各値が 0 未満か非数値、--account-id/--registry 未指定、リポジトリ名・タグ接頭辞・--base-image-tag の形式違反、--image-uri-file の出力先ディレクトリ不在 (またはディレクトリを指定)、JBoss オプションの排他違反、--copy-file の書式不正</t>
         </is>
       </c>
     </row>
@@ -11899,7 +11978,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="99.0" customHeight="1">
+    <row r="14" ht="33.0" customHeight="1">
       <c r="A14" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">build_and_push.sh</t>
@@ -11912,105 +11991,152 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">レジストリを直接指定 (アカウント ID 不要)
+          <t xml:space="preserve">レジストリを直接指定 (アカウント ID 不要)</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">./build_and_push.sh --registry 123456789012.dkr.ecr.ap-northeast-1.amazonaws.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="66.0" customHeight="1">
+      <c r="A15" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">build_and_push.sh</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フロントイメージ: プッシュ済みベースイメージのタグをビルド引数 BASE_IMAGE_TAG で渡す</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">./build_and_push.sh --account-id 123456789012 \
+    --repository frontimage --tag-prefix FrontImage \
+    --compose-service frontend --local-image j1/front.local \
+    --base-image-tag BaseImage-20260923120000</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="115.5" customHeight="1">
+      <c r="A16" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">build_and_push.sh</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ベース → フロント → バックをラッパー経由で一括実行し、タグを受け渡す (5.9 参照)
 ビルドが exporting layers から進まないときの調査 (進捗 10 秒 / 停滞判定 60 秒)
 30 分を超えたらビルドを中断して確実にプロンプトを戻す</t>
         </is>
       </c>
-      <c r="D14" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">./build_and_push.sh --registry 123456789012.dkr.ecr.ap-northeast-1.amazonaws.com
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">./build_and_push_all.sh
 ./build_and_push.sh --account-id 123456789012 \
     --build-progress-interval 10 --build-stall-timeout 60
 ./build_and_push.sh --account-id 123456789012 --build-timeout 1800</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="19.5" customHeight="1">
-      <c r="A15" s="11" t="inlineStr">
+    <row r="17" ht="19.5" customHeight="1">
+      <c r="A17" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">buildx_build_and_push.sh</t>
         </is>
       </c>
-      <c r="B15" s="7" t="inlineStr">
+      <c r="B17" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
+      <c r="C17" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">最小構成</t>
         </is>
       </c>
-      <c r="D15" s="6" t="inlineStr">
+      <c r="D17" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">./buildx_build_and_push.sh --account-id 123456789012</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="33.0" customHeight="1">
-      <c r="A16" s="11" t="inlineStr">
+    <row r="18" ht="33.0" customHeight="1">
+      <c r="A18" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">buildx_build_and_push.sh</t>
         </is>
       </c>
-      <c r="B16" s="7" t="inlineStr">
+      <c r="B18" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr">
+      <c r="C18" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Dockerfile とコンテキストを明示</t>
         </is>
       </c>
-      <c r="D16" s="6" t="inlineStr">
+      <c r="D18" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">./buildx_build_and_push.sh --account-id 123456789012 \
     --dockerfile ./docker/base.Dockerfile --context ./docker</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="33.0" customHeight="1">
-      <c r="A17" s="11" t="inlineStr">
+    <row r="19" ht="33.0" customHeight="1">
+      <c r="A19" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">buildx_build_and_push.sh</t>
         </is>
       </c>
-      <c r="B17" s="7" t="inlineStr">
+      <c r="B19" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr">
+      <c r="C19" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">プラットフォームとビルダーを指定し、CI 向けに plain 出力</t>
         </is>
       </c>
-      <c r="D17" s="6" t="inlineStr">
+      <c r="D19" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">./buildx_build_and_push.sh --account-id 123456789012 \
     --platform linux/amd64 --builder mybuilder --progress plain</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="49.5" customHeight="1">
-      <c r="A18" s="11" t="inlineStr">
+    <row r="20" ht="49.5" customHeight="1">
+      <c r="A20" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">buildx_build_and_push.sh</t>
         </is>
       </c>
-      <c r="B18" s="7" t="inlineStr">
+      <c r="B20" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="C18" s="3" t="inlineStr">
+      <c r="C20" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">ビルド引数と追加コンテキスト</t>
         </is>
       </c>
-      <c r="D18" s="6" t="inlineStr">
+      <c r="D20" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">./buildx_build_and_push.sh --account-id 123456789012 \
     --build-arg JAVA_VERSION=17 \
@@ -12018,23 +12144,23 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="66.0" customHeight="1">
-      <c r="A19" s="11" t="inlineStr">
+    <row r="21" ht="66.0" customHeight="1">
+      <c r="A21" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">buildx_build_and_push.sh</t>
         </is>
       </c>
-      <c r="B19" s="7" t="inlineStr">
+      <c r="B21" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">5</t>
         </is>
       </c>
-      <c r="C19" s="3" t="inlineStr">
+      <c r="C21" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">任意のシークレットを渡す</t>
         </is>
       </c>
-      <c r="D19" s="6" t="inlineStr">
+      <c r="D21" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">export GITHUB_TOKEN=ghp_xxx
 ./buildx_build_and_push.sh --account-id 123456789012 \
@@ -12043,23 +12169,23 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="49.5" customHeight="1">
-      <c r="A20" s="11" t="inlineStr">
+    <row r="22" ht="49.5" customHeight="1">
+      <c r="A22" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">buildx_build_and_push.sh</t>
         </is>
       </c>
-      <c r="B20" s="7" t="inlineStr">
+      <c r="B22" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">6</t>
         </is>
       </c>
-      <c r="C20" s="3" t="inlineStr">
+      <c r="C22" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">JBoss マスターパスワードをパラメータストアから取得</t>
         </is>
       </c>
-      <c r="D20" s="6" t="inlineStr">
+      <c r="D22" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">./buildx_build_and_push.sh --account-id 123456789012 \
     --jboss-password-param /j1/jboss/master-password \
@@ -12067,47 +12193,47 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="19.5" customHeight="1">
-      <c r="A21" s="11" t="inlineStr">
+    <row r="23" ht="19.5" customHeight="1">
+      <c r="A23" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">buildx_build_and_push.sh</t>
         </is>
       </c>
-      <c r="B21" s="7" t="inlineStr">
+      <c r="B23" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">7</t>
         </is>
       </c>
-      <c r="C21" s="3" t="inlineStr">
+      <c r="C23" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">実行内容の事前確認</t>
         </is>
       </c>
-      <c r="D21" s="6" t="inlineStr">
+      <c r="D23" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">./buildx_build_and_push.sh --account-id 123456789012 --dry-run</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="99.0" customHeight="1">
-      <c r="A22" s="11" t="inlineStr">
+    <row r="24" ht="99.0" customHeight="1">
+      <c r="A24" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">buildx_build_and_push.sh</t>
         </is>
       </c>
-      <c r="B22" s="7" t="inlineStr">
+      <c r="B24" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">8</t>
         </is>
       </c>
-      <c r="C22" s="3" t="inlineStr">
+      <c r="C24" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">ECR 権限が無い場合に自動スイッチバック + ログ保存
 ビルドが exporting layers から進まないときの調査 (進捗 10 秒 / 停滞判定 60 秒)
 30 分を超えたらビルドを中断して確実にプロンプトを戻す</t>
         </is>
       </c>
-      <c r="D22" s="6" t="inlineStr">
+      <c r="D24" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">./buildx_build_and_push.sh --account-id 123456789012 \
     --auto-switchback --switchback-shell /opt/team/switchback.sh \
@@ -12118,158 +12244,158 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="19.5" customHeight="1">
-      <c r="A23" s="11" t="inlineStr">
+    <row r="25" ht="19.5" customHeight="1">
+      <c r="A25" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">build_and_verify.sh</t>
         </is>
       </c>
-      <c r="B23" s="7" t="inlineStr">
+      <c r="B25" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="C23" s="3" t="inlineStr">
+      <c r="C25" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">ビルドのみ</t>
         </is>
       </c>
-      <c r="D23" s="6" t="inlineStr">
+      <c r="D25" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">./build_and_verify.sh</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="19.5" customHeight="1">
-      <c r="A24" s="11" t="inlineStr">
+    <row r="26" ht="19.5" customHeight="1">
+      <c r="A26" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">build_and_verify.sh</t>
         </is>
       </c>
-      <c r="B24" s="7" t="inlineStr">
+      <c r="B26" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="C24" s="3" t="inlineStr">
+      <c r="C26" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">ビルド + JBoss EAP の起動確認</t>
         </is>
       </c>
-      <c r="D24" s="6" t="inlineStr">
+      <c r="D26" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">./build_and_verify.sh --verify-startup</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="33.0" customHeight="1">
-      <c r="A25" s="11" t="inlineStr">
+    <row r="27" ht="33.0" customHeight="1">
+      <c r="A27" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">build_and_verify.sh</t>
         </is>
       </c>
-      <c r="B25" s="7" t="inlineStr">
+      <c r="B27" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="C25" s="3" t="inlineStr">
+      <c r="C27" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">起動確認 + ヘルスチェック URL の応答確認</t>
         </is>
       </c>
-      <c r="D25" s="6" t="inlineStr">
+      <c r="D27" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">./build_and_verify.sh --verify-startup \
     --verify-url http://localhost:8080/health --expect-status 200</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="33.0" customHeight="1">
-      <c r="A26" s="11" t="inlineStr">
+    <row r="28" ht="33.0" customHeight="1">
+      <c r="A28" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">build_and_verify.sh</t>
         </is>
       </c>
-      <c r="B26" s="7" t="inlineStr">
+      <c r="B28" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="C26" s="3" t="inlineStr">
+      <c r="C28" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">複数サービスを同時に起動し、app のみ起動確認する</t>
         </is>
       </c>
-      <c r="D26" s="6" t="inlineStr">
+      <c r="D28" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">./build_and_verify.sh --compose-service app,db --startup-service app</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="33.0" customHeight="1">
-      <c r="A27" s="11" t="inlineStr">
+    <row r="29" ht="33.0" customHeight="1">
+      <c r="A29" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">build_and_verify.sh</t>
         </is>
       </c>
-      <c r="B27" s="7" t="inlineStr">
+      <c r="B29" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">5</t>
         </is>
       </c>
-      <c r="C27" s="3" t="inlineStr">
+      <c r="C29" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">依存サービスが healthy になるまで待ってから起動確認</t>
         </is>
       </c>
-      <c r="D27" s="6" t="inlineStr">
+      <c r="D29" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">./build_and_verify.sh --compose-service app,db --startup-service app \
     --wait-healthy --wait-timeout 300</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="33.0" customHeight="1">
-      <c r="A28" s="11" t="inlineStr">
+    <row r="30" ht="33.0" customHeight="1">
+      <c r="A30" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">build_and_verify.sh</t>
         </is>
       </c>
-      <c r="B28" s="7" t="inlineStr">
+      <c r="B30" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">6</t>
         </is>
       </c>
-      <c r="C28" s="3" t="inlineStr">
+      <c r="C30" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">初期化専用サービスの停止を失敗扱いにしない</t>
         </is>
       </c>
-      <c r="D28" s="6" t="inlineStr">
+      <c r="D30" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">./build_and_verify.sh --compose-service app,db,init --startup-service app \
     --allow-service-exit init</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="49.5" customHeight="1">
-      <c r="A29" s="11" t="inlineStr">
+    <row r="31" ht="49.5" customHeight="1">
+      <c r="A31" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">build_and_verify.sh</t>
         </is>
       </c>
-      <c r="B29" s="7" t="inlineStr">
+      <c r="B31" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">7</t>
         </is>
       </c>
-      <c r="C29" s="3" t="inlineStr">
+      <c r="C31" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">POST でボディを送って確認</t>
         </is>
       </c>
-      <c r="D29" s="6" t="inlineStr">
+      <c r="D31" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">./build_and_verify.sh --verify-startup \
     --verify-url http://localhost:8080/app/api --url-method POST \
@@ -12277,158 +12403,158 @@
         </is>
       </c>
     </row>
-    <row r="30" ht="19.5" customHeight="1">
-      <c r="A30" s="11" t="inlineStr">
+    <row r="32" ht="19.5" customHeight="1">
+      <c r="A32" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">build_and_verify.sh</t>
         </is>
       </c>
-      <c r="B30" s="7" t="inlineStr">
+      <c r="B32" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">8</t>
         </is>
       </c>
-      <c r="C30" s="3" t="inlineStr">
+      <c r="C32" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">起動後にコンテナへ bash で入る</t>
         </is>
       </c>
-      <c r="D30" s="6" t="inlineStr">
+      <c r="D32" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">./build_and_verify.sh --keep-container-mode bash</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="33.0" customHeight="1">
-      <c r="A31" s="11" t="inlineStr">
+    <row r="33" ht="33.0" customHeight="1">
+      <c r="A33" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">build_and_verify.sh</t>
         </is>
       </c>
-      <c r="B31" s="7" t="inlineStr">
+      <c r="B33" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">9</t>
         </is>
       </c>
-      <c r="C31" s="3" t="inlineStr">
+      <c r="C33" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">起動後に対話式 HTTP リクエストを送る</t>
         </is>
       </c>
-      <c r="D31" s="6" t="inlineStr">
+      <c r="D33" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">./build_and_verify.sh --keep-container-mode http \
     --jboss-context-root /app --jboss-http-port 8080</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="33.0" customHeight="1">
-      <c r="A32" s="11" t="inlineStr">
+    <row r="34" ht="33.0" customHeight="1">
+      <c r="A34" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">build_and_verify.sh</t>
         </is>
       </c>
-      <c r="B32" s="7" t="inlineStr">
+      <c r="B34" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">10</t>
         </is>
       </c>
-      <c r="C32" s="3" t="inlineStr">
+      <c r="C34" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">起動中サービスのログ・healthcheck・送達診断を調べる</t>
         </is>
       </c>
-      <c r="D32" s="6" t="inlineStr">
+      <c r="D34" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">./build_and_verify.sh --compose-service app,db,cwagent --keep-container-mode logs</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="66.0" customHeight="1">
-      <c r="A33" s="11" t="inlineStr">
+    <row r="35" ht="66.0" customHeight="1">
+      <c r="A35" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">build_and_verify.sh</t>
         </is>
       </c>
-      <c r="B33" s="7" t="inlineStr">
+      <c r="B35" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">10-2</t>
         </is>
       </c>
-      <c r="C33" s="3" t="inlineStr">
+      <c r="C35" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">デプロイエラーになってもコンテナを残して調査する (既定の動作)
 AP サーバ起動後にデプロイが失敗すると、そのまま対話操作が始まる</t>
         </is>
       </c>
-      <c r="D33" s="6" t="inlineStr">
+      <c r="D35" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">./build_and_verify.sh --verify-startup --compose-service app,db</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="33.0" customHeight="1">
-      <c r="A34" s="11" t="inlineStr">
+    <row r="36" ht="33.0" customHeight="1">
+      <c r="A36" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">build_and_verify.sh</t>
         </is>
       </c>
-      <c r="B34" s="7" t="inlineStr">
+      <c r="B36" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">10-3</t>
         </is>
       </c>
-      <c r="C34" s="3" t="inlineStr">
+      <c r="C36" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">従来どおり、デプロイエラーならそのまま終了する (CI 向け)</t>
         </is>
       </c>
-      <c r="D34" s="6" t="inlineStr">
+      <c r="D36" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">./build_and_verify.sh --verify-startup --exit-on-deploy-error</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="82.5" customHeight="1">
-      <c r="A35" s="11" t="inlineStr">
+    <row r="37" ht="82.5" customHeight="1">
+      <c r="A37" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">build_and_verify.sh</t>
         </is>
       </c>
-      <c r="B35" s="7" t="inlineStr">
+      <c r="B37" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">10-4</t>
         </is>
       </c>
-      <c r="C35" s="3" t="inlineStr">
+      <c r="C37" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">起動後に JMeter で性能試験を行う (対話で計画とスレッド数 / Ramp-Up / ループを指定)
 結果 (result.jtl) と HTML レポートは --report-dir と同じディレクトリへ出る</t>
         </is>
       </c>
-      <c r="D35" s="6" t="inlineStr">
+      <c r="D37" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">./build_and_verify.sh --verify-startup --keep-container-mode logs --report-dir ./reports</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="82.5" customHeight="1">
-      <c r="A36" s="11" t="inlineStr">
+    <row r="38" ht="82.5" customHeight="1">
+      <c r="A38" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">build_and_verify.sh</t>
         </is>
       </c>
-      <c r="B36" s="7" t="inlineStr">
+      <c r="B38" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">10-5</t>
         </is>
       </c>
-      <c r="C36" s="3" t="inlineStr">
+      <c r="C38" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">負荷条件をあらかじめ決めておき、対話での入力を省く</t>
         </is>
       </c>
-      <c r="D36" s="6" t="inlineStr">
+      <c r="D38" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">./build_and_verify.sh --verify-startup --keep-container-mode logs --report-dir ./reports \
   --jmeter-plan sample-frontend.jmx --jmeter-threads 200 --jmeter-rampup 200 --jmeter-loops -1 \
@@ -12436,69 +12562,69 @@
         </is>
       </c>
     </row>
-    <row r="37" ht="33.0" customHeight="1">
-      <c r="A37" s="11" t="inlineStr">
+    <row r="39" ht="33.0" customHeight="1">
+      <c r="A39" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">build_and_verify.sh</t>
         </is>
       </c>
-      <c r="B37" s="7" t="inlineStr">
+      <c r="B39" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">10-6</t>
         </is>
       </c>
-      <c r="C37" s="3" t="inlineStr">
+      <c r="C39" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">背面で走らせた性能試験の進捗を、別の端末から確認する</t>
         </is>
       </c>
-      <c r="D37" s="6" t="inlineStr">
+      <c r="D39" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">./build_and_verify.sh --jmeter-status --report-dir ./reports</t>
         </is>
       </c>
     </row>
-    <row r="38" ht="66.0" customHeight="1">
-      <c r="A38" s="11" t="inlineStr">
+    <row r="40" ht="66.0" customHeight="1">
+      <c r="A40" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">build_and_verify.sh</t>
         </is>
       </c>
-      <c r="B38" s="7" t="inlineStr">
+      <c r="B40" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">11</t>
         </is>
       </c>
-      <c r="C38" s="3" t="inlineStr">
+      <c r="C40" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">全量レポートを保存 (ツリーは画面・レポートとも既定では出さない)
 (JVM パラメータと OpenTelemetry 設定は指定不要で同じレポートへ保存される)</t>
         </is>
       </c>
-      <c r="D38" s="6" t="inlineStr">
+      <c r="D40" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">./build_and_verify.sh --verify-startup --report-dir ./reports</t>
         </is>
       </c>
     </row>
-    <row r="39" ht="82.5" customHeight="1">
-      <c r="A39" s="11" t="inlineStr">
+    <row r="41" ht="82.5" customHeight="1">
+      <c r="A41" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">build_and_verify.sh</t>
         </is>
       </c>
-      <c r="B39" s="7" t="inlineStr">
+      <c r="B41" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">11-2</t>
         </is>
       </c>
-      <c r="C39" s="3" t="inlineStr">
+      <c r="C41" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">画面にもレポートにもコンテナ内ツリーを出す
 --directory-tree-depth / --directory-file-limit を付けると画面表示は自動で有効になる</t>
         </is>
       </c>
-      <c r="D39" s="6" t="inlineStr">
+      <c r="D41" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">./build_and_verify.sh --verify-startup \
     --report-dir ./reports --directory-tree-report \
@@ -12506,160 +12632,160 @@
         </is>
       </c>
     </row>
-    <row r="40" ht="33.0" customHeight="1">
-      <c r="A40" s="11" t="inlineStr">
+    <row r="42" ht="33.0" customHeight="1">
+      <c r="A42" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">build_and_verify.sh</t>
         </is>
       </c>
-      <c r="B40" s="7" t="inlineStr">
+      <c r="B42" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">11-3</t>
         </is>
       </c>
-      <c r="C40" s="3" t="inlineStr">
+      <c r="C42" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">画面には出さず、全量レポートにだけツリーを残す</t>
         </is>
       </c>
-      <c r="D40" s="6" t="inlineStr">
+      <c r="D42" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">./build_and_verify.sh --verify-startup \
     --report-dir ./reports --directory-tree-report</t>
         </is>
       </c>
     </row>
-    <row r="41" ht="33.0" customHeight="1">
-      <c r="A41" s="11" t="inlineStr">
+    <row r="43" ht="33.0" customHeight="1">
+      <c r="A43" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">build_and_verify.sh</t>
         </is>
       </c>
-      <c r="B41" s="7" t="inlineStr">
+      <c r="B43" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">12</t>
         </is>
       </c>
-      <c r="C41" s="3" t="inlineStr">
+      <c r="C43" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">デプロイ構造を環境変数から特定して表示 (指定すると画面表示が有効になる)</t>
         </is>
       </c>
-      <c r="D41" s="6" t="inlineStr">
+      <c r="D43" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">./build_and_verify.sh --verify-startup \
     --deployment-dir-env JBOSS_HOME,APP_DEPLOY_DIR</t>
         </is>
       </c>
     </row>
-    <row r="42" ht="49.5" customHeight="1">
-      <c r="A42" s="11" t="inlineStr">
+    <row r="44" ht="49.5" customHeight="1">
+      <c r="A44" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">build_and_verify.sh</t>
         </is>
       </c>
-      <c r="B42" s="7" t="inlineStr">
+      <c r="B44" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">13</t>
         </is>
       </c>
-      <c r="C42" s="3" t="inlineStr">
+      <c r="C44" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">認証情報を一時配置してビルド
 (コピー先に .npmrc があっても強制上書きし、終了時に元のファイルへ戻す)</t>
         </is>
       </c>
-      <c r="D42" s="6" t="inlineStr">
+      <c r="D44" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">./build_and_verify.sh --copy-file .npmrc:./app</t>
         </is>
       </c>
     </row>
-    <row r="43" ht="33.0" customHeight="1">
-      <c r="A43" s="11" t="inlineStr">
+    <row r="45" ht="33.0" customHeight="1">
+      <c r="A45" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">build_and_verify.sh</t>
         </is>
       </c>
-      <c r="B43" s="7" t="inlineStr">
+      <c r="B45" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">13-2</t>
         </is>
       </c>
-      <c r="C43" s="3" t="inlineStr">
+      <c r="C45" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">コピー先の既存ファイルには一切触れず、あれば中止する</t>
         </is>
       </c>
-      <c r="D43" s="6" t="inlineStr">
+      <c r="D45" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">./build_and_verify.sh --copy-file-no-overwrite --copy-file .npmrc:./app</t>
         </is>
       </c>
     </row>
-    <row r="44" ht="33.0" customHeight="1">
-      <c r="A44" s="11" t="inlineStr">
+    <row r="46" ht="33.0" customHeight="1">
+      <c r="A46" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">build_and_verify.sh</t>
         </is>
       </c>
-      <c r="B44" s="7" t="inlineStr">
+      <c r="B46" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">14</t>
         </is>
       </c>
-      <c r="C44" s="3" t="inlineStr">
+      <c r="C46" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">パラメータストアのマスターパスワードを使ってビルド</t>
         </is>
       </c>
-      <c r="D44" s="6" t="inlineStr">
+      <c r="D46" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">./build_and_verify.sh --jboss-password-param /j1/jboss/master-password</t>
         </is>
       </c>
     </row>
-    <row r="45" ht="66.0" customHeight="1">
-      <c r="A45" s="11" t="inlineStr">
+    <row r="47" ht="66.0" customHeight="1">
+      <c r="A47" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">build_and_verify.sh</t>
         </is>
       </c>
-      <c r="B45" s="7" t="inlineStr">
+      <c r="B47" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">14-2</t>
         </is>
       </c>
-      <c r="C45" s="3" t="inlineStr">
+      <c r="C47" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">マスターパスワードが実行時の値まで一致しているかを検証
 (standalone.xml と CredentialStore まで見るので起動確認と併用する)</t>
         </is>
       </c>
-      <c r="D45" s="6" t="inlineStr">
+      <c r="D47" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">export JBOSS_MASTER_PASSWORD='pa$w#o"r`d&amp;x'
 ./build_and_verify.sh --verify-startup --verify-jboss-password</t>
         </is>
       </c>
     </row>
-    <row r="46" ht="49.5" customHeight="1">
-      <c r="A46" s="11" t="inlineStr">
+    <row r="48" ht="49.5" customHeight="1">
+      <c r="A48" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">build_and_verify.sh</t>
         </is>
       </c>
-      <c r="B46" s="7" t="inlineStr">
+      <c r="B48" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">14-3</t>
         </is>
       </c>
-      <c r="C46" s="3" t="inlineStr">
+      <c r="C48" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">パラメータストアから取得した値で検証し、平文は伏せる</t>
         </is>
       </c>
-      <c r="D46" s="6" t="inlineStr">
+      <c r="D48" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">./build_and_verify.sh --verify-startup \
     --jboss-password-param /j1/jboss/master-password \
@@ -12667,23 +12793,23 @@
         </is>
       </c>
     </row>
-    <row r="47" ht="49.5" customHeight="1">
-      <c r="A47" s="11" t="inlineStr">
+    <row r="49" ht="49.5" customHeight="1">
+      <c r="A49" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">build_and_verify.sh</t>
         </is>
       </c>
-      <c r="B47" s="7" t="inlineStr">
+      <c r="B49" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">14-4</t>
         </is>
       </c>
-      <c r="C47" s="3" t="inlineStr">
+      <c r="C49" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">既定以外のパスに設定ファイル・CredentialStore がある場合</t>
         </is>
       </c>
-      <c r="D47" s="6" t="inlineStr">
+      <c r="D49" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">./build_and_verify.sh --verify-startup --verify-jboss-password \
     --jboss-config-file /opt/eap/standalone/configuration/standalone-full.xml \
@@ -12691,47 +12817,47 @@
         </is>
       </c>
     </row>
-    <row r="48" ht="66.0" customHeight="1">
-      <c r="A48" s="11" t="inlineStr">
+    <row r="50" ht="66.0" customHeight="1">
+      <c r="A50" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">build_and_verify.sh</t>
         </is>
       </c>
-      <c r="B48" s="7" t="inlineStr">
+      <c r="B50" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">14-5</t>
         </is>
       </c>
-      <c r="C48" s="3" t="inlineStr">
+      <c r="C50" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">cwagent の設定ファイルチェックとコンテナ内設定の照合を行う
 (compose.yml に cwagent があれば自動。送達レポートは既定では行わない)</t>
         </is>
       </c>
-      <c r="D48" s="6" t="inlineStr">
+      <c r="D50" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">./build_and_verify.sh --verify-startup \
     --compose-service app,cwagent,cloudwatch-logs-mock --startup-service app</t>
         </is>
       </c>
     </row>
-    <row r="49" ht="66.0" customHeight="1">
-      <c r="A49" s="11" t="inlineStr">
+    <row r="51" ht="66.0" customHeight="1">
+      <c r="A51" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">build_and_verify.sh</t>
         </is>
       </c>
-      <c r="B49" s="7" t="inlineStr">
+      <c r="B51" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">14-6</t>
         </is>
       </c>
-      <c r="C49" s="3" t="inlineStr">
+      <c r="C51" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">送達レポートまで行い、送達待ちを 3 分へ延ばして届かなければビルド失敗とする</t>
         </is>
       </c>
-      <c r="D49" s="6" t="inlineStr">
+      <c r="D51" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">./build_and_verify.sh --verify-startup \
     --compose-service app,cwagent,cloudwatch-logs-mock --startup-service app \
@@ -12740,24 +12866,24 @@
         </is>
       </c>
     </row>
-    <row r="50" ht="66.0" customHeight="1">
-      <c r="A50" s="11" t="inlineStr">
+    <row r="52" ht="66.0" customHeight="1">
+      <c r="A52" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">build_and_verify.sh</t>
         </is>
       </c>
-      <c r="B50" s="7" t="inlineStr">
+      <c r="B52" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">14-7</t>
         </is>
       </c>
-      <c r="C50" s="3" t="inlineStr">
+      <c r="C52" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">実 CloudWatch Logs のロググループへ届いたかを aws logs で確認する
 (ロググループが無ければ設定ファイルの名前で作成してから確認する)</t>
         </is>
       </c>
-      <c r="D50" s="6" t="inlineStr">
+      <c r="D52" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">./build_and_verify.sh --verify-startup \
     --compose-service app,cwagent --startup-service app \
@@ -12766,97 +12892,53 @@
         </is>
       </c>
     </row>
-    <row r="51" ht="33.0" customHeight="1">
-      <c r="A51" s="11" t="inlineStr">
+    <row r="53" ht="33.0" customHeight="1">
+      <c r="A53" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">build_and_verify.sh</t>
         </is>
       </c>
-      <c r="B51" s="7" t="inlineStr">
+      <c r="B53" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">15</t>
         </is>
       </c>
-      <c r="C51" s="3" t="inlineStr">
+      <c r="C53" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">検証後に Docker を完全クリーンアップ (確認フレーズ入力が必要)</t>
         </is>
       </c>
-      <c r="D51" s="6" t="inlineStr">
+      <c r="D53" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">./build_and_verify.sh --verify-startup --cleanup-all-docker-data</t>
         </is>
       </c>
     </row>
-    <row r="52" ht="82.5" customHeight="1">
-      <c r="A52" s="11" t="inlineStr">
+    <row r="54" ht="82.5" customHeight="1">
+      <c r="A54" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">build_and_verify.sh</t>
         </is>
       </c>
-      <c r="B52" s="7" t="inlineStr">
+      <c r="B54" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">15-2</t>
         </is>
       </c>
-      <c r="C52" s="3" t="inlineStr">
+      <c r="C54" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">ディスクを増やさずに --no-cache の検証を回す
 旧世代イメージの回収は既定で有効。ビルドキャッシュは 10GB まで残して削除し、
 実行前からの増減を表示する</t>
         </is>
       </c>
-      <c r="D52" s="6" t="inlineStr">
+      <c r="D54" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">./build_and_verify.sh --no-cache --verify-startup \
     --disk-usage-report --prune-build-cache-keep 10GB</t>
         </is>
       </c>
     </row>
-    <row r="53" ht="33.0" customHeight="1">
-      <c r="A53" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">build_and_verify.sh</t>
-        </is>
-      </c>
-      <c r="B53" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">15-3</t>
-        </is>
-      </c>
-      <c r="C53" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">使用量の増減だけを先に測る (削除は行わない)</t>
-        </is>
-      </c>
-      <c r="D53" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">./build_and_verify.sh --no-cache --disk-usage-report</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" ht="33.0" customHeight="1">
-      <c r="A54" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">build_and_verify.sh</t>
-        </is>
-      </c>
-      <c r="B54" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">15-4</t>
-        </is>
-      </c>
-      <c r="C54" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">世代を比較したいので旧イメージを残す (調査用)</t>
-        </is>
-      </c>
-      <c r="D54" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">./build_and_verify.sh --no-cache --no-reclaim-old-image</t>
-        </is>
-      </c>
-    </row>
     <row r="55" ht="33.0" customHeight="1">
       <c r="A55" s="11" t="inlineStr">
         <is>
@@ -12865,32 +12947,76 @@
       </c>
       <c r="B55" s="7" t="inlineStr">
         <is>
+          <t xml:space="preserve">15-3</t>
+        </is>
+      </c>
+      <c r="C55" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">使用量の増減だけを先に測る (削除は行わない)</t>
+        </is>
+      </c>
+      <c r="D55" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">./build_and_verify.sh --no-cache --disk-usage-report</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="33.0" customHeight="1">
+      <c r="A56" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">build_and_verify.sh</t>
+        </is>
+      </c>
+      <c r="B56" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15-4</t>
+        </is>
+      </c>
+      <c r="C56" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">世代を比較したいので旧イメージを残す (調査用)</t>
+        </is>
+      </c>
+      <c r="D56" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">./build_and_verify.sh --no-cache --no-reclaim-old-image</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="33.0" customHeight="1">
+      <c r="A57" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">build_and_verify.sh</t>
+        </is>
+      </c>
+      <c r="B57" s="7" t="inlineStr">
+        <is>
           <t xml:space="preserve">16</t>
         </is>
       </c>
-      <c r="C55" s="3" t="inlineStr">
+      <c r="C57" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">build_and_push.sh 経由での呼び出し (同じ処理)</t>
         </is>
       </c>
-      <c r="D55" s="6" t="inlineStr">
+      <c r="D57" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">./build_and_push.sh --build-only --verify-startup --log-dir ./logs</t>
         </is>
       </c>
     </row>
-    <row r="56" ht="115.5" customHeight="1">
-      <c r="A56" s="11" t="inlineStr">
+    <row r="58" ht="115.5" customHeight="1">
+      <c r="A58" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">build_and_verify.sh</t>
         </is>
       </c>
-      <c r="B56" s="7" t="inlineStr">
+      <c r="B58" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">17</t>
         </is>
       </c>
-      <c r="C56" s="3" t="inlineStr">
+      <c r="C58" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">全量レポートへ Java 例外解析を残す
 (reports/build_and_verify_&lt;日時&gt;.txt … [10] に例外解析の全文。
@@ -12898,7 +13024,7 @@
 画面表示も Excel / テキストの出力も行わない)</t>
         </is>
       </c>
-      <c r="D56" s="6" t="inlineStr">
+      <c r="D58" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">./build_and_verify.sh --verify-startup \
     --compose-service app --startup-service app \
@@ -12907,23 +13033,23 @@
         </is>
       </c>
     </row>
-    <row r="57" ht="82.5" customHeight="1">
-      <c r="A57" s="11" t="inlineStr">
+    <row r="59" ht="82.5" customHeight="1">
+      <c r="A59" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">build_and_verify.sh</t>
         </is>
       </c>
-      <c r="B57" s="7" t="inlineStr">
+      <c r="B59" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">17-2</t>
         </is>
       </c>
-      <c r="C57" s="3" t="inlineStr">
+      <c r="C59" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">解析結果を画面でも読む (既定は非表示)</t>
         </is>
       </c>
-      <c r="D57" s="6" t="inlineStr">
+      <c r="D59" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">./build_and_verify.sh --verify-startup \
     --compose-service app --startup-service app \
@@ -12933,24 +13059,24 @@
         </is>
       </c>
     </row>
-    <row r="58" ht="66.0" customHeight="1">
-      <c r="A58" s="11" t="inlineStr">
+    <row r="60" ht="66.0" customHeight="1">
+      <c r="A60" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">build_and_verify.sh</t>
         </is>
       </c>
-      <c r="B58" s="7" t="inlineStr">
+      <c r="B60" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">17-3</t>
         </is>
       </c>
-      <c r="C58" s="3" t="inlineStr">
+      <c r="C60" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Java 例外解析の Excel / テキストを任意のパスへ出力する
 (テキストは --deploy-exception-text を指定したときだけ出力される)</t>
         </is>
       </c>
-      <c r="D58" s="6" t="inlineStr">
+      <c r="D60" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">./build_and_verify.sh --verify-startup \
     --compose-service app --startup-service app \
@@ -12959,40 +13085,40 @@
         </is>
       </c>
     </row>
-    <row r="59" ht="33.0" customHeight="1">
-      <c r="A59" s="11" t="inlineStr">
+    <row r="61" ht="33.0" customHeight="1">
+      <c r="A61" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">build_and_verify.sh</t>
         </is>
       </c>
-      <c r="B59" s="7" t="inlineStr">
+      <c r="B61" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">17-4</t>
         </is>
       </c>
-      <c r="C59" s="3" t="inlineStr">
+      <c r="C61" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Java 例外解析を行わない (解析処理ごと省く)</t>
         </is>
       </c>
-      <c r="D59" s="6" t="inlineStr">
+      <c r="D61" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">./build_and_verify.sh --verify-startup --no-deploy-exception-analysis</t>
         </is>
       </c>
     </row>
-    <row r="60" ht="198.0" customHeight="1">
-      <c r="A60" s="11" t="inlineStr">
+    <row r="62" ht="198.0" customHeight="1">
+      <c r="A62" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">build_and_verify.sh</t>
         </is>
       </c>
-      <c r="B60" s="7" t="inlineStr">
+      <c r="B62" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">17-5</t>
         </is>
       </c>
-      <c r="C60" s="3" t="inlineStr">
+      <c r="C62" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">読み取り専用ファイルシステム (read_only) の書き込み先分析
 既定で毎回実行される。--report-dir があれば
@@ -13002,7 +13128,7 @@
 対象から外し、entrypoint.sh などが起動のたびに書く場所を「要対応」に挙げる</t>
         </is>
       </c>
-      <c r="D60" s="6" t="inlineStr">
+      <c r="D62" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">./build_and_verify.sh --verify-startup \
     --compose-service app --startup-service app \
@@ -13011,23 +13137,23 @@
         </is>
       </c>
     </row>
-    <row r="61" ht="66.0" customHeight="1">
-      <c r="A61" s="11" t="inlineStr">
+    <row r="63" ht="66.0" customHeight="1">
+      <c r="A63" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">build_and_verify.sh</t>
         </is>
       </c>
-      <c r="B61" s="7" t="inlineStr">
+      <c r="B63" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">17-6</t>
         </is>
       </c>
-      <c r="C61" s="3" t="inlineStr">
+      <c r="C63" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">読み取り専用ファイルシステム分析の Excel / テキストを任意のパスへ出力する</t>
         </is>
       </c>
-      <c r="D61" s="6" t="inlineStr">
+      <c r="D63" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">./build_and_verify.sh --verify-startup \
     --compose-service app --startup-service app \
@@ -13036,24 +13162,24 @@
         </is>
       </c>
     </row>
-    <row r="62" ht="66.0" customHeight="1">
-      <c r="A62" s="11" t="inlineStr">
+    <row r="64" ht="66.0" customHeight="1">
+      <c r="A64" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">build_and_verify.sh</t>
         </is>
       </c>
-      <c r="B62" s="7" t="inlineStr">
+      <c r="B64" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">17-7</t>
         </is>
       </c>
-      <c r="C62" s="3" t="inlineStr">
+      <c r="C64" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">読み取り専用ファイルシステム分析の結果を画面でも読む
 既定では画面へ出さず、Excel / テキストへ残すだけ</t>
         </is>
       </c>
-      <c r="D62" s="6" t="inlineStr">
+      <c r="D64" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">./build_and_verify.sh --verify-startup \
     --compose-service app --startup-service app \
@@ -13061,85 +13187,85 @@
         </is>
       </c>
     </row>
-    <row r="63" ht="33.0" customHeight="1">
-      <c r="A63" s="11" t="inlineStr">
+    <row r="65" ht="33.0" customHeight="1">
+      <c r="A65" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">build_and_verify.sh</t>
         </is>
       </c>
-      <c r="B63" s="7" t="inlineStr">
+      <c r="B65" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">17-8</t>
         </is>
       </c>
-      <c r="C63" s="3" t="inlineStr">
+      <c r="C65" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">読み取り専用ファイルシステムの分析を行わない</t>
         </is>
       </c>
-      <c r="D63" s="6" t="inlineStr">
+      <c r="D65" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">./build_and_verify.sh --verify-startup --no-readonly-analysis</t>
         </is>
       </c>
     </row>
-    <row r="64" ht="66.0" customHeight="1">
-      <c r="A64" s="11" t="inlineStr">
+    <row r="66" ht="66.0" customHeight="1">
+      <c r="A66" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">build_and_verify.sh</t>
         </is>
       </c>
-      <c r="B64" s="7" t="inlineStr">
+      <c r="B66" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">18</t>
         </is>
       </c>
-      <c r="C64" s="3" t="inlineStr">
+      <c r="C66" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">ビルドが exporting layers から進まないときの調査
 進捗を 10 秒ごとに表示し、60 秒出力が途切れたら診断を出す</t>
         </is>
       </c>
-      <c r="D64" s="6" t="inlineStr">
+      <c r="D66" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">./build_and_verify.sh --build-progress-interval 10 --build-stall-timeout 60</t>
         </is>
       </c>
     </row>
-    <row r="65" ht="33.0" customHeight="1">
-      <c r="A65" s="11" t="inlineStr">
+    <row r="67" ht="33.0" customHeight="1">
+      <c r="A67" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">build_and_verify.sh</t>
         </is>
       </c>
-      <c r="B65" s="7" t="inlineStr">
+      <c r="B67" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">19</t>
         </is>
       </c>
-      <c r="C65" s="3" t="inlineStr">
+      <c r="C67" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">30 分を超えたらビルドを中断して確実にプロンプトを戻す</t>
         </is>
       </c>
-      <c r="D65" s="6" t="inlineStr">
+      <c r="D67" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">./build_and_verify.sh --build-timeout 1800</t>
         </is>
       </c>
     </row>
-    <row r="66" ht="132.0" customHeight="1">
-      <c r="A66" s="11" t="inlineStr">
+    <row r="68" ht="132.0" customHeight="1">
+      <c r="A68" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">build_and_verify.sh</t>
         </is>
       </c>
-      <c r="B66" s="7" t="inlineStr">
+      <c r="B68" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">20</t>
         </is>
       </c>
-      <c r="C66" s="3" t="inlineStr">
+      <c r="C68" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">ECS サーキットブレーカによるタスク停止の再現 (既定で有効)
 必須コンテナの healthcheck が unhealthy になった実行でだけ動く。
@@ -13147,7 +13273,7 @@
 停止前後の server.log を突き合わせて切れ方まで判定する</t>
         </is>
       </c>
-      <c r="D66" s="6" t="inlineStr">
+      <c r="D68" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">./build_and_verify.sh --verify-startup \
     --compose-service app --startup-service app \
@@ -13155,24 +13281,24 @@
         </is>
       </c>
     </row>
-    <row r="67" ht="66.0" customHeight="1">
-      <c r="A67" s="11" t="inlineStr">
+    <row r="69" ht="66.0" customHeight="1">
+      <c r="A69" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">build_and_verify.sh</t>
         </is>
       </c>
-      <c r="B67" s="7" t="inlineStr">
+      <c r="B69" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">20-2</t>
         </is>
       </c>
-      <c r="C67" s="3" t="inlineStr">
+      <c r="C69" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">正常に起動する構成でも、事象を手元で起こしてみる
 (動作確認をすべて終えた後に 1 回だけ停止する。置き換えは行わない)</t>
         </is>
       </c>
-      <c r="D67" s="6" t="inlineStr">
+      <c r="D69" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">./build_and_verify.sh --verify-startup \
     --compose-service app --startup-service app \
@@ -13180,75 +13306,75 @@
         </is>
       </c>
     </row>
-    <row r="68" ht="33.0" customHeight="1">
-      <c r="A68" s="11" t="inlineStr">
+    <row r="70" ht="33.0" customHeight="1">
+      <c r="A70" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">build_and_verify.sh</t>
         </is>
       </c>
-      <c r="B68" s="7" t="inlineStr">
+      <c r="B70" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">20-3</t>
         </is>
       </c>
-      <c r="C68" s="3" t="inlineStr">
+      <c r="C70" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">SIGKILL を早めて reload との重なりを作りやすくする</t>
         </is>
       </c>
-      <c r="D68" s="6" t="inlineStr">
+      <c r="D70" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">./build_and_verify.sh --verify-startup \
     --ecs-stop-timeout 5 --ecs-circuit-breaker-reload-delay 0</t>
         </is>
       </c>
     </row>
-    <row r="69" ht="33.0" customHeight="1">
-      <c r="A69" s="11" t="inlineStr">
+    <row r="71" ht="33.0" customHeight="1">
+      <c r="A71" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">build_and_verify.sh</t>
         </is>
       </c>
-      <c r="B69" s="7" t="inlineStr">
+      <c r="B71" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">20-4</t>
         </is>
       </c>
-      <c r="C69" s="3" t="inlineStr">
+      <c r="C71" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">切断の要因を切り分ける (reload を挟まず、停止だけを再現する)</t>
         </is>
       </c>
-      <c r="D69" s="6" t="inlineStr">
+      <c r="D71" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">./build_and_verify.sh --verify-startup --no-ecs-circuit-breaker-reload</t>
         </is>
       </c>
     </row>
-    <row r="70" ht="33.0" customHeight="1">
-      <c r="A70" s="11" t="inlineStr">
+    <row r="72" ht="33.0" customHeight="1">
+      <c r="A72" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">build_and_verify.sh</t>
         </is>
       </c>
-      <c r="B70" s="7" t="inlineStr">
+      <c r="B72" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">20-5</t>
         </is>
       </c>
-      <c r="C70" s="3" t="inlineStr">
+      <c r="C72" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">再現を行わない (従来どおり、unhealthy でも止めない)</t>
         </is>
       </c>
-      <c r="D70" s="6" t="inlineStr">
+      <c r="D72" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">./build_and_verify.sh --verify-startup --no-ecs-circuit-breaker</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:D70"/>
+  <autoFilter ref="A4:D72"/>
   <mergeCells count="2">
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A2:D2"/>

--- a/docs/scripts_reference.xlsx
+++ b/docs/scripts_reference.xlsx
@@ -7337,7 +7337,7 @@
         </is>
       </c>
     </row>
-    <row r="149" ht="115.5" customHeight="1">
+    <row r="149" ht="165.0" customHeight="1">
       <c r="A149" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">4.7 情報表示・レポート</t>
@@ -7365,7 +7365,7 @@
       </c>
       <c r="F149" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">全量レポートを DIR/build_and_verify_&lt;日時&gt;.txt へ保存。サービス別ビルドログ (..._build_log_&lt;サービス名&gt;.txt) と読み取り専用ファイルシステム分析の Excel / テキストも同じディレクトリへ追加出力。Java 例外解析の Excel / テキストは --deploy-exception-excel / --deploy-exception-text 指定時のみ。ディレクトリ構成のツリー Excel は --directory-tree-excel 指定時のみ。ツリーとデプロイ構造は --directory-tree-report、[10] は --deploy-exception-report、[11] は --readonly-analysis-report 併用時のみ保存</t>
+          <t xml:space="preserve">全量レポートを DIR/build_and_verify_&lt;日時&gt;.txt へ保存。サービス別ビルドログ (..._build_log_&lt;サービス名&gt;.txt) と読み取り専用ファイルシステム分析の Excel / テキストも同じディレクトリへ追加出力。logs モードの server.log の FD 点検 / ログ設定の静的点検の結果 (..._server_log_fd_&lt;サービス名&gt;.txt / ..._logging_config_audit_&lt;サービス名&gt;.txt) も同じディレクトリへ出力。Java 例外解析の Excel / テキストは --deploy-exception-excel / --deploy-exception-text 指定時のみ。ディレクトリ構成のツリー Excel は --directory-tree-excel 指定時のみ。ツリーとデプロイ構造は --directory-tree-report、[10] は --deploy-exception-report、[11] は --readonly-analysis-report 併用時のみ保存</t>
         </is>
       </c>
     </row>

--- a/docs/scripts_reference.xlsx
+++ b/docs/scripts_reference.xlsx
@@ -355,7 +355,7 @@
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">205 件</t>
+          <t xml:space="preserve">206 件</t>
         </is>
       </c>
     </row>
@@ -8297,59 +8297,63 @@
         </is>
       </c>
     </row>
-    <row r="179" ht="33.0" customHeight="1">
+    <row r="179" ht="82.5" customHeight="1">
       <c r="A179" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.8 終了時のクリーンアップ</t>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
         </is>
       </c>
       <c r="B179" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--cleanup-all-docker-data</t>
+          <t xml:space="preserve">--backend-port-offset N</t>
         </is>
       </c>
       <c r="C179" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
-        </is>
-      </c>
-      <c r="D179" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
-        </is>
-      </c>
-      <c r="E179" s="7"/>
+          <t xml:space="preserve">0〜55545 の整数</t>
+        </is>
+      </c>
+      <c r="D179" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10000</t>
+        </is>
+      </c>
+      <c r="E179" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
       <c r="F179" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">終了時に確認フレーズ入力のうえ、Docker context の全データを削除。--keep-container とは排他</t>
+          <t xml:space="preserve">ログ設定の静的点検 (--keep-container-mode logs の操作) で jboss-cli.sh --connect の管理ポート 9990 へ加算する backend の port-offset。サービス名に backend を含むサービスは --controller=localhost:&lt;9990 + N&gt; (既定 19990) で接続し、それ以外は 0 (9990)。JVM の -Djboss.socket.binding.port-offset があればそちらを優先</t>
         </is>
       </c>
     </row>
     <row r="180" ht="33.0" customHeight="1">
       <c r="A180" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
+          <t xml:space="preserve">4.8 終了時のクリーンアップ</t>
         </is>
       </c>
       <c r="B180" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">(オプション不要)</t>
+          <t xml:space="preserve">--cleanup-all-docker-data</t>
         </is>
       </c>
       <c r="C180" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">—</t>
-        </is>
-      </c>
-      <c r="D180" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">有効</t>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D180" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
         </is>
       </c>
       <c r="E180" s="7"/>
       <c r="F180" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">旧世代イメージの回収。ビルド前後で image ID を突き合わせ、世代交代した旧 ID がどのタグからも参照されていない場合だけ削除する</t>
+          <t xml:space="preserve">終了時に確認フレーズ入力のうえ、Docker context の全データを削除。--keep-container とは排他</t>
         </is>
       </c>
     </row>
@@ -8361,23 +8365,23 @@
       </c>
       <c r="B181" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-reclaim-old-image</t>
+          <t xml:space="preserve">(オプション不要)</t>
         </is>
       </c>
       <c r="C181" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
-        </is>
-      </c>
-      <c r="D181" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="D181" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">有効</t>
         </is>
       </c>
       <c r="E181" s="7"/>
       <c r="F181" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">旧世代イメージの回収を行わない (従来どおり残す)</t>
+          <t xml:space="preserve">旧世代イメージの回収。ビルド前後で image ID を突き合わせ、世代交代した旧 ID がどのタグからも参照されていない場合だけ削除する</t>
         </is>
       </c>
     </row>
@@ -8389,7 +8393,7 @@
       </c>
       <c r="B182" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--prune-build-cache</t>
+          <t xml:space="preserve">--no-reclaim-old-image</t>
         </is>
       </c>
       <c r="C182" s="3" t="inlineStr">
@@ -8405,7 +8409,7 @@
       <c r="E182" s="7"/>
       <c r="F182" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">終了時に docker builder prune --all --force を実行</t>
+          <t xml:space="preserve">旧世代イメージの回収を行わない (従来どおり残す)</t>
         </is>
       </c>
     </row>
@@ -8417,23 +8421,23 @@
       </c>
       <c r="B183" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--prune-build-cache-keep SIZE</t>
+          <t xml:space="preserve">--prune-build-cache</t>
         </is>
       </c>
       <c r="C183" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">サイズ (10GB / 512MB)</t>
+          <t xml:space="preserve">フラグ</t>
         </is>
       </c>
       <c r="D183" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">(なし)</t>
+          <t xml:space="preserve">false</t>
         </is>
       </c>
       <c r="E183" s="7"/>
       <c r="F183" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">終了時に docker builder prune --force --keep-storage SIZE を実行。指定すると --prune-build-cache も暗黙に有効化</t>
+          <t xml:space="preserve">終了時に docker builder prune --all --force を実行</t>
         </is>
       </c>
     </row>
@@ -8445,35 +8449,35 @@
       </c>
       <c r="B184" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--disk-usage-report</t>
+          <t xml:space="preserve">--prune-build-cache-keep SIZE</t>
         </is>
       </c>
       <c r="C184" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
+          <t xml:space="preserve">サイズ (10GB / 512MB)</t>
         </is>
       </c>
       <c r="D184" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">(なし)</t>
         </is>
       </c>
       <c r="E184" s="7"/>
       <c r="F184" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ビルド前と終了時に Docker 管理対象の使用量を測定し、実行前からの増減を表示 (削除は行わない)</t>
-        </is>
-      </c>
-    </row>
-    <row r="185" ht="66.0" customHeight="1">
+          <t xml:space="preserve">終了時に docker builder prune --force --keep-storage SIZE を実行。指定すると --prune-build-cache も暗黙に有効化</t>
+        </is>
+      </c>
+    </row>
+    <row r="185" ht="33.0" customHeight="1">
       <c r="A185" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.8-3 ホスト側システムログ (/var/log/messages) への出力抑制</t>
+          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
         </is>
       </c>
       <c r="B185" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--suppress-syslog</t>
+          <t xml:space="preserve">--disk-usage-report</t>
         </is>
       </c>
       <c r="C185" s="3" t="inlineStr">
@@ -8481,19 +8485,19 @@
           <t xml:space="preserve">フラグ</t>
         </is>
       </c>
-      <c r="D185" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">有効</t>
+      <c r="D185" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
         </is>
       </c>
       <c r="E185" s="7"/>
       <c r="F185" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">/var/log/messages への docker 関連ログを抑制する。(1) journald / syslog になるサービスのログドライバを差し替える (元の compose ファイルは変更しない) (2) 存在確認の docker inspect を、エラーにならない一覧 API へ置き換える</t>
-        </is>
-      </c>
-    </row>
-    <row r="186" ht="49.5" customHeight="1">
+          <t xml:space="preserve">ビルド前と終了時に Docker 管理対象の使用量を測定し、実行前からの増減を表示 (削除は行わない)</t>
+        </is>
+      </c>
+    </row>
+    <row r="186" ht="66.0" customHeight="1">
       <c r="A186" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">4.8-3 ホスト側システムログ (/var/log/messages) への出力抑制</t>
@@ -8501,7 +8505,7 @@
       </c>
       <c r="B186" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-suppress-syslog</t>
+          <t xml:space="preserve">--suppress-syslog</t>
         </is>
       </c>
       <c r="C186" s="3" t="inlineStr">
@@ -8509,15 +8513,15 @@
           <t xml:space="preserve">フラグ</t>
         </is>
       </c>
-      <c r="D186" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
+      <c r="D186" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">有効</t>
         </is>
       </c>
       <c r="E186" s="7"/>
       <c r="F186" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">上記の抑制を行わず、従来どおりの動作にする</t>
+          <t xml:space="preserve">/var/log/messages への docker 関連ログを抑制する。(1) journald / syslog になるサービスのログドライバを差し替える (元の compose ファイルは変更しない) (2) 存在確認の docker inspect を、エラーにならない一覧 API へ置き換える</t>
         </is>
       </c>
     </row>
@@ -8529,23 +8533,23 @@
       </c>
       <c r="B187" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--syslog-log-driver DRIVER</t>
+          <t xml:space="preserve">--no-suppress-syslog</t>
         </is>
       </c>
       <c r="C187" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">json-file / local</t>
-        </is>
-      </c>
-      <c r="D187" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">json-file</t>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D187" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
         </is>
       </c>
       <c r="E187" s="7"/>
       <c r="F187" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">コンテナログの差し替え先ドライバ。journald / syslog は抑制にならず、none は起動確認のログが読めなくなるため受け付けない</t>
+          <t xml:space="preserve">上記の抑制を行わず、従来どおりの動作にする</t>
         </is>
       </c>
     </row>
@@ -8557,23 +8561,23 @@
       </c>
       <c r="B188" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--syslog-audit</t>
+          <t xml:space="preserve">--syslog-log-driver DRIVER</t>
         </is>
       </c>
       <c r="C188" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
-        </is>
-      </c>
-      <c r="D188" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">json-file / local</t>
+        </is>
+      </c>
+      <c r="D188" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">json-file</t>
         </is>
       </c>
       <c r="E188" s="7"/>
       <c r="F188" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">実行前後で /var/log/messages の行数を数え、増えた分を出力元別に集計して表示する (読み取りに root 権限が必要)</t>
+          <t xml:space="preserve">コンテナログの差し替え先ドライバ。journald / syslog は抑制にならず、none は起動確認のログが読めなくなるため受け付けない</t>
         </is>
       </c>
     </row>
@@ -8585,7 +8589,7 @@
       </c>
       <c r="B189" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-syslog-audit</t>
+          <t xml:space="preserve">--syslog-audit</t>
         </is>
       </c>
       <c r="C189" s="3" t="inlineStr">
@@ -8593,15 +8597,15 @@
           <t xml:space="preserve">フラグ</t>
         </is>
       </c>
-      <c r="D189" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">有効</t>
+      <c r="D189" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
         </is>
       </c>
       <c r="E189" s="7"/>
       <c r="F189" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">増加量の計測を行わない</t>
+          <t xml:space="preserve">実行前後で /var/log/messages の行数を数え、増えた分を出力元別に集計して表示する (読み取りに root 権限が必要)</t>
         </is>
       </c>
     </row>
@@ -8613,61 +8617,73 @@
       </c>
       <c r="B190" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--syslog-audit-file FILE</t>
+          <t xml:space="preserve">--no-syslog-audit</t>
         </is>
       </c>
       <c r="C190" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ファイルパス</t>
+          <t xml:space="preserve">フラグ</t>
         </is>
       </c>
       <c r="D190" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">/var/log/messages</t>
+          <t xml:space="preserve">有効</t>
         </is>
       </c>
       <c r="E190" s="7"/>
       <c r="F190" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">計測対象のログファイル。指定すると --syslog-audit も有効になる</t>
-        </is>
-      </c>
-    </row>
-    <row r="191" ht="19.5" customHeight="1">
+          <t xml:space="preserve">増加量の計測を行わない</t>
+        </is>
+      </c>
+    </row>
+    <row r="191" ht="49.5" customHeight="1">
       <c r="A191" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.9 その他</t>
+          <t xml:space="preserve">4.8-3 ホスト側システムログ (/var/log/messages) への出力抑制</t>
         </is>
       </c>
       <c r="B191" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">-h, --help</t>
-        </is>
-      </c>
-      <c r="C191" s="3"/>
-      <c r="D191" s="3"/>
+          <t xml:space="preserve">--syslog-audit-file FILE</t>
+        </is>
+      </c>
+      <c r="C191" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ファイルパス</t>
+        </is>
+      </c>
+      <c r="D191" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">/var/log/messages</t>
+        </is>
+      </c>
       <c r="E191" s="7"/>
       <c r="F191" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ヘルプを表示して exit 0</t>
-        </is>
-      </c>
-    </row>
-    <row r="192" ht="33.0" customHeight="1">
+          <t xml:space="preserve">計測対象のログファイル。指定すると --syslog-audit も有効になる</t>
+        </is>
+      </c>
+    </row>
+    <row r="192" ht="19.5" customHeight="1">
       <c r="A192" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.4-3 対話 bash セッションの tree</t>
+          <t xml:space="preserve">4.9 その他</t>
         </is>
       </c>
       <c r="B192" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">-a</t>
+          <t xml:space="preserve">-h, --help</t>
         </is>
       </c>
       <c r="C192" s="3"/>
       <c r="D192" s="3"/>
       <c r="E192" s="7"/>
-      <c r="F192" s="3"/>
+      <c r="F192" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ヘルプを表示して exit 0</t>
+        </is>
+      </c>
     </row>
     <row r="193" ht="33.0" customHeight="1">
       <c r="A193" s="11" t="inlineStr">
@@ -8677,7 +8693,7 @@
       </c>
       <c r="B193" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">-d</t>
+          <t xml:space="preserve">-a</t>
         </is>
       </c>
       <c r="C193" s="3"/>
@@ -8693,7 +8709,7 @@
       </c>
       <c r="B194" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">-f</t>
+          <t xml:space="preserve">-d</t>
         </is>
       </c>
       <c r="C194" s="3"/>
@@ -8709,7 +8725,7 @@
       </c>
       <c r="B195" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">-L 深さ</t>
+          <t xml:space="preserve">-f</t>
         </is>
       </c>
       <c r="C195" s="3"/>
@@ -8725,7 +8741,7 @@
       </c>
       <c r="B196" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--noreport</t>
+          <t xml:space="preserve">-L 深さ</t>
         </is>
       </c>
       <c r="C196" s="3"/>
@@ -8736,22 +8752,18 @@
     <row r="197" ht="33.0" customHeight="1">
       <c r="A197" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+          <t xml:space="preserve">5.4-3 対話 bash セッションの tree</t>
         </is>
       </c>
       <c r="B197" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">(未指定)</t>
+          <t xml:space="preserve">--noreport</t>
         </is>
       </c>
       <c r="C197" s="3"/>
       <c r="D197" s="3"/>
       <c r="E197" s="7"/>
-      <c r="F197" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">画面表示・レポート出力とも行わない (既定)。画面には有効化方法を 1 行だけ案内する</t>
-        </is>
-      </c>
+      <c r="F197" s="3"/>
     </row>
     <row r="198" ht="33.0" customHeight="1">
       <c r="A198" s="11" t="inlineStr">
@@ -8761,7 +8773,7 @@
       </c>
       <c r="B198" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-tree</t>
+          <t xml:space="preserve">(未指定)</t>
         </is>
       </c>
       <c r="C198" s="3"/>
@@ -8769,7 +8781,7 @@
       <c r="E198" s="7"/>
       <c r="F198" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">画面へツリーと JBoss EAP デプロイ構造を表示する</t>
+          <t xml:space="preserve">画面表示・レポート出力とも行わない (既定)。画面には有効化方法を 1 行だけ案内する</t>
         </is>
       </c>
     </row>
@@ -8781,7 +8793,7 @@
       </c>
       <c r="B199" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-directory-tree</t>
+          <t xml:space="preserve">--directory-tree</t>
         </is>
       </c>
       <c r="C199" s="3"/>
@@ -8789,7 +8801,7 @@
       <c r="E199" s="7"/>
       <c r="F199" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">画面表示を行わない。下記オプションによる自動有効化も打ち消す</t>
+          <t xml:space="preserve">画面へツリーと JBoss EAP デプロイ構造を表示する</t>
         </is>
       </c>
     </row>
@@ -8801,7 +8813,7 @@
       </c>
       <c r="B200" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-tree-report</t>
+          <t xml:space="preserve">--no-directory-tree</t>
         </is>
       </c>
       <c r="C200" s="3"/>
@@ -8809,7 +8821,7 @@
       <c r="E200" s="7"/>
       <c r="F200" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">--report-dir の全量レポート [3] [4] へ出力する (画面表示とは独立)</t>
+          <t xml:space="preserve">画面表示を行わない。下記オプションによる自動有効化も打ち消す</t>
         </is>
       </c>
     </row>
@@ -8821,7 +8833,7 @@
       </c>
       <c r="B201" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-directory-tree-report</t>
+          <t xml:space="preserve">--directory-tree-report</t>
         </is>
       </c>
       <c r="C201" s="3"/>
@@ -8829,7 +8841,7 @@
       <c r="E201" s="7"/>
       <c r="F201" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">全量レポートへ出力しない (既定)</t>
+          <t xml:space="preserve">--report-dir の全量レポート [3] [4] へ出力する (画面表示とは独立)</t>
         </is>
       </c>
     </row>
@@ -8841,7 +8853,7 @@
       </c>
       <c r="B202" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-tree-excel</t>
+          <t xml:space="preserve">--no-directory-tree-report</t>
         </is>
       </c>
       <c r="C202" s="3"/>
@@ -8849,7 +8861,7 @@
       <c r="E202" s="7"/>
       <c r="F202" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ディレクトリとシンボリックリンクのツリーを Excel ブックへ追加出力する (frontend / backend の両方が対象。リンク先は右端の列)</t>
+          <t xml:space="preserve">全量レポートへ出力しない (既定)</t>
         </is>
       </c>
     </row>
@@ -8861,7 +8873,7 @@
       </c>
       <c r="B203" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-directory-tree-excel</t>
+          <t xml:space="preserve">--directory-tree-excel</t>
         </is>
       </c>
       <c r="C203" s="3"/>
@@ -8869,7 +8881,7 @@
       <c r="E203" s="7"/>
       <c r="F203" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">上記の Excel 出力を行わない (既定)</t>
+          <t xml:space="preserve">ディレクトリとシンボリックリンクのツリーを Excel ブックへ追加出力する (frontend / backend の両方が対象。リンク先は右端の列)</t>
         </is>
       </c>
     </row>
@@ -8881,7 +8893,7 @@
       </c>
       <c r="B204" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-tree-excel-file FILE</t>
+          <t xml:space="preserve">--no-directory-tree-excel</t>
         </is>
       </c>
       <c r="C204" s="3"/>
@@ -8889,7 +8901,7 @@
       <c r="E204" s="7"/>
       <c r="F204" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">上記 Excel の出力先を明示指定する (.xlsx)。指定すると Excel 出力を有効にする</t>
+          <t xml:space="preserve">上記の Excel 出力を行わない (既定)</t>
         </is>
       </c>
     </row>
@@ -8901,7 +8913,7 @@
       </c>
       <c r="B205" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-tree-depth N</t>
+          <t xml:space="preserve">--directory-tree-excel-file FILE</t>
         </is>
       </c>
       <c r="C205" s="3"/>
@@ -8909,7 +8921,7 @@
       <c r="E205" s="7"/>
       <c r="F205" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">/ 直下を深さ 1 として N 階層まで表示 (既定 all は最下層まで)。指定すると画面表示を自動で有効化</t>
+          <t xml:space="preserve">上記 Excel の出力先を明示指定する (.xlsx)。指定すると Excel 出力を有効にする</t>
         </is>
       </c>
     </row>
@@ -8921,7 +8933,7 @@
       </c>
       <c r="B206" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-file-limit N</t>
+          <t xml:space="preserve">--directory-tree-depth N</t>
         </is>
       </c>
       <c r="C206" s="3"/>
@@ -8929,7 +8941,7 @@
       <c r="E206" s="7"/>
       <c r="F206" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">通常ファイルを表示。各ディレクトリ直下が N 件以下なら全ファイル名、超過時は拡張子別件数。指定すると画面表示を自動で有効化</t>
+          <t xml:space="preserve">/ 直下を深さ 1 として N 階層まで表示 (既定 all は最下層まで)。指定すると画面表示を自動で有効化</t>
         </is>
       </c>
     </row>
@@ -8941,7 +8953,7 @@
       </c>
       <c r="B207" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-file-limit all</t>
+          <t xml:space="preserve">--directory-file-limit N</t>
         </is>
       </c>
       <c r="C207" s="3"/>
@@ -8949,7 +8961,7 @@
       <c r="E207" s="7"/>
       <c r="F207" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">件数にかかわらず全ファイル名を表示</t>
+          <t xml:space="preserve">通常ファイルを表示。各ディレクトリ直下が N 件以下なら全ファイル名、超過時は拡張子別件数。指定すると画面表示を自動で有効化</t>
         </is>
       </c>
     </row>
@@ -8961,7 +8973,7 @@
       </c>
       <c r="B208" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--deployment-dir-env NAME</t>
+          <t xml:space="preserve">--directory-file-limit all</t>
         </is>
       </c>
       <c r="C208" s="3"/>
@@ -8969,7 +8981,7 @@
       <c r="E208" s="7"/>
       <c r="F208" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">指定した環境変数のディレクトリも表示対象へ追加。指定すると画面表示を自動で有効化</t>
+          <t xml:space="preserve">件数にかかわらず全ファイル名を表示</t>
         </is>
       </c>
     </row>
@@ -8981,7 +8993,7 @@
       </c>
       <c r="B209" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">ファイル表示の既定</t>
+          <t xml:space="preserve">--deployment-dir-env NAME</t>
         </is>
       </c>
       <c r="C209" s="3"/>
@@ -8989,12 +9001,32 @@
       <c r="E209" s="7"/>
       <c r="F209" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">指定した環境変数のディレクトリも表示対象へ追加。指定すると画面表示を自動で有効化</t>
+        </is>
+      </c>
+    </row>
+    <row r="210" ht="33.0" customHeight="1">
+      <c r="A210" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+        </is>
+      </c>
+      <c r="B210" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ファイル表示の既定</t>
+        </is>
+      </c>
+      <c r="C210" s="3"/>
+      <c r="D210" s="3"/>
+      <c r="E210" s="7"/>
+      <c r="F210" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">表示を有効にした場合もディレクトリのみ (通常ファイルは --directory-file-limit 指定時のみ)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:F209"/>
+  <autoFilter ref="A4:F210"/>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A2:F2"/>

--- a/docs/scripts_reference.xlsx
+++ b/docs/scripts_reference.xlsx
@@ -355,7 +355,7 @@
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">206 件</t>
+          <t xml:space="preserve">208 件</t>
         </is>
       </c>
     </row>
@@ -7337,7 +7337,7 @@
         </is>
       </c>
     </row>
-    <row r="149" ht="165.0" customHeight="1">
+    <row r="149" ht="198.0" customHeight="1">
       <c r="A149" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">4.7 情報表示・レポート</t>
@@ -7365,7 +7365,7 @@
       </c>
       <c r="F149" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">全量レポートを DIR/build_and_verify_&lt;日時&gt;.txt へ保存。サービス別ビルドログ (..._build_log_&lt;サービス名&gt;.txt) と読み取り専用ファイルシステム分析の Excel / テキストも同じディレクトリへ追加出力。logs モードの server.log の FD 点検 / ログ設定の静的点検の結果 (..._server_log_fd_&lt;サービス名&gt;.txt / ..._logging_config_audit_&lt;サービス名&gt;.txt) も同じディレクトリへ出力。Java 例外解析の Excel / テキストは --deploy-exception-excel / --deploy-exception-text 指定時のみ。ディレクトリ構成のツリー Excel は --directory-tree-excel 指定時のみ。ツリーとデプロイ構造は --directory-tree-report、[10] は --deploy-exception-report、[11] は --readonly-analysis-report 併用時のみ保存</t>
+          <t xml:space="preserve">全量レポートを DIR/build_and_verify_&lt;日時&gt;.txt へ保存。サービス別ビルドログ (..._build_log_&lt;サービス名&gt;.txt) と読み取り専用ファイルシステム分析の Excel / テキストも同じディレクトリへ追加出力。logs モードの server.log の FD 点検 / ログ設定の静的点検の結果 (..._server_log_fd_&lt;サービス名&gt;.txt / ..._logging_config_audit_&lt;サービス名&gt;.txt) も同じディレクトリへ出力。ログローテーションのタイムゾーン点検の結果 (..._log_rotation_tz_&lt;サービス名&gt;.md) も既定で同じディレクトリへ出力 (--no-log-rotation-tz-md で抑制)。Java 例外解析の Excel / テキストは --deploy-exception-excel / --deploy-exception-text 指定時のみ。ディレクトリ構成のツリー Excel は --directory-tree-excel 指定時のみ。ツリーとデプロイ構造は --directory-tree-report、[10] は --deploy-exception-report、[11] は --readonly-analysis-report 併用時のみ保存</t>
         </is>
       </c>
     </row>
@@ -8329,71 +8329,79 @@
         </is>
       </c>
     </row>
-    <row r="180" ht="33.0" customHeight="1">
+    <row r="180" ht="66.0" customHeight="1">
       <c r="A180" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.8 終了時のクリーンアップ</t>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
         </is>
       </c>
       <c r="B180" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--cleanup-all-docker-data</t>
+          <t xml:space="preserve">--log-rotation-tz-md FILE</t>
         </is>
       </c>
       <c r="C180" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
+          <t xml:space="preserve">ファイルパス</t>
         </is>
       </c>
       <c r="D180" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">false</t>
-        </is>
-      </c>
-      <c r="E180" s="7"/>
+          <t xml:space="preserve">(なし)</t>
+        </is>
+      </c>
+      <c r="E180" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
       <c r="F180" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">終了時に確認フレーズ入力のうえ、Docker context の全データを削除。--keep-container とは排他</t>
+          <t xml:space="preserve">ログローテーションのタイムゾーン点検 (--keep-container-mode logs の操作) の結果を Markdown で出力する先。未指定時は --report-dir 配下 (無ければ一時ディレクトリ) へ build_and_verify_&lt;日時&gt;_log_rotation_tz_&lt;サービス名&gt;.md として自動命名。--no-log-rotation-tz-md とは排他</t>
         </is>
       </c>
     </row>
     <row r="181" ht="33.0" customHeight="1">
       <c r="A181" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
+          <t xml:space="preserve">4.7 情報表示・レポート</t>
         </is>
       </c>
       <c r="B181" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">(オプション不要)</t>
+          <t xml:space="preserve">--no-log-rotation-tz-md</t>
         </is>
       </c>
       <c r="C181" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">—</t>
-        </is>
-      </c>
-      <c r="D181" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">有効</t>
-        </is>
-      </c>
-      <c r="E181" s="7"/>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D181" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="E181" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
       <c r="F181" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">旧世代イメージの回収。ビルド前後で image ID を突き合わせ、世代交代した旧 ID がどのタグからも参照されていない場合だけ削除する</t>
+          <t xml:space="preserve">ログローテーションのタイムゾーン点検の Markdown 出力を行わない (画面表示だけにする)</t>
         </is>
       </c>
     </row>
     <row r="182" ht="33.0" customHeight="1">
       <c r="A182" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
+          <t xml:space="preserve">4.8 終了時のクリーンアップ</t>
         </is>
       </c>
       <c r="B182" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-reclaim-old-image</t>
+          <t xml:space="preserve">--cleanup-all-docker-data</t>
         </is>
       </c>
       <c r="C182" s="3" t="inlineStr">
@@ -8409,7 +8417,7 @@
       <c r="E182" s="7"/>
       <c r="F182" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">旧世代イメージの回収を行わない (従来どおり残す)</t>
+          <t xml:space="preserve">終了時に確認フレーズ入力のうえ、Docker context の全データを削除。--keep-container とは排他</t>
         </is>
       </c>
     </row>
@@ -8421,23 +8429,23 @@
       </c>
       <c r="B183" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--prune-build-cache</t>
+          <t xml:space="preserve">(オプション不要)</t>
         </is>
       </c>
       <c r="C183" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
-        </is>
-      </c>
-      <c r="D183" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="D183" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">有効</t>
         </is>
       </c>
       <c r="E183" s="7"/>
       <c r="F183" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">終了時に docker builder prune --all --force を実行</t>
+          <t xml:space="preserve">旧世代イメージの回収。ビルド前後で image ID を突き合わせ、世代交代した旧 ID がどのタグからも参照されていない場合だけ削除する</t>
         </is>
       </c>
     </row>
@@ -8449,23 +8457,23 @@
       </c>
       <c r="B184" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--prune-build-cache-keep SIZE</t>
+          <t xml:space="preserve">--no-reclaim-old-image</t>
         </is>
       </c>
       <c r="C184" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">サイズ (10GB / 512MB)</t>
+          <t xml:space="preserve">フラグ</t>
         </is>
       </c>
       <c r="D184" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">(なし)</t>
+          <t xml:space="preserve">false</t>
         </is>
       </c>
       <c r="E184" s="7"/>
       <c r="F184" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">終了時に docker builder prune --force --keep-storage SIZE を実行。指定すると --prune-build-cache も暗黙に有効化</t>
+          <t xml:space="preserve">旧世代イメージの回収を行わない (従来どおり残す)</t>
         </is>
       </c>
     </row>
@@ -8477,7 +8485,7 @@
       </c>
       <c r="B185" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--disk-usage-report</t>
+          <t xml:space="preserve">--prune-build-cache</t>
         </is>
       </c>
       <c r="C185" s="3" t="inlineStr">
@@ -8493,47 +8501,47 @@
       <c r="E185" s="7"/>
       <c r="F185" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ビルド前と終了時に Docker 管理対象の使用量を測定し、実行前からの増減を表示 (削除は行わない)</t>
-        </is>
-      </c>
-    </row>
-    <row r="186" ht="66.0" customHeight="1">
+          <t xml:space="preserve">終了時に docker builder prune --all --force を実行</t>
+        </is>
+      </c>
+    </row>
+    <row r="186" ht="33.0" customHeight="1">
       <c r="A186" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.8-3 ホスト側システムログ (/var/log/messages) への出力抑制</t>
+          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
         </is>
       </c>
       <c r="B186" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--suppress-syslog</t>
+          <t xml:space="preserve">--prune-build-cache-keep SIZE</t>
         </is>
       </c>
       <c r="C186" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
-        </is>
-      </c>
-      <c r="D186" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">有効</t>
+          <t xml:space="preserve">サイズ (10GB / 512MB)</t>
+        </is>
+      </c>
+      <c r="D186" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(なし)</t>
         </is>
       </c>
       <c r="E186" s="7"/>
       <c r="F186" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">/var/log/messages への docker 関連ログを抑制する。(1) journald / syslog になるサービスのログドライバを差し替える (元の compose ファイルは変更しない) (2) 存在確認の docker inspect を、エラーにならない一覧 API へ置き換える</t>
-        </is>
-      </c>
-    </row>
-    <row r="187" ht="49.5" customHeight="1">
+          <t xml:space="preserve">終了時に docker builder prune --force --keep-storage SIZE を実行。指定すると --prune-build-cache も暗黙に有効化</t>
+        </is>
+      </c>
+    </row>
+    <row r="187" ht="33.0" customHeight="1">
       <c r="A187" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.8-3 ホスト側システムログ (/var/log/messages) への出力抑制</t>
+          <t xml:space="preserve">4.8-2 ディスク使用量の抑制</t>
         </is>
       </c>
       <c r="B187" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-suppress-syslog</t>
+          <t xml:space="preserve">--disk-usage-report</t>
         </is>
       </c>
       <c r="C187" s="3" t="inlineStr">
@@ -8549,11 +8557,11 @@
       <c r="E187" s="7"/>
       <c r="F187" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">上記の抑制を行わず、従来どおりの動作にする</t>
-        </is>
-      </c>
-    </row>
-    <row r="188" ht="49.5" customHeight="1">
+          <t xml:space="preserve">ビルド前と終了時に Docker 管理対象の使用量を測定し、実行前からの増減を表示 (削除は行わない)</t>
+        </is>
+      </c>
+    </row>
+    <row r="188" ht="66.0" customHeight="1">
       <c r="A188" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">4.8-3 ホスト側システムログ (/var/log/messages) への出力抑制</t>
@@ -8561,23 +8569,23 @@
       </c>
       <c r="B188" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--syslog-log-driver DRIVER</t>
+          <t xml:space="preserve">--suppress-syslog</t>
         </is>
       </c>
       <c r="C188" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">json-file / local</t>
+          <t xml:space="preserve">フラグ</t>
         </is>
       </c>
       <c r="D188" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">json-file</t>
+          <t xml:space="preserve">有効</t>
         </is>
       </c>
       <c r="E188" s="7"/>
       <c r="F188" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">コンテナログの差し替え先ドライバ。journald / syslog は抑制にならず、none は起動確認のログが読めなくなるため受け付けない</t>
+          <t xml:space="preserve">/var/log/messages への docker 関連ログを抑制する。(1) journald / syslog になるサービスのログドライバを差し替える (元の compose ファイルは変更しない) (2) 存在確認の docker inspect を、エラーにならない一覧 API へ置き換える</t>
         </is>
       </c>
     </row>
@@ -8589,7 +8597,7 @@
       </c>
       <c r="B189" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--syslog-audit</t>
+          <t xml:space="preserve">--no-suppress-syslog</t>
         </is>
       </c>
       <c r="C189" s="3" t="inlineStr">
@@ -8605,7 +8613,7 @@
       <c r="E189" s="7"/>
       <c r="F189" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">実行前後で /var/log/messages の行数を数え、増えた分を出力元別に集計して表示する (読み取りに root 権限が必要)</t>
+          <t xml:space="preserve">上記の抑制を行わず、従来どおりの動作にする</t>
         </is>
       </c>
     </row>
@@ -8617,23 +8625,23 @@
       </c>
       <c r="B190" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-syslog-audit</t>
+          <t xml:space="preserve">--syslog-log-driver DRIVER</t>
         </is>
       </c>
       <c r="C190" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
+          <t xml:space="preserve">json-file / local</t>
         </is>
       </c>
       <c r="D190" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">有効</t>
+          <t xml:space="preserve">json-file</t>
         </is>
       </c>
       <c r="E190" s="7"/>
       <c r="F190" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">増加量の計測を行わない</t>
+          <t xml:space="preserve">コンテナログの差し替え先ドライバ。journald / syslog は抑制にならず、none は起動確認のログが読めなくなるため受け付けない</t>
         </is>
       </c>
     </row>
@@ -8645,77 +8653,101 @@
       </c>
       <c r="B191" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--syslog-audit-file FILE</t>
+          <t xml:space="preserve">--syslog-audit</t>
         </is>
       </c>
       <c r="C191" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ファイルパス</t>
-        </is>
-      </c>
-      <c r="D191" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">/var/log/messages</t>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D191" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
         </is>
       </c>
       <c r="E191" s="7"/>
       <c r="F191" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">計測対象のログファイル。指定すると --syslog-audit も有効になる</t>
-        </is>
-      </c>
-    </row>
-    <row r="192" ht="19.5" customHeight="1">
+          <t xml:space="preserve">実行前後で /var/log/messages の行数を数え、増えた分を出力元別に集計して表示する (読み取りに root 権限が必要)</t>
+        </is>
+      </c>
+    </row>
+    <row r="192" ht="49.5" customHeight="1">
       <c r="A192" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.9 その他</t>
+          <t xml:space="preserve">4.8-3 ホスト側システムログ (/var/log/messages) への出力抑制</t>
         </is>
       </c>
       <c r="B192" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">-h, --help</t>
-        </is>
-      </c>
-      <c r="C192" s="3"/>
-      <c r="D192" s="3"/>
+          <t xml:space="preserve">--no-syslog-audit</t>
+        </is>
+      </c>
+      <c r="C192" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D192" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">有効</t>
+        </is>
+      </c>
       <c r="E192" s="7"/>
       <c r="F192" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ヘルプを表示して exit 0</t>
-        </is>
-      </c>
-    </row>
-    <row r="193" ht="33.0" customHeight="1">
+          <t xml:space="preserve">増加量の計測を行わない</t>
+        </is>
+      </c>
+    </row>
+    <row r="193" ht="49.5" customHeight="1">
       <c r="A193" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.4-3 対話 bash セッションの tree</t>
+          <t xml:space="preserve">4.8-3 ホスト側システムログ (/var/log/messages) への出力抑制</t>
         </is>
       </c>
       <c r="B193" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">-a</t>
-        </is>
-      </c>
-      <c r="C193" s="3"/>
-      <c r="D193" s="3"/>
+          <t xml:space="preserve">--syslog-audit-file FILE</t>
+        </is>
+      </c>
+      <c r="C193" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ファイルパス</t>
+        </is>
+      </c>
+      <c r="D193" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">/var/log/messages</t>
+        </is>
+      </c>
       <c r="E193" s="7"/>
-      <c r="F193" s="3"/>
-    </row>
-    <row r="194" ht="33.0" customHeight="1">
+      <c r="F193" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">計測対象のログファイル。指定すると --syslog-audit も有効になる</t>
+        </is>
+      </c>
+    </row>
+    <row r="194" ht="19.5" customHeight="1">
       <c r="A194" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.4-3 対話 bash セッションの tree</t>
+          <t xml:space="preserve">4.9 その他</t>
         </is>
       </c>
       <c r="B194" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">-d</t>
+          <t xml:space="preserve">-h, --help</t>
         </is>
       </c>
       <c r="C194" s="3"/>
       <c r="D194" s="3"/>
       <c r="E194" s="7"/>
-      <c r="F194" s="3"/>
+      <c r="F194" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ヘルプを表示して exit 0</t>
+        </is>
+      </c>
     </row>
     <row r="195" ht="33.0" customHeight="1">
       <c r="A195" s="11" t="inlineStr">
@@ -8725,7 +8757,7 @@
       </c>
       <c r="B195" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">-f</t>
+          <t xml:space="preserve">-a</t>
         </is>
       </c>
       <c r="C195" s="3"/>
@@ -8741,7 +8773,7 @@
       </c>
       <c r="B196" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">-L 深さ</t>
+          <t xml:space="preserve">-d</t>
         </is>
       </c>
       <c r="C196" s="3"/>
@@ -8757,7 +8789,7 @@
       </c>
       <c r="B197" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--noreport</t>
+          <t xml:space="preserve">-f</t>
         </is>
       </c>
       <c r="C197" s="3"/>
@@ -8768,42 +8800,34 @@
     <row r="198" ht="33.0" customHeight="1">
       <c r="A198" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+          <t xml:space="preserve">5.4-3 対話 bash セッションの tree</t>
         </is>
       </c>
       <c r="B198" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">(未指定)</t>
+          <t xml:space="preserve">-L 深さ</t>
         </is>
       </c>
       <c r="C198" s="3"/>
       <c r="D198" s="3"/>
       <c r="E198" s="7"/>
-      <c r="F198" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">画面表示・レポート出力とも行わない (既定)。画面には有効化方法を 1 行だけ案内する</t>
-        </is>
-      </c>
+      <c r="F198" s="3"/>
     </row>
     <row r="199" ht="33.0" customHeight="1">
       <c r="A199" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+          <t xml:space="preserve">5.4-3 対話 bash セッションの tree</t>
         </is>
       </c>
       <c r="B199" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-tree</t>
+          <t xml:space="preserve">--noreport</t>
         </is>
       </c>
       <c r="C199" s="3"/>
       <c r="D199" s="3"/>
       <c r="E199" s="7"/>
-      <c r="F199" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">画面へツリーと JBoss EAP デプロイ構造を表示する</t>
-        </is>
-      </c>
+      <c r="F199" s="3"/>
     </row>
     <row r="200" ht="33.0" customHeight="1">
       <c r="A200" s="11" t="inlineStr">
@@ -8813,7 +8837,7 @@
       </c>
       <c r="B200" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-directory-tree</t>
+          <t xml:space="preserve">(未指定)</t>
         </is>
       </c>
       <c r="C200" s="3"/>
@@ -8821,7 +8845,7 @@
       <c r="E200" s="7"/>
       <c r="F200" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">画面表示を行わない。下記オプションによる自動有効化も打ち消す</t>
+          <t xml:space="preserve">画面表示・レポート出力とも行わない (既定)。画面には有効化方法を 1 行だけ案内する</t>
         </is>
       </c>
     </row>
@@ -8833,7 +8857,7 @@
       </c>
       <c r="B201" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-tree-report</t>
+          <t xml:space="preserve">--directory-tree</t>
         </is>
       </c>
       <c r="C201" s="3"/>
@@ -8841,7 +8865,7 @@
       <c r="E201" s="7"/>
       <c r="F201" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">--report-dir の全量レポート [3] [4] へ出力する (画面表示とは独立)</t>
+          <t xml:space="preserve">画面へツリーと JBoss EAP デプロイ構造を表示する</t>
         </is>
       </c>
     </row>
@@ -8853,7 +8877,7 @@
       </c>
       <c r="B202" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-directory-tree-report</t>
+          <t xml:space="preserve">--no-directory-tree</t>
         </is>
       </c>
       <c r="C202" s="3"/>
@@ -8861,7 +8885,7 @@
       <c r="E202" s="7"/>
       <c r="F202" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">全量レポートへ出力しない (既定)</t>
+          <t xml:space="preserve">画面表示を行わない。下記オプションによる自動有効化も打ち消す</t>
         </is>
       </c>
     </row>
@@ -8873,7 +8897,7 @@
       </c>
       <c r="B203" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-tree-excel</t>
+          <t xml:space="preserve">--directory-tree-report</t>
         </is>
       </c>
       <c r="C203" s="3"/>
@@ -8881,7 +8905,7 @@
       <c r="E203" s="7"/>
       <c r="F203" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ディレクトリとシンボリックリンクのツリーを Excel ブックへ追加出力する (frontend / backend の両方が対象。リンク先は右端の列)</t>
+          <t xml:space="preserve">--report-dir の全量レポート [3] [4] へ出力する (画面表示とは独立)</t>
         </is>
       </c>
     </row>
@@ -8893,7 +8917,7 @@
       </c>
       <c r="B204" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--no-directory-tree-excel</t>
+          <t xml:space="preserve">--no-directory-tree-report</t>
         </is>
       </c>
       <c r="C204" s="3"/>
@@ -8901,7 +8925,7 @@
       <c r="E204" s="7"/>
       <c r="F204" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">上記の Excel 出力を行わない (既定)</t>
+          <t xml:space="preserve">全量レポートへ出力しない (既定)</t>
         </is>
       </c>
     </row>
@@ -8913,7 +8937,7 @@
       </c>
       <c r="B205" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-tree-excel-file FILE</t>
+          <t xml:space="preserve">--directory-tree-excel</t>
         </is>
       </c>
       <c r="C205" s="3"/>
@@ -8921,7 +8945,7 @@
       <c r="E205" s="7"/>
       <c r="F205" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">上記 Excel の出力先を明示指定する (.xlsx)。指定すると Excel 出力を有効にする</t>
+          <t xml:space="preserve">ディレクトリとシンボリックリンクのツリーを Excel ブックへ追加出力する (frontend / backend の両方が対象。リンク先は右端の列)</t>
         </is>
       </c>
     </row>
@@ -8933,7 +8957,7 @@
       </c>
       <c r="B206" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-tree-depth N</t>
+          <t xml:space="preserve">--no-directory-tree-excel</t>
         </is>
       </c>
       <c r="C206" s="3"/>
@@ -8941,7 +8965,7 @@
       <c r="E206" s="7"/>
       <c r="F206" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">/ 直下を深さ 1 として N 階層まで表示 (既定 all は最下層まで)。指定すると画面表示を自動で有効化</t>
+          <t xml:space="preserve">上記の Excel 出力を行わない (既定)</t>
         </is>
       </c>
     </row>
@@ -8953,7 +8977,7 @@
       </c>
       <c r="B207" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-file-limit N</t>
+          <t xml:space="preserve">--directory-tree-excel-file FILE</t>
         </is>
       </c>
       <c r="C207" s="3"/>
@@ -8961,7 +8985,7 @@
       <c r="E207" s="7"/>
       <c r="F207" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">通常ファイルを表示。各ディレクトリ直下が N 件以下なら全ファイル名、超過時は拡張子別件数。指定すると画面表示を自動で有効化</t>
+          <t xml:space="preserve">上記 Excel の出力先を明示指定する (.xlsx)。指定すると Excel 出力を有効にする</t>
         </is>
       </c>
     </row>
@@ -8973,7 +8997,7 @@
       </c>
       <c r="B208" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--directory-file-limit all</t>
+          <t xml:space="preserve">--directory-tree-depth N</t>
         </is>
       </c>
       <c r="C208" s="3"/>
@@ -8981,7 +9005,7 @@
       <c r="E208" s="7"/>
       <c r="F208" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">件数にかかわらず全ファイル名を表示</t>
+          <t xml:space="preserve">/ 直下を深さ 1 として N 階層まで表示 (既定 all は最下層まで)。指定すると画面表示を自動で有効化</t>
         </is>
       </c>
     </row>
@@ -8993,7 +9017,7 @@
       </c>
       <c r="B209" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--deployment-dir-env NAME</t>
+          <t xml:space="preserve">--directory-file-limit N</t>
         </is>
       </c>
       <c r="C209" s="3"/>
@@ -9001,7 +9025,7 @@
       <c r="E209" s="7"/>
       <c r="F209" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">指定した環境変数のディレクトリも表示対象へ追加。指定すると画面表示を自動で有効化</t>
+          <t xml:space="preserve">通常ファイルを表示。各ディレクトリ直下が N 件以下なら全ファイル名、超過時は拡張子別件数。指定すると画面表示を自動で有効化</t>
         </is>
       </c>
     </row>
@@ -9013,7 +9037,7 @@
       </c>
       <c r="B210" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">ファイル表示の既定</t>
+          <t xml:space="preserve">--directory-file-limit all</t>
         </is>
       </c>
       <c r="C210" s="3"/>
@@ -9021,12 +9045,52 @@
       <c r="E210" s="7"/>
       <c r="F210" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">件数にかかわらず全ファイル名を表示</t>
+        </is>
+      </c>
+    </row>
+    <row r="211" ht="33.0" customHeight="1">
+      <c r="A211" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+        </is>
+      </c>
+      <c r="B211" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--deployment-dir-env NAME</t>
+        </is>
+      </c>
+      <c r="C211" s="3"/>
+      <c r="D211" s="3"/>
+      <c r="E211" s="7"/>
+      <c r="F211" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">指定した環境変数のディレクトリも表示対象へ追加。指定すると画面表示を自動で有効化</t>
+        </is>
+      </c>
+    </row>
+    <row r="212" ht="33.0" customHeight="1">
+      <c r="A212" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.6 コンテナ内ディレクトリツリーの表示制御</t>
+        </is>
+      </c>
+      <c r="B212" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ファイル表示の既定</t>
+        </is>
+      </c>
+      <c r="C212" s="3"/>
+      <c r="D212" s="3"/>
+      <c r="E212" s="7"/>
+      <c r="F212" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">表示を有効にした場合もディレクトリのみ (通常ファイルは --directory-file-limit 指定時のみ)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:F210"/>
+  <autoFilter ref="A4:F212"/>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A2:F2"/>
